--- a/plantillas/20.xlsx
+++ b/plantillas/20.xlsx
@@ -1,53 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="MARCA_1">Listas!$D$2:$D$2</definedName>
     <definedName name="MARCA_2">Listas!$E$2:$E$5</definedName>
     <definedName name="MARCA_3">Listas!$F$2:$F$3</definedName>
-    <definedName name="MARCA_4">Listas!$G$2:$G$3</definedName>
-    <definedName name="MARCA_5">Listas!$H$2:$H$2</definedName>
-    <definedName name="MARCA_6">Listas!$I$2:$I$5</definedName>
-    <definedName name="MARCA_7">Listas!$J$2:$J$2</definedName>
-    <definedName name="MARCA_8">Listas!$K$2:$K$3</definedName>
+    <definedName name="MARCA_4">Listas!$G$2:$G$2</definedName>
+    <definedName name="MARCA_5">Listas!$H$2:$H$3</definedName>
+    <definedName name="MARCA_6">Listas!$I$2:$I$2</definedName>
+    <definedName name="MARCA_7">Listas!$J$2:$J$5</definedName>
+    <definedName name="MARCA_8">Listas!$K$2:$K$2</definedName>
     <definedName name="MARCA_9">Listas!$L$2:$L$3</definedName>
     <definedName name="MARCA_10">Listas!$M$2:$M$4</definedName>
-    <definedName name="MARCA_11">Listas!$N$2:$N$7</definedName>
+    <definedName name="MARCA_11">Listas!$N$2:$N$6</definedName>
     <definedName name="MARCA_12">Listas!$O$2:$O$5</definedName>
     <definedName name="MARCA_13">Listas!$P$2:$P$6</definedName>
-    <definedName name="MARCA_14">Listas!$Q$2:$Q$4</definedName>
+    <definedName name="MARCA_14">Listas!$Q$2:$Q$3</definedName>
     <definedName name="MARCA_15">Listas!$R$2:$R$2</definedName>
     <definedName name="MARCA_16">Listas!$S$2:$S$2</definedName>
     <definedName name="MARCA_17">Listas!$T$2:$T$5</definedName>
     <definedName name="MARCA_18">Listas!$U$2:$U$5</definedName>
-    <definedName name="MARCA_19">Listas!$V$2:$V$16</definedName>
+    <definedName name="MARCA_19">Listas!$V$2:$V$19</definedName>
     <definedName name="MARCA_20">Listas!$W$2:$W$18</definedName>
-    <definedName name="MARCA_21">Listas!$X$2:$X$3</definedName>
-    <definedName name="MARCA_22">Listas!$Y$2:$Y$2</definedName>
-    <definedName name="MARCA_23">Listas!$Z$2:$Z$7</definedName>
+    <definedName name="MARCA_21">Listas!$X$2:$X$2</definedName>
+    <definedName name="MARCA_22">Listas!$Y$2:$Y$7</definedName>
+    <definedName name="MARCA_23">Listas!$Z$2:$Z$5</definedName>
     <definedName name="MARCA_24">Listas!$AA$2:$AA$5</definedName>
-    <definedName name="MARCA_25">Listas!$AB$2:$AB$6</definedName>
-    <definedName name="MARCA_26">Listas!$AC$2:$AC$8</definedName>
+    <definedName name="MARCA_25">Listas!$AB$2:$AB$8</definedName>
+    <definedName name="MARCA_26">Listas!$AC$2:$AC$2</definedName>
     <definedName name="MARCA_27">Listas!$AD$2:$AD$2</definedName>
-    <definedName name="MARCA_28">Listas!$AE$2:$AE$2</definedName>
-    <definedName name="MARCA_29">Listas!$AF$2:$AF$3</definedName>
-    <definedName name="MARCA_30">Listas!$AG$2:$AG$5</definedName>
-    <definedName name="MARCA_31">Listas!$AH$2:$AH$11</definedName>
-    <definedName name="MARCA_32">Listas!$AI$2:$AI$9</definedName>
-    <definedName name="MARCA_33">Listas!$AJ$2:$AJ$2</definedName>
-    <definedName name="MARCA_34">Listas!$AK$2:$AK$5</definedName>
+    <definedName name="MARCA_28">Listas!$AE$2:$AE$3</definedName>
+    <definedName name="MARCA_29">Listas!$AF$2:$AF$5</definedName>
+    <definedName name="MARCA_30">Listas!$AG$2:$AG$10</definedName>
+    <definedName name="MARCA_31">Listas!$AH$2:$AH$9</definedName>
+    <definedName name="MARCA_32">Listas!$AI$2:$AI$2</definedName>
+    <definedName name="MARCA_33">Listas!$AJ$2:$AJ$5</definedName>
     <definedName name="MESES">Listas!$C$2:$C$5</definedName>
-    <definedName name="MARCAS">Listas!$A$2:$A$35</definedName>
+    <definedName name="MARCAS">Listas!$A$2:$A$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -652,11 +651,11 @@
       <c r="A3" s="5" t="n"/>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B3,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B3,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D3" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B3,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B3,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E3" s="8" t="n"/>
@@ -676,11 +675,11 @@
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B4,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B4,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D4" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B4,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B4,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E4" s="8" t="n"/>
@@ -700,11 +699,11 @@
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B5,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B5,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B5,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B5,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E5" s="8" t="n"/>
@@ -724,11 +723,11 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B6,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B6,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B6,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B6,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E6" s="8" t="n"/>
@@ -743,11 +742,11 @@
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B7,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B7,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B7,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B7,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -762,11 +761,11 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B8,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B8,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B8,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B8,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E8" s="8" t="n"/>
@@ -781,11 +780,11 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B9,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B9,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B9,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B9,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E9" s="8" t="n"/>
@@ -800,11 +799,11 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B10,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B10,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B10,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B10,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E10" s="8" t="n"/>
@@ -819,11 +818,11 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B11,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B11,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B11,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B11,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E11" s="8" t="n"/>
@@ -838,11 +837,11 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B12,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B12,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B12,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B12,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -857,11 +856,11 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B13,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B13,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B13,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B13,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E13" s="8" t="n"/>
@@ -876,11 +875,11 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B14,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B14,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B14,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B14,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E14" s="8" t="n"/>
@@ -895,11 +894,11 @@
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B15,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B15,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B15,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B15,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E15" s="8" t="n"/>
@@ -914,11 +913,11 @@
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B16,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B16,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B16,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B16,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E16" s="8" t="n"/>
@@ -933,11 +932,11 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B17,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B17,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B17,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B17,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E17" s="8" t="n"/>
@@ -952,11 +951,11 @@
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B18,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B18,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B18,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B18,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E18" s="8" t="n"/>
@@ -971,11 +970,11 @@
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B19,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B19,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B19,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B19,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E19" s="8" t="n"/>
@@ -990,11 +989,11 @@
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B20,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B20,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D20" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B20,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B20,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -1009,11 +1008,11 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B21,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B21,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B21,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B21,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E21" s="8" t="n"/>
@@ -1028,11 +1027,11 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B22,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B22,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B22,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B22,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E22" s="8" t="n"/>
@@ -1047,11 +1046,11 @@
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B23,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B23,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B23,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B23,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E23" s="8" t="n"/>
@@ -1066,11 +1065,11 @@
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B24,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B24,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B24,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B24,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E24" s="8" t="n"/>
@@ -1085,11 +1084,11 @@
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B25,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B25,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B25,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B25,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="8" t="n"/>
@@ -1104,11 +1103,11 @@
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B26,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B26,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B26,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B26,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -1123,11 +1122,11 @@
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B27,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B27,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B27,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B27,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -1142,11 +1141,11 @@
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B28,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B28,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B28,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B28,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E28" s="8" t="n"/>
@@ -1161,11 +1160,11 @@
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B29,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B29,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B29,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B29,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -1180,11 +1179,11 @@
       <c r="A30" s="5" t="n"/>
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B30,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B30,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B30,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B30,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -1199,11 +1198,11 @@
       <c r="A31" s="5" t="n"/>
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B31,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B31,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B31,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B31,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -1218,11 +1217,11 @@
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B32,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B32,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B32,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B32,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -1237,11 +1236,11 @@
       <c r="A33" s="5" t="n"/>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B33,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B33,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B33,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B33,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -1256,11 +1255,11 @@
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B34,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B34,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B34,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B34,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -1275,11 +1274,11 @@
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B35,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B35,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B35,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B35,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -1294,11 +1293,11 @@
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B36,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B36,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B36,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B36,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -1313,11 +1312,11 @@
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B37,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B37,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B37,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B37,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -1332,11 +1331,11 @@
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B38,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B38,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B38,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B38,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E38" s="8" t="n"/>
@@ -1351,11 +1350,11 @@
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B39,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B39,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B39,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B39,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -1370,11 +1369,11 @@
       <c r="A40" s="5" t="n"/>
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B40,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B40,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B40,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B40,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E40" s="8" t="n"/>
@@ -1389,11 +1388,11 @@
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B41,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B41,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B41,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B41,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -1408,11 +1407,11 @@
       <c r="A42" s="5" t="n"/>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B42,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B42,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B42,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B42,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -1427,11 +1426,11 @@
       <c r="A43" s="5" t="n"/>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B43,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B43,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B43,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B43,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -1446,11 +1445,11 @@
       <c r="A44" s="5" t="n"/>
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B44,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B44,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B44,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B44,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -1465,11 +1464,11 @@
       <c r="A45" s="5" t="n"/>
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B45,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B45,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B45,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B45,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -1484,11 +1483,11 @@
       <c r="A46" s="5" t="n"/>
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B46,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B46,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B46,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B46,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -1503,11 +1502,11 @@
       <c r="A47" s="5" t="n"/>
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B47,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B47,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B47,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B47,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -1522,11 +1521,11 @@
       <c r="A48" s="5" t="n"/>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B48,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B48,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B48,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B48,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -1541,11 +1540,11 @@
       <c r="A49" s="5" t="n"/>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B49,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B49,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B49,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B49,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -1560,11 +1559,11 @@
       <c r="A50" s="5" t="n"/>
       <c r="B50" s="5" t="n"/>
       <c r="C50" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B50,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B50,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B50,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B50,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -1579,11 +1578,11 @@
       <c r="A51" s="5" t="n"/>
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B51,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B51,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B51,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B51,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E51" s="8" t="n"/>
@@ -1598,11 +1597,11 @@
       <c r="A52" s="5" t="n"/>
       <c r="B52" s="5" t="n"/>
       <c r="C52" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B52,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B52,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D52" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B52,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B52,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E52" s="8" t="n"/>
@@ -1617,11 +1616,11 @@
       <c r="A53" s="5" t="n"/>
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B53,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B53,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D53" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B53,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B53,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E53" s="8" t="n"/>
@@ -1636,11 +1635,11 @@
       <c r="A54" s="5" t="n"/>
       <c r="B54" s="5" t="n"/>
       <c r="C54" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B54,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B54,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D54" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B54,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B54,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E54" s="8" t="n"/>
@@ -1655,11 +1654,11 @@
       <c r="A55" s="5" t="n"/>
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B55,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B55,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D55" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B55,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B55,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -1674,11 +1673,11 @@
       <c r="A56" s="5" t="n"/>
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B56,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B56,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D56" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B56,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B56,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E56" s="8" t="n"/>
@@ -1693,11 +1692,11 @@
       <c r="A57" s="5" t="n"/>
       <c r="B57" s="5" t="n"/>
       <c r="C57" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B57,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B57,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D57" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B57,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B57,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E57" s="8" t="n"/>
@@ -1712,11 +1711,11 @@
       <c r="A58" s="5" t="n"/>
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B58,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B58,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D58" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B58,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B58,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -1731,11 +1730,11 @@
       <c r="A59" s="5" t="n"/>
       <c r="B59" s="5" t="n"/>
       <c r="C59" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B59,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B59,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D59" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B59,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B59,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -1750,11 +1749,11 @@
       <c r="A60" s="5" t="n"/>
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B60,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B60,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D60" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B60,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B60,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -1769,11 +1768,11 @@
       <c r="A61" s="5" t="n"/>
       <c r="B61" s="5" t="n"/>
       <c r="C61" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B61,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B61,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D61" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B61,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B61,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -1788,11 +1787,11 @@
       <c r="A62" s="5" t="n"/>
       <c r="B62" s="5" t="n"/>
       <c r="C62" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B62,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B62,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D62" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B62,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B62,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E62" s="8" t="n"/>
@@ -1807,11 +1806,11 @@
       <c r="A63" s="5" t="n"/>
       <c r="B63" s="5" t="n"/>
       <c r="C63" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B63,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B63,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D63" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B63,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B63,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -1826,11 +1825,11 @@
       <c r="A64" s="5" t="n"/>
       <c r="B64" s="5" t="n"/>
       <c r="C64" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B64,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B64,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D64" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B64,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B64,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -1845,11 +1844,11 @@
       <c r="A65" s="5" t="n"/>
       <c r="B65" s="5" t="n"/>
       <c r="C65" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B65,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B65,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D65" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B65,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B65,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -1864,11 +1863,11 @@
       <c r="A66" s="5" t="n"/>
       <c r="B66" s="5" t="n"/>
       <c r="C66" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B66,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B66,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D66" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B66,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B66,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E66" s="8" t="n"/>
@@ -1883,11 +1882,11 @@
       <c r="A67" s="5" t="n"/>
       <c r="B67" s="5" t="n"/>
       <c r="C67" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B67,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B67,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D67" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B67,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B67,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E67" s="8" t="n"/>
@@ -1902,11 +1901,11 @@
       <c r="A68" s="5" t="n"/>
       <c r="B68" s="5" t="n"/>
       <c r="C68" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B68,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B68,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D68" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B68,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B68,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -1921,11 +1920,11 @@
       <c r="A69" s="5" t="n"/>
       <c r="B69" s="5" t="n"/>
       <c r="C69" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B69,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B69,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D69" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B69,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B69,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -1940,11 +1939,11 @@
       <c r="A70" s="5" t="n"/>
       <c r="B70" s="5" t="n"/>
       <c r="C70" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B70,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B70,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D70" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B70,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B70,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -1959,11 +1958,11 @@
       <c r="A71" s="5" t="n"/>
       <c r="B71" s="5" t="n"/>
       <c r="C71" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B71,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B71,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D71" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B71,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B71,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E71" s="8" t="n"/>
@@ -1978,11 +1977,11 @@
       <c r="A72" s="5" t="n"/>
       <c r="B72" s="5" t="n"/>
       <c r="C72" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B72,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B72,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D72" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B72,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B72,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -1997,11 +1996,11 @@
       <c r="A73" s="5" t="n"/>
       <c r="B73" s="5" t="n"/>
       <c r="C73" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B73,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B73,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D73" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B73,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B73,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E73" s="8" t="n"/>
@@ -2016,11 +2015,11 @@
       <c r="A74" s="5" t="n"/>
       <c r="B74" s="5" t="n"/>
       <c r="C74" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B74,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B74,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D74" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B74,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B74,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -2035,11 +2034,11 @@
       <c r="A75" s="5" t="n"/>
       <c r="B75" s="5" t="n"/>
       <c r="C75" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B75,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B75,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D75" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B75,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B75,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -2054,11 +2053,11 @@
       <c r="A76" s="5" t="n"/>
       <c r="B76" s="5" t="n"/>
       <c r="C76" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B76,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B76,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D76" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B76,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B76,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E76" s="8" t="n"/>
@@ -2073,11 +2072,11 @@
       <c r="A77" s="5" t="n"/>
       <c r="B77" s="5" t="n"/>
       <c r="C77" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B77,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B77,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D77" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B77,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B77,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -2092,11 +2091,11 @@
       <c r="A78" s="5" t="n"/>
       <c r="B78" s="5" t="n"/>
       <c r="C78" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B78,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B78,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D78" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B78,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B78,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E78" s="8" t="n"/>
@@ -2111,11 +2110,11 @@
       <c r="A79" s="5" t="n"/>
       <c r="B79" s="5" t="n"/>
       <c r="C79" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B79,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B79,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D79" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B79,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B79,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E79" s="8" t="n"/>
@@ -2130,11 +2129,11 @@
       <c r="A80" s="5" t="n"/>
       <c r="B80" s="5" t="n"/>
       <c r="C80" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B80,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B80,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D80" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B80,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B80,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E80" s="8" t="n"/>
@@ -2149,11 +2148,11 @@
       <c r="A81" s="5" t="n"/>
       <c r="B81" s="5" t="n"/>
       <c r="C81" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B81,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B81,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D81" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B81,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B81,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E81" s="8" t="n"/>
@@ -2168,11 +2167,11 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="5" t="n"/>
       <c r="C82" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B82,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B82,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D82" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B82,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B82,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -2187,11 +2186,11 @@
       <c r="A83" s="5" t="n"/>
       <c r="B83" s="5" t="n"/>
       <c r="C83" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B83,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B83,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D83" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B83,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B83,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -2206,11 +2205,11 @@
       <c r="A84" s="5" t="n"/>
       <c r="B84" s="5" t="n"/>
       <c r="C84" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B84,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B84,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D84" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B84,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B84,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -2225,11 +2224,11 @@
       <c r="A85" s="5" t="n"/>
       <c r="B85" s="5" t="n"/>
       <c r="C85" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B85,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B85,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D85" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B85,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B85,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -2244,11 +2243,11 @@
       <c r="A86" s="5" t="n"/>
       <c r="B86" s="5" t="n"/>
       <c r="C86" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B86,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B86,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D86" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B86,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B86,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -2263,11 +2262,11 @@
       <c r="A87" s="5" t="n"/>
       <c r="B87" s="5" t="n"/>
       <c r="C87" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B87,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B87,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D87" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B87,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B87,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -2282,11 +2281,11 @@
       <c r="A88" s="5" t="n"/>
       <c r="B88" s="5" t="n"/>
       <c r="C88" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B88,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B88,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D88" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B88,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B88,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E88" s="8" t="n"/>
@@ -2301,11 +2300,11 @@
       <c r="A89" s="5" t="n"/>
       <c r="B89" s="5" t="n"/>
       <c r="C89" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B89,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B89,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D89" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B89,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B89,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E89" s="8" t="n"/>
@@ -2320,11 +2319,11 @@
       <c r="A90" s="5" t="n"/>
       <c r="B90" s="5" t="n"/>
       <c r="C90" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B90,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B90,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D90" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B90,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B90,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E90" s="8" t="n"/>
@@ -2339,11 +2338,11 @@
       <c r="A91" s="5" t="n"/>
       <c r="B91" s="5" t="n"/>
       <c r="C91" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B91,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B91,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D91" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B91,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B91,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E91" s="8" t="n"/>
@@ -2358,11 +2357,11 @@
       <c r="A92" s="5" t="n"/>
       <c r="B92" s="5" t="n"/>
       <c r="C92" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B92,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B92,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D92" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B92,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B92,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -2377,11 +2376,11 @@
       <c r="A93" s="5" t="n"/>
       <c r="B93" s="5" t="n"/>
       <c r="C93" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B93,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B93,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D93" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B93,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B93,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -2396,11 +2395,11 @@
       <c r="A94" s="5" t="n"/>
       <c r="B94" s="5" t="n"/>
       <c r="C94" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B94,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B94,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D94" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B94,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B94,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -2415,11 +2414,11 @@
       <c r="A95" s="5" t="n"/>
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B95,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B95,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D95" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B95,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B95,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -2434,11 +2433,11 @@
       <c r="A96" s="5" t="n"/>
       <c r="B96" s="5" t="n"/>
       <c r="C96" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B96,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B96,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D96" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B96,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B96,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -2453,11 +2452,11 @@
       <c r="A97" s="5" t="n"/>
       <c r="B97" s="5" t="n"/>
       <c r="C97" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B97,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B97,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D97" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B97,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B97,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -2472,11 +2471,11 @@
       <c r="A98" s="5" t="n"/>
       <c r="B98" s="5" t="n"/>
       <c r="C98" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B98,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B98,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D98" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B98,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B98,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E98" s="8" t="n"/>
@@ -2491,11 +2490,11 @@
       <c r="A99" s="5" t="n"/>
       <c r="B99" s="5" t="n"/>
       <c r="C99" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B99,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B99,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D99" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B99,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B99,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E99" s="8" t="n"/>
@@ -2510,11 +2509,11 @@
       <c r="A100" s="5" t="n"/>
       <c r="B100" s="5" t="n"/>
       <c r="C100" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B100,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B100,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D100" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B100,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B100,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E100" s="8" t="n"/>
@@ -2529,11 +2528,11 @@
       <c r="A101" s="5" t="n"/>
       <c r="B101" s="5" t="n"/>
       <c r="C101" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B101,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B101,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D101" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B101,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B101,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -2548,11 +2547,11 @@
       <c r="A102" s="5" t="n"/>
       <c r="B102" s="5" t="n"/>
       <c r="C102" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B102,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B102,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D102" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B102,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B102,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -2567,11 +2566,11 @@
       <c r="A103" s="5" t="n"/>
       <c r="B103" s="5" t="n"/>
       <c r="C103" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B103,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B103,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D103" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B103,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B103,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E103" s="8" t="n"/>
@@ -2586,11 +2585,11 @@
       <c r="A104" s="5" t="n"/>
       <c r="B104" s="5" t="n"/>
       <c r="C104" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B104,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B104,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D104" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B104,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B104,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E104" s="8" t="n"/>
@@ -2605,11 +2604,11 @@
       <c r="A105" s="5" t="n"/>
       <c r="B105" s="5" t="n"/>
       <c r="C105" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B105,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B105,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D105" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B105,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B105,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E105" s="8" t="n"/>
@@ -2624,11 +2623,11 @@
       <c r="A106" s="5" t="n"/>
       <c r="B106" s="5" t="n"/>
       <c r="C106" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B106,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B106,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D106" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B106,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B106,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E106" s="8" t="n"/>
@@ -2643,11 +2642,11 @@
       <c r="A107" s="5" t="n"/>
       <c r="B107" s="5" t="n"/>
       <c r="C107" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B107,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B107,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D107" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B107,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B107,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E107" s="8" t="n"/>
@@ -2662,11 +2661,11 @@
       <c r="A108" s="5" t="n"/>
       <c r="B108" s="5" t="n"/>
       <c r="C108" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B108,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B108,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D108" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B108,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B108,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E108" s="8" t="n"/>
@@ -2681,11 +2680,11 @@
       <c r="A109" s="5" t="n"/>
       <c r="B109" s="5" t="n"/>
       <c r="C109" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B109,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B109,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D109" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B109,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B109,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E109" s="8" t="n"/>
@@ -2700,11 +2699,11 @@
       <c r="A110" s="5" t="n"/>
       <c r="B110" s="5" t="n"/>
       <c r="C110" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B110,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B110,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D110" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B110,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B110,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E110" s="8" t="n"/>
@@ -2719,11 +2718,11 @@
       <c r="A111" s="5" t="n"/>
       <c r="B111" s="5" t="n"/>
       <c r="C111" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B111,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B111,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D111" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B111,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B111,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E111" s="8" t="n"/>
@@ -2738,11 +2737,11 @@
       <c r="A112" s="5" t="n"/>
       <c r="B112" s="5" t="n"/>
       <c r="C112" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B112,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B112,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D112" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B112,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B112,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E112" s="8" t="n"/>
@@ -2757,11 +2756,11 @@
       <c r="A113" s="5" t="n"/>
       <c r="B113" s="5" t="n"/>
       <c r="C113" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B113,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B113,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D113" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B113,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B113,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E113" s="8" t="n"/>
@@ -2776,11 +2775,11 @@
       <c r="A114" s="5" t="n"/>
       <c r="B114" s="5" t="n"/>
       <c r="C114" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B114,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B114,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D114" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B114,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B114,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E114" s="8" t="n"/>
@@ -2795,11 +2794,11 @@
       <c r="A115" s="5" t="n"/>
       <c r="B115" s="5" t="n"/>
       <c r="C115" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B115,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B115,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D115" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B115,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B115,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E115" s="8" t="n"/>
@@ -2814,11 +2813,11 @@
       <c r="A116" s="5" t="n"/>
       <c r="B116" s="5" t="n"/>
       <c r="C116" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B116,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B116,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D116" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B116,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B116,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E116" s="8" t="n"/>
@@ -2833,11 +2832,11 @@
       <c r="A117" s="5" t="n"/>
       <c r="B117" s="5" t="n"/>
       <c r="C117" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B117,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B117,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D117" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B117,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B117,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E117" s="8" t="n"/>
@@ -2852,11 +2851,11 @@
       <c r="A118" s="5" t="n"/>
       <c r="B118" s="5" t="n"/>
       <c r="C118" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B118,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B118,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D118" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B118,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B118,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E118" s="8" t="n"/>
@@ -2871,11 +2870,11 @@
       <c r="A119" s="5" t="n"/>
       <c r="B119" s="5" t="n"/>
       <c r="C119" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B119,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B119,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D119" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B119,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B119,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E119" s="8" t="n"/>
@@ -2890,11 +2889,11 @@
       <c r="A120" s="5" t="n"/>
       <c r="B120" s="5" t="n"/>
       <c r="C120" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B120,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B120,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D120" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B120,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B120,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E120" s="8" t="n"/>
@@ -2909,11 +2908,11 @@
       <c r="A121" s="5" t="n"/>
       <c r="B121" s="5" t="n"/>
       <c r="C121" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B121,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B121,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D121" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B121,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B121,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E121" s="8" t="n"/>
@@ -2928,11 +2927,11 @@
       <c r="A122" s="5" t="n"/>
       <c r="B122" s="5" t="n"/>
       <c r="C122" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B122,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B122,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D122" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B122,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B122,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E122" s="8" t="n"/>
@@ -2947,11 +2946,11 @@
       <c r="A123" s="5" t="n"/>
       <c r="B123" s="5" t="n"/>
       <c r="C123" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B123,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B123,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D123" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B123,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B123,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E123" s="8" t="n"/>
@@ -2966,11 +2965,11 @@
       <c r="A124" s="5" t="n"/>
       <c r="B124" s="5" t="n"/>
       <c r="C124" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B124,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B124,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D124" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B124,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B124,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E124" s="8" t="n"/>
@@ -2985,11 +2984,11 @@
       <c r="A125" s="5" t="n"/>
       <c r="B125" s="5" t="n"/>
       <c r="C125" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B125,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B125,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D125" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B125,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B125,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E125" s="8" t="n"/>
@@ -3004,11 +3003,11 @@
       <c r="A126" s="5" t="n"/>
       <c r="B126" s="5" t="n"/>
       <c r="C126" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B126,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B126,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D126" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B126,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B126,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E126" s="8" t="n"/>
@@ -3023,11 +3022,11 @@
       <c r="A127" s="5" t="n"/>
       <c r="B127" s="5" t="n"/>
       <c r="C127" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B127,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B127,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D127" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B127,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B127,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E127" s="8" t="n"/>
@@ -3042,11 +3041,11 @@
       <c r="A128" s="5" t="n"/>
       <c r="B128" s="5" t="n"/>
       <c r="C128" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B128,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B128,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D128" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B128,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B128,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E128" s="8" t="n"/>
@@ -3061,11 +3060,11 @@
       <c r="A129" s="5" t="n"/>
       <c r="B129" s="5" t="n"/>
       <c r="C129" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B129,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B129,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D129" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B129,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B129,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E129" s="8" t="n"/>
@@ -3080,11 +3079,11 @@
       <c r="A130" s="5" t="n"/>
       <c r="B130" s="5" t="n"/>
       <c r="C130" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B130,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B130,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D130" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B130,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B130,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E130" s="8" t="n"/>
@@ -3099,11 +3098,11 @@
       <c r="A131" s="5" t="n"/>
       <c r="B131" s="5" t="n"/>
       <c r="C131" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B131,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B131,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D131" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B131,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B131,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E131" s="8" t="n"/>
@@ -3118,11 +3117,11 @@
       <c r="A132" s="5" t="n"/>
       <c r="B132" s="5" t="n"/>
       <c r="C132" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B132,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B132,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D132" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B132,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B132,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E132" s="8" t="n"/>
@@ -3137,11 +3136,11 @@
       <c r="A133" s="5" t="n"/>
       <c r="B133" s="5" t="n"/>
       <c r="C133" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B133,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B133,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D133" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B133,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B133,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E133" s="8" t="n"/>
@@ -3156,11 +3155,11 @@
       <c r="A134" s="5" t="n"/>
       <c r="B134" s="5" t="n"/>
       <c r="C134" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B134,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B134,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D134" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B134,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B134,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E134" s="8" t="n"/>
@@ -3175,11 +3174,11 @@
       <c r="A135" s="5" t="n"/>
       <c r="B135" s="5" t="n"/>
       <c r="C135" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B135,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B135,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D135" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B135,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B135,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E135" s="8" t="n"/>
@@ -3194,11 +3193,11 @@
       <c r="A136" s="5" t="n"/>
       <c r="B136" s="5" t="n"/>
       <c r="C136" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B136,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B136,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D136" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B136,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B136,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E136" s="8" t="n"/>
@@ -3213,11 +3212,11 @@
       <c r="A137" s="5" t="n"/>
       <c r="B137" s="5" t="n"/>
       <c r="C137" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B137,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B137,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D137" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B137,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B137,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E137" s="8" t="n"/>
@@ -3232,11 +3231,11 @@
       <c r="A138" s="5" t="n"/>
       <c r="B138" s="5" t="n"/>
       <c r="C138" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B138,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B138,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D138" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B138,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B138,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E138" s="8" t="n"/>
@@ -3251,11 +3250,11 @@
       <c r="A139" s="5" t="n"/>
       <c r="B139" s="5" t="n"/>
       <c r="C139" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B139,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B139,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D139" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B139,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B139,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E139" s="8" t="n"/>
@@ -3270,11 +3269,11 @@
       <c r="A140" s="5" t="n"/>
       <c r="B140" s="5" t="n"/>
       <c r="C140" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B140,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B140,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D140" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B140,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B140,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E140" s="8" t="n"/>
@@ -3289,11 +3288,11 @@
       <c r="A141" s="5" t="n"/>
       <c r="B141" s="5" t="n"/>
       <c r="C141" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B141,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B141,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D141" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B141,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B141,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E141" s="8" t="n"/>
@@ -3308,11 +3307,11 @@
       <c r="A142" s="5" t="n"/>
       <c r="B142" s="5" t="n"/>
       <c r="C142" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B142,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B142,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D142" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B142,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B142,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E142" s="8" t="n"/>
@@ -3327,11 +3326,11 @@
       <c r="A143" s="5" t="n"/>
       <c r="B143" s="5" t="n"/>
       <c r="C143" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B143,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B143,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D143" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B143,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B143,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E143" s="8" t="n"/>
@@ -3346,11 +3345,11 @@
       <c r="A144" s="5" t="n"/>
       <c r="B144" s="5" t="n"/>
       <c r="C144" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B144,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B144,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D144" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B144,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B144,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E144" s="8" t="n"/>
@@ -3365,11 +3364,11 @@
       <c r="A145" s="5" t="n"/>
       <c r="B145" s="5" t="n"/>
       <c r="C145" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B145,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B145,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D145" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B145,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B145,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E145" s="8" t="n"/>
@@ -3384,11 +3383,11 @@
       <c r="A146" s="5" t="n"/>
       <c r="B146" s="5" t="n"/>
       <c r="C146" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B146,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B146,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D146" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B146,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B146,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E146" s="8" t="n"/>
@@ -3403,11 +3402,11 @@
       <c r="A147" s="5" t="n"/>
       <c r="B147" s="5" t="n"/>
       <c r="C147" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B147,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B147,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D147" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B147,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B147,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E147" s="8" t="n"/>
@@ -3422,11 +3421,11 @@
       <c r="A148" s="5" t="n"/>
       <c r="B148" s="5" t="n"/>
       <c r="C148" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B148,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B148,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D148" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B148,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B148,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E148" s="8" t="n"/>
@@ -3441,11 +3440,11 @@
       <c r="A149" s="5" t="n"/>
       <c r="B149" s="5" t="n"/>
       <c r="C149" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B149,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B149,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D149" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B149,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B149,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E149" s="8" t="n"/>
@@ -3460,11 +3459,11 @@
       <c r="A150" s="5" t="n"/>
       <c r="B150" s="5" t="n"/>
       <c r="C150" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B150,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B150,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D150" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B150,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B150,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E150" s="8" t="n"/>
@@ -3479,11 +3478,11 @@
       <c r="A151" s="5" t="n"/>
       <c r="B151" s="5" t="n"/>
       <c r="C151" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B151,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B151,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D151" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B151,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B151,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E151" s="8" t="n"/>
@@ -3498,11 +3497,11 @@
       <c r="A152" s="5" t="n"/>
       <c r="B152" s="5" t="n"/>
       <c r="C152" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B152,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B152,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D152" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B152,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B152,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E152" s="8" t="n"/>
@@ -3517,11 +3516,11 @@
       <c r="A153" s="5" t="n"/>
       <c r="B153" s="5" t="n"/>
       <c r="C153" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B153,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B153,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D153" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B153,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B153,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E153" s="8" t="n"/>
@@ -3536,11 +3535,11 @@
       <c r="A154" s="5" t="n"/>
       <c r="B154" s="5" t="n"/>
       <c r="C154" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B154,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B154,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D154" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B154,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B154,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E154" s="8" t="n"/>
@@ -3555,11 +3554,11 @@
       <c r="A155" s="5" t="n"/>
       <c r="B155" s="5" t="n"/>
       <c r="C155" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B155,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B155,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D155" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B155,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B155,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E155" s="8" t="n"/>
@@ -3574,11 +3573,11 @@
       <c r="A156" s="5" t="n"/>
       <c r="B156" s="5" t="n"/>
       <c r="C156" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B156,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B156,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D156" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B156,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B156,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E156" s="8" t="n"/>
@@ -3593,11 +3592,11 @@
       <c r="A157" s="5" t="n"/>
       <c r="B157" s="5" t="n"/>
       <c r="C157" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B157,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B157,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D157" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B157,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B157,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E157" s="8" t="n"/>
@@ -3612,11 +3611,11 @@
       <c r="A158" s="5" t="n"/>
       <c r="B158" s="5" t="n"/>
       <c r="C158" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B158,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B158,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D158" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B158,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B158,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E158" s="8" t="n"/>
@@ -3631,11 +3630,11 @@
       <c r="A159" s="5" t="n"/>
       <c r="B159" s="5" t="n"/>
       <c r="C159" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B159,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B159,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D159" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B159,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B159,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E159" s="8" t="n"/>
@@ -3650,11 +3649,11 @@
       <c r="A160" s="5" t="n"/>
       <c r="B160" s="5" t="n"/>
       <c r="C160" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B160,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B160,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D160" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B160,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B160,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E160" s="8" t="n"/>
@@ -3669,11 +3668,11 @@
       <c r="A161" s="5" t="n"/>
       <c r="B161" s="5" t="n"/>
       <c r="C161" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B161,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B161,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D161" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B161,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B161,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E161" s="8" t="n"/>
@@ -3688,11 +3687,11 @@
       <c r="A162" s="5" t="n"/>
       <c r="B162" s="5" t="n"/>
       <c r="C162" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B162,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B162,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D162" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B162,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B162,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E162" s="8" t="n"/>
@@ -3707,11 +3706,11 @@
       <c r="A163" s="5" t="n"/>
       <c r="B163" s="5" t="n"/>
       <c r="C163" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B163,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B163,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D163" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B163,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B163,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E163" s="8" t="n"/>
@@ -3726,11 +3725,11 @@
       <c r="A164" s="5" t="n"/>
       <c r="B164" s="5" t="n"/>
       <c r="C164" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B164,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B164,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D164" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B164,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B164,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E164" s="8" t="n"/>
@@ -3745,11 +3744,11 @@
       <c r="A165" s="5" t="n"/>
       <c r="B165" s="5" t="n"/>
       <c r="C165" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B165,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B165,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D165" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B165,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B165,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E165" s="8" t="n"/>
@@ -3764,11 +3763,11 @@
       <c r="A166" s="5" t="n"/>
       <c r="B166" s="5" t="n"/>
       <c r="C166" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B166,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B166,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D166" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B166,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B166,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E166" s="8" t="n"/>
@@ -3783,11 +3782,11 @@
       <c r="A167" s="5" t="n"/>
       <c r="B167" s="5" t="n"/>
       <c r="C167" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B167,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B167,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D167" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B167,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B167,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E167" s="8" t="n"/>
@@ -3802,11 +3801,11 @@
       <c r="A168" s="5" t="n"/>
       <c r="B168" s="5" t="n"/>
       <c r="C168" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B168,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B168,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D168" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B168,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B168,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E168" s="8" t="n"/>
@@ -3821,11 +3820,11 @@
       <c r="A169" s="5" t="n"/>
       <c r="B169" s="5" t="n"/>
       <c r="C169" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B169,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B169,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D169" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B169,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B169,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E169" s="8" t="n"/>
@@ -3840,11 +3839,11 @@
       <c r="A170" s="5" t="n"/>
       <c r="B170" s="5" t="n"/>
       <c r="C170" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B170,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B170,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D170" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B170,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B170,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E170" s="8" t="n"/>
@@ -3859,11 +3858,11 @@
       <c r="A171" s="5" t="n"/>
       <c r="B171" s="5" t="n"/>
       <c r="C171" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B171,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B171,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D171" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B171,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B171,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E171" s="8" t="n"/>
@@ -3878,11 +3877,11 @@
       <c r="A172" s="5" t="n"/>
       <c r="B172" s="5" t="n"/>
       <c r="C172" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B172,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B172,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D172" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B172,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B172,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E172" s="8" t="n"/>
@@ -3897,11 +3896,11 @@
       <c r="A173" s="5" t="n"/>
       <c r="B173" s="5" t="n"/>
       <c r="C173" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B173,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B173,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D173" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B173,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B173,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E173" s="8" t="n"/>
@@ -3916,11 +3915,11 @@
       <c r="A174" s="5" t="n"/>
       <c r="B174" s="5" t="n"/>
       <c r="C174" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B174,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B174,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D174" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B174,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B174,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E174" s="8" t="n"/>
@@ -3935,11 +3934,11 @@
       <c r="A175" s="5" t="n"/>
       <c r="B175" s="5" t="n"/>
       <c r="C175" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B175,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B175,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D175" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B175,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B175,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E175" s="8" t="n"/>
@@ -3954,11 +3953,11 @@
       <c r="A176" s="5" t="n"/>
       <c r="B176" s="5" t="n"/>
       <c r="C176" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B176,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B176,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D176" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B176,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B176,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E176" s="8" t="n"/>
@@ -3973,11 +3972,11 @@
       <c r="A177" s="5" t="n"/>
       <c r="B177" s="5" t="n"/>
       <c r="C177" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B177,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B177,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D177" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B177,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B177,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E177" s="8" t="n"/>
@@ -3992,11 +3991,11 @@
       <c r="A178" s="5" t="n"/>
       <c r="B178" s="5" t="n"/>
       <c r="C178" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B178,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B178,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D178" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B178,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B178,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E178" s="8" t="n"/>
@@ -4011,11 +4010,11 @@
       <c r="A179" s="5" t="n"/>
       <c r="B179" s="5" t="n"/>
       <c r="C179" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B179,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B179,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D179" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B179,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B179,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E179" s="8" t="n"/>
@@ -4030,11 +4029,11 @@
       <c r="A180" s="5" t="n"/>
       <c r="B180" s="5" t="n"/>
       <c r="C180" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B180,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B180,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D180" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B180,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B180,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E180" s="8" t="n"/>
@@ -4049,11 +4048,11 @@
       <c r="A181" s="5" t="n"/>
       <c r="B181" s="5" t="n"/>
       <c r="C181" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B181,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B181,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D181" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B181,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B181,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E181" s="8" t="n"/>
@@ -4068,11 +4067,11 @@
       <c r="A182" s="5" t="n"/>
       <c r="B182" s="5" t="n"/>
       <c r="C182" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B182,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B182,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D182" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B182,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B182,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E182" s="8" t="n"/>
@@ -4087,11 +4086,11 @@
       <c r="A183" s="5" t="n"/>
       <c r="B183" s="5" t="n"/>
       <c r="C183" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B183,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B183,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D183" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B183,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B183,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E183" s="8" t="n"/>
@@ -4106,11 +4105,11 @@
       <c r="A184" s="5" t="n"/>
       <c r="B184" s="5" t="n"/>
       <c r="C184" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B184,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B184,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D184" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B184,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B184,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E184" s="8" t="n"/>
@@ -4125,11 +4124,11 @@
       <c r="A185" s="5" t="n"/>
       <c r="B185" s="5" t="n"/>
       <c r="C185" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B185,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B185,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D185" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B185,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B185,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E185" s="8" t="n"/>
@@ -4144,11 +4143,11 @@
       <c r="A186" s="5" t="n"/>
       <c r="B186" s="5" t="n"/>
       <c r="C186" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B186,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B186,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D186" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B186,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B186,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E186" s="8" t="n"/>
@@ -4163,11 +4162,11 @@
       <c r="A187" s="5" t="n"/>
       <c r="B187" s="5" t="n"/>
       <c r="C187" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B187,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B187,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D187" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B187,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B187,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E187" s="8" t="n"/>
@@ -4182,11 +4181,11 @@
       <c r="A188" s="5" t="n"/>
       <c r="B188" s="5" t="n"/>
       <c r="C188" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B188,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B188,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D188" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B188,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B188,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E188" s="8" t="n"/>
@@ -4201,11 +4200,11 @@
       <c r="A189" s="5" t="n"/>
       <c r="B189" s="5" t="n"/>
       <c r="C189" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B189,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B189,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D189" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B189,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B189,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E189" s="8" t="n"/>
@@ -4220,11 +4219,11 @@
       <c r="A190" s="5" t="n"/>
       <c r="B190" s="5" t="n"/>
       <c r="C190" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B190,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B190,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D190" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B190,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B190,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E190" s="8" t="n"/>
@@ -4239,11 +4238,11 @@
       <c r="A191" s="5" t="n"/>
       <c r="B191" s="5" t="n"/>
       <c r="C191" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B191,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B191,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D191" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B191,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B191,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E191" s="8" t="n"/>
@@ -4258,11 +4257,11 @@
       <c r="A192" s="5" t="n"/>
       <c r="B192" s="5" t="n"/>
       <c r="C192" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B192,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B192,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D192" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B192,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B192,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E192" s="8" t="n"/>
@@ -4277,11 +4276,11 @@
       <c r="A193" s="5" t="n"/>
       <c r="B193" s="5" t="n"/>
       <c r="C193" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B193,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B193,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D193" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B193,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B193,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E193" s="8" t="n"/>
@@ -4296,11 +4295,11 @@
       <c r="A194" s="5" t="n"/>
       <c r="B194" s="5" t="n"/>
       <c r="C194" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B194,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B194,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D194" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B194,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B194,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E194" s="8" t="n"/>
@@ -4315,11 +4314,11 @@
       <c r="A195" s="5" t="n"/>
       <c r="B195" s="5" t="n"/>
       <c r="C195" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B195,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B195,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D195" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B195,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B195,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E195" s="8" t="n"/>
@@ -4334,11 +4333,11 @@
       <c r="A196" s="5" t="n"/>
       <c r="B196" s="5" t="n"/>
       <c r="C196" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B196,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B196,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D196" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B196,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B196,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E196" s="8" t="n"/>
@@ -4353,11 +4352,11 @@
       <c r="A197" s="5" t="n"/>
       <c r="B197" s="5" t="n"/>
       <c r="C197" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B197,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B197,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D197" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B197,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B197,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E197" s="8" t="n"/>
@@ -4372,11 +4371,11 @@
       <c r="A198" s="5" t="n"/>
       <c r="B198" s="5" t="n"/>
       <c r="C198" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B198,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B198,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D198" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B198,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B198,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E198" s="8" t="n"/>
@@ -4391,11 +4390,11 @@
       <c r="A199" s="5" t="n"/>
       <c r="B199" s="5" t="n"/>
       <c r="C199" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B199,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B199,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D199" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B199,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B199,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E199" s="8" t="n"/>
@@ -4410,11 +4409,11 @@
       <c r="A200" s="5" t="n"/>
       <c r="B200" s="5" t="n"/>
       <c r="C200" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B200,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B200,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D200" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B200,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B200,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E200" s="8" t="n"/>
@@ -4429,11 +4428,11 @@
       <c r="A201" s="5" t="n"/>
       <c r="B201" s="5" t="n"/>
       <c r="C201" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B201,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B201,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D201" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B201,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B201,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E201" s="8" t="n"/>
@@ -4448,11 +4447,11 @@
       <c r="A202" s="5" t="n"/>
       <c r="B202" s="5" t="n"/>
       <c r="C202" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B202,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B202,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D202" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B202,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B202,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E202" s="8" t="n"/>
@@ -4467,11 +4466,11 @@
       <c r="A203" s="5" t="n"/>
       <c r="B203" s="5" t="n"/>
       <c r="C203" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B203,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B203,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D203" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B203,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B203,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E203" s="8" t="n"/>
@@ -4486,11 +4485,11 @@
       <c r="A204" s="5" t="n"/>
       <c r="B204" s="5" t="n"/>
       <c r="C204" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B204,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B204,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D204" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B204,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B204,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E204" s="8" t="n"/>
@@ -4505,11 +4504,11 @@
       <c r="A205" s="5" t="n"/>
       <c r="B205" s="5" t="n"/>
       <c r="C205" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B205,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B205,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D205" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B205,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B205,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E205" s="8" t="n"/>
@@ -4524,11 +4523,11 @@
       <c r="A206" s="5" t="n"/>
       <c r="B206" s="5" t="n"/>
       <c r="C206" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B206,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B206,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D206" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B206,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B206,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E206" s="8" t="n"/>
@@ -4543,11 +4542,11 @@
       <c r="A207" s="5" t="n"/>
       <c r="B207" s="5" t="n"/>
       <c r="C207" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B207,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B207,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D207" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B207,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B207,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E207" s="8" t="n"/>
@@ -4562,11 +4561,11 @@
       <c r="A208" s="5" t="n"/>
       <c r="B208" s="5" t="n"/>
       <c r="C208" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B208,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B208,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D208" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B208,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B208,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E208" s="8" t="n"/>
@@ -4581,11 +4580,11 @@
       <c r="A209" s="5" t="n"/>
       <c r="B209" s="5" t="n"/>
       <c r="C209" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B209,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B209,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D209" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B209,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B209,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E209" s="8" t="n"/>
@@ -4600,11 +4599,11 @@
       <c r="A210" s="5" t="n"/>
       <c r="B210" s="5" t="n"/>
       <c r="C210" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B210,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B210,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D210" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B210,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B210,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E210" s="8" t="n"/>
@@ -4619,11 +4618,11 @@
       <c r="A211" s="5" t="n"/>
       <c r="B211" s="5" t="n"/>
       <c r="C211" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B211,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B211,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D211" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B211,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B211,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E211" s="8" t="n"/>
@@ -4638,11 +4637,11 @@
       <c r="A212" s="5" t="n"/>
       <c r="B212" s="5" t="n"/>
       <c r="C212" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B212,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B212,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D212" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B212,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B212,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E212" s="8" t="n"/>
@@ -4657,11 +4656,11 @@
       <c r="A213" s="5" t="n"/>
       <c r="B213" s="5" t="n"/>
       <c r="C213" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B213,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B213,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D213" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B213,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B213,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E213" s="8" t="n"/>
@@ -4676,11 +4675,11 @@
       <c r="A214" s="5" t="n"/>
       <c r="B214" s="5" t="n"/>
       <c r="C214" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B214,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B214,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D214" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B214,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B214,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E214" s="8" t="n"/>
@@ -4695,11 +4694,11 @@
       <c r="A215" s="5" t="n"/>
       <c r="B215" s="5" t="n"/>
       <c r="C215" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B215,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B215,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D215" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B215,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B215,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E215" s="8" t="n"/>
@@ -4714,11 +4713,11 @@
       <c r="A216" s="5" t="n"/>
       <c r="B216" s="5" t="n"/>
       <c r="C216" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B216,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B216,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D216" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B216,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B216,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E216" s="8" t="n"/>
@@ -4733,11 +4732,11 @@
       <c r="A217" s="5" t="n"/>
       <c r="B217" s="5" t="n"/>
       <c r="C217" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B217,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B217,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D217" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B217,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B217,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E217" s="8" t="n"/>
@@ -4752,11 +4751,11 @@
       <c r="A218" s="5" t="n"/>
       <c r="B218" s="5" t="n"/>
       <c r="C218" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B218,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B218,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D218" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B218,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B218,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E218" s="8" t="n"/>
@@ -4771,11 +4770,11 @@
       <c r="A219" s="5" t="n"/>
       <c r="B219" s="5" t="n"/>
       <c r="C219" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B219,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B219,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D219" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B219,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B219,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E219" s="8" t="n"/>
@@ -4790,11 +4789,11 @@
       <c r="A220" s="5" t="n"/>
       <c r="B220" s="5" t="n"/>
       <c r="C220" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B220,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B220,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D220" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B220,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B220,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E220" s="8" t="n"/>
@@ -4809,11 +4808,11 @@
       <c r="A221" s="5" t="n"/>
       <c r="B221" s="5" t="n"/>
       <c r="C221" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B221,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B221,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D221" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B221,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B221,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E221" s="8" t="n"/>
@@ -4828,11 +4827,11 @@
       <c r="A222" s="5" t="n"/>
       <c r="B222" s="5" t="n"/>
       <c r="C222" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B222,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B222,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D222" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B222,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B222,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E222" s="8" t="n"/>
@@ -4847,11 +4846,11 @@
       <c r="A223" s="5" t="n"/>
       <c r="B223" s="5" t="n"/>
       <c r="C223" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B223,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B223,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D223" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B223,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B223,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E223" s="8" t="n"/>
@@ -4866,11 +4865,11 @@
       <c r="A224" s="5" t="n"/>
       <c r="B224" s="5" t="n"/>
       <c r="C224" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B224,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B224,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D224" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B224,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B224,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E224" s="8" t="n"/>
@@ -4885,11 +4884,11 @@
       <c r="A225" s="5" t="n"/>
       <c r="B225" s="5" t="n"/>
       <c r="C225" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B225,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B225,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D225" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B225,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B225,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E225" s="8" t="n"/>
@@ -4904,11 +4903,11 @@
       <c r="A226" s="5" t="n"/>
       <c r="B226" s="5" t="n"/>
       <c r="C226" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B226,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B226,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D226" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B226,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B226,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E226" s="8" t="n"/>
@@ -4923,11 +4922,11 @@
       <c r="A227" s="5" t="n"/>
       <c r="B227" s="5" t="n"/>
       <c r="C227" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B227,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B227,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D227" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B227,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B227,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E227" s="8" t="n"/>
@@ -4942,11 +4941,11 @@
       <c r="A228" s="5" t="n"/>
       <c r="B228" s="5" t="n"/>
       <c r="C228" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B228,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B228,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D228" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B228,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B228,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E228" s="8" t="n"/>
@@ -4961,11 +4960,11 @@
       <c r="A229" s="5" t="n"/>
       <c r="B229" s="5" t="n"/>
       <c r="C229" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B229,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B229,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D229" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B229,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B229,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E229" s="8" t="n"/>
@@ -4980,11 +4979,11 @@
       <c r="A230" s="5" t="n"/>
       <c r="B230" s="5" t="n"/>
       <c r="C230" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B230,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B230,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D230" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B230,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B230,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E230" s="8" t="n"/>
@@ -4999,11 +4998,11 @@
       <c r="A231" s="5" t="n"/>
       <c r="B231" s="5" t="n"/>
       <c r="C231" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B231,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B231,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D231" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B231,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B231,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E231" s="8" t="n"/>
@@ -5018,11 +5017,11 @@
       <c r="A232" s="5" t="n"/>
       <c r="B232" s="5" t="n"/>
       <c r="C232" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B232,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B232,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D232" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B232,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B232,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E232" s="8" t="n"/>
@@ -5037,11 +5036,11 @@
       <c r="A233" s="5" t="n"/>
       <c r="B233" s="5" t="n"/>
       <c r="C233" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B233,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B233,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D233" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B233,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B233,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E233" s="8" t="n"/>
@@ -5056,11 +5055,11 @@
       <c r="A234" s="5" t="n"/>
       <c r="B234" s="5" t="n"/>
       <c r="C234" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B234,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B234,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D234" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B234,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B234,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E234" s="8" t="n"/>
@@ -5075,11 +5074,11 @@
       <c r="A235" s="5" t="n"/>
       <c r="B235" s="5" t="n"/>
       <c r="C235" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B235,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B235,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D235" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B235,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B235,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E235" s="8" t="n"/>
@@ -5094,11 +5093,11 @@
       <c r="A236" s="5" t="n"/>
       <c r="B236" s="5" t="n"/>
       <c r="C236" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B236,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B236,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D236" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B236,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B236,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E236" s="8" t="n"/>
@@ -5113,11 +5112,11 @@
       <c r="A237" s="5" t="n"/>
       <c r="B237" s="5" t="n"/>
       <c r="C237" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B237,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B237,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D237" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B237,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B237,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E237" s="8" t="n"/>
@@ -5132,11 +5131,11 @@
       <c r="A238" s="5" t="n"/>
       <c r="B238" s="5" t="n"/>
       <c r="C238" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B238,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B238,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D238" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B238,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B238,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E238" s="8" t="n"/>
@@ -5151,11 +5150,11 @@
       <c r="A239" s="5" t="n"/>
       <c r="B239" s="5" t="n"/>
       <c r="C239" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B239,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B239,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D239" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B239,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B239,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E239" s="8" t="n"/>
@@ -5170,11 +5169,11 @@
       <c r="A240" s="5" t="n"/>
       <c r="B240" s="5" t="n"/>
       <c r="C240" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B240,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B240,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D240" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B240,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B240,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E240" s="8" t="n"/>
@@ -5189,11 +5188,11 @@
       <c r="A241" s="5" t="n"/>
       <c r="B241" s="5" t="n"/>
       <c r="C241" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B241,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B241,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D241" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B241,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B241,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E241" s="8" t="n"/>
@@ -5208,11 +5207,11 @@
       <c r="A242" s="5" t="n"/>
       <c r="B242" s="5" t="n"/>
       <c r="C242" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B242,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B242,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D242" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B242,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B242,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E242" s="8" t="n"/>
@@ -5227,11 +5226,11 @@
       <c r="A243" s="5" t="n"/>
       <c r="B243" s="5" t="n"/>
       <c r="C243" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B243,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B243,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D243" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B243,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B243,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E243" s="8" t="n"/>
@@ -5246,11 +5245,11 @@
       <c r="A244" s="5" t="n"/>
       <c r="B244" s="5" t="n"/>
       <c r="C244" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B244,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B244,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D244" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B244,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B244,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E244" s="8" t="n"/>
@@ -5265,11 +5264,11 @@
       <c r="A245" s="5" t="n"/>
       <c r="B245" s="5" t="n"/>
       <c r="C245" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B245,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B245,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D245" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B245,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B245,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E245" s="8" t="n"/>
@@ -5284,11 +5283,11 @@
       <c r="A246" s="5" t="n"/>
       <c r="B246" s="5" t="n"/>
       <c r="C246" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B246,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B246,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D246" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B246,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B246,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E246" s="8" t="n"/>
@@ -5303,11 +5302,11 @@
       <c r="A247" s="5" t="n"/>
       <c r="B247" s="5" t="n"/>
       <c r="C247" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B247,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B247,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D247" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B247,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B247,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E247" s="8" t="n"/>
@@ -5322,11 +5321,11 @@
       <c r="A248" s="5" t="n"/>
       <c r="B248" s="5" t="n"/>
       <c r="C248" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B248,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B248,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D248" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B248,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B248,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E248" s="8" t="n"/>
@@ -5341,11 +5340,11 @@
       <c r="A249" s="5" t="n"/>
       <c r="B249" s="5" t="n"/>
       <c r="C249" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B249,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B249,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D249" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B249,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B249,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E249" s="8" t="n"/>
@@ -5360,11 +5359,11 @@
       <c r="A250" s="5" t="n"/>
       <c r="B250" s="5" t="n"/>
       <c r="C250" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B250,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B250,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D250" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B250,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B250,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E250" s="8" t="n"/>
@@ -5379,11 +5378,11 @@
       <c r="A251" s="5" t="n"/>
       <c r="B251" s="5" t="n"/>
       <c r="C251" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B251,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B251,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D251" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B251,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B251,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E251" s="8" t="n"/>
@@ -5398,11 +5397,11 @@
       <c r="A252" s="5" t="n"/>
       <c r="B252" s="5" t="n"/>
       <c r="C252" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B252,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B252,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D252" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B252,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B252,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E252" s="8" t="n"/>
@@ -5417,11 +5416,11 @@
       <c r="A253" s="5" t="n"/>
       <c r="B253" s="5" t="n"/>
       <c r="C253" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B253,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B253,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D253" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B253,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B253,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E253" s="8" t="n"/>
@@ -5436,11 +5435,11 @@
       <c r="A254" s="5" t="n"/>
       <c r="B254" s="5" t="n"/>
       <c r="C254" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B254,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B254,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D254" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B254,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B254,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E254" s="8" t="n"/>
@@ -5455,11 +5454,11 @@
       <c r="A255" s="5" t="n"/>
       <c r="B255" s="5" t="n"/>
       <c r="C255" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B255,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B255,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D255" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B255,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B255,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E255" s="8" t="n"/>
@@ -5474,11 +5473,11 @@
       <c r="A256" s="5" t="n"/>
       <c r="B256" s="5" t="n"/>
       <c r="C256" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B256,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B256,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D256" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B256,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B256,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E256" s="8" t="n"/>
@@ -5493,11 +5492,11 @@
       <c r="A257" s="5" t="n"/>
       <c r="B257" s="5" t="n"/>
       <c r="C257" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B257,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B257,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D257" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B257,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B257,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E257" s="8" t="n"/>
@@ -5512,11 +5511,11 @@
       <c r="A258" s="5" t="n"/>
       <c r="B258" s="5" t="n"/>
       <c r="C258" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B258,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B258,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D258" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B258,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B258,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E258" s="8" t="n"/>
@@ -5531,11 +5530,11 @@
       <c r="A259" s="5" t="n"/>
       <c r="B259" s="5" t="n"/>
       <c r="C259" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B259,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B259,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D259" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B259,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B259,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E259" s="8" t="n"/>
@@ -5550,11 +5549,11 @@
       <c r="A260" s="5" t="n"/>
       <c r="B260" s="5" t="n"/>
       <c r="C260" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B260,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B260,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D260" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B260,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B260,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E260" s="8" t="n"/>
@@ -5569,11 +5568,11 @@
       <c r="A261" s="5" t="n"/>
       <c r="B261" s="5" t="n"/>
       <c r="C261" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B261,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B261,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D261" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B261,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B261,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E261" s="8" t="n"/>
@@ -5588,11 +5587,11 @@
       <c r="A262" s="5" t="n"/>
       <c r="B262" s="5" t="n"/>
       <c r="C262" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B262,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B262,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D262" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B262,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B262,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E262" s="8" t="n"/>
@@ -5607,11 +5606,11 @@
       <c r="A263" s="5" t="n"/>
       <c r="B263" s="5" t="n"/>
       <c r="C263" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B263,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B263,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D263" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B263,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B263,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E263" s="8" t="n"/>
@@ -5626,11 +5625,11 @@
       <c r="A264" s="5" t="n"/>
       <c r="B264" s="5" t="n"/>
       <c r="C264" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B264,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B264,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D264" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B264,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B264,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E264" s="8" t="n"/>
@@ -5645,11 +5644,11 @@
       <c r="A265" s="5" t="n"/>
       <c r="B265" s="5" t="n"/>
       <c r="C265" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B265,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B265,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D265" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B265,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B265,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E265" s="8" t="n"/>
@@ -5664,11 +5663,11 @@
       <c r="A266" s="5" t="n"/>
       <c r="B266" s="5" t="n"/>
       <c r="C266" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B266,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B266,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D266" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B266,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B266,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E266" s="8" t="n"/>
@@ -5683,11 +5682,11 @@
       <c r="A267" s="5" t="n"/>
       <c r="B267" s="5" t="n"/>
       <c r="C267" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B267,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B267,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D267" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B267,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B267,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E267" s="8" t="n"/>
@@ -5702,11 +5701,11 @@
       <c r="A268" s="5" t="n"/>
       <c r="B268" s="5" t="n"/>
       <c r="C268" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B268,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B268,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D268" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B268,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B268,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E268" s="8" t="n"/>
@@ -5721,11 +5720,11 @@
       <c r="A269" s="5" t="n"/>
       <c r="B269" s="5" t="n"/>
       <c r="C269" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B269,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B269,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D269" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B269,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B269,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E269" s="8" t="n"/>
@@ -5740,11 +5739,11 @@
       <c r="A270" s="5" t="n"/>
       <c r="B270" s="5" t="n"/>
       <c r="C270" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B270,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B270,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D270" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B270,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B270,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E270" s="8" t="n"/>
@@ -5759,11 +5758,11 @@
       <c r="A271" s="5" t="n"/>
       <c r="B271" s="5" t="n"/>
       <c r="C271" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B271,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B271,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D271" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B271,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B271,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E271" s="8" t="n"/>
@@ -5778,11 +5777,11 @@
       <c r="A272" s="5" t="n"/>
       <c r="B272" s="5" t="n"/>
       <c r="C272" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B272,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B272,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D272" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B272,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B272,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E272" s="8" t="n"/>
@@ -5797,11 +5796,11 @@
       <c r="A273" s="5" t="n"/>
       <c r="B273" s="5" t="n"/>
       <c r="C273" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B273,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B273,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D273" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B273,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B273,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E273" s="8" t="n"/>
@@ -5816,11 +5815,11 @@
       <c r="A274" s="5" t="n"/>
       <c r="B274" s="5" t="n"/>
       <c r="C274" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B274,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B274,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D274" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B274,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B274,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E274" s="8" t="n"/>
@@ -5835,11 +5834,11 @@
       <c r="A275" s="5" t="n"/>
       <c r="B275" s="5" t="n"/>
       <c r="C275" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B275,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B275,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D275" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B275,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B275,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E275" s="8" t="n"/>
@@ -5854,11 +5853,11 @@
       <c r="A276" s="5" t="n"/>
       <c r="B276" s="5" t="n"/>
       <c r="C276" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B276,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B276,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D276" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B276,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B276,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E276" s="8" t="n"/>
@@ -5873,11 +5872,11 @@
       <c r="A277" s="5" t="n"/>
       <c r="B277" s="5" t="n"/>
       <c r="C277" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B277,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B277,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D277" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B277,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B277,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E277" s="8" t="n"/>
@@ -5892,11 +5891,11 @@
       <c r="A278" s="5" t="n"/>
       <c r="B278" s="5" t="n"/>
       <c r="C278" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B278,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B278,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D278" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B278,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B278,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E278" s="8" t="n"/>
@@ -5911,11 +5910,11 @@
       <c r="A279" s="5" t="n"/>
       <c r="B279" s="5" t="n"/>
       <c r="C279" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B279,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B279,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D279" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B279,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B279,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E279" s="8" t="n"/>
@@ -5930,11 +5929,11 @@
       <c r="A280" s="5" t="n"/>
       <c r="B280" s="5" t="n"/>
       <c r="C280" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B280,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B280,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D280" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B280,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B280,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E280" s="8" t="n"/>
@@ -5949,11 +5948,11 @@
       <c r="A281" s="5" t="n"/>
       <c r="B281" s="5" t="n"/>
       <c r="C281" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B281,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B281,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D281" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B281,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B281,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E281" s="8" t="n"/>
@@ -5968,11 +5967,11 @@
       <c r="A282" s="5" t="n"/>
       <c r="B282" s="5" t="n"/>
       <c r="C282" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B282,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B282,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D282" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B282,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B282,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E282" s="8" t="n"/>
@@ -5987,11 +5986,11 @@
       <c r="A283" s="5" t="n"/>
       <c r="B283" s="5" t="n"/>
       <c r="C283" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B283,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B283,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D283" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B283,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B283,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E283" s="8" t="n"/>
@@ -6006,11 +6005,11 @@
       <c r="A284" s="5" t="n"/>
       <c r="B284" s="5" t="n"/>
       <c r="C284" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B284,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B284,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D284" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B284,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B284,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E284" s="8" t="n"/>
@@ -6025,11 +6024,11 @@
       <c r="A285" s="5" t="n"/>
       <c r="B285" s="5" t="n"/>
       <c r="C285" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B285,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B285,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D285" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B285,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B285,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E285" s="8" t="n"/>
@@ -6044,11 +6043,11 @@
       <c r="A286" s="5" t="n"/>
       <c r="B286" s="5" t="n"/>
       <c r="C286" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B286,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B286,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D286" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B286,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B286,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E286" s="8" t="n"/>
@@ -6063,11 +6062,11 @@
       <c r="A287" s="5" t="n"/>
       <c r="B287" s="5" t="n"/>
       <c r="C287" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B287,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B287,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D287" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B287,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B287,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E287" s="8" t="n"/>
@@ -6082,11 +6081,11 @@
       <c r="A288" s="5" t="n"/>
       <c r="B288" s="5" t="n"/>
       <c r="C288" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B288,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B288,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D288" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B288,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B288,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E288" s="8" t="n"/>
@@ -6101,11 +6100,11 @@
       <c r="A289" s="5" t="n"/>
       <c r="B289" s="5" t="n"/>
       <c r="C289" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B289,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B289,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D289" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B289,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B289,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E289" s="8" t="n"/>
@@ -6120,11 +6119,11 @@
       <c r="A290" s="5" t="n"/>
       <c r="B290" s="5" t="n"/>
       <c r="C290" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B290,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B290,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D290" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B290,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B290,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E290" s="8" t="n"/>
@@ -6139,11 +6138,11 @@
       <c r="A291" s="5" t="n"/>
       <c r="B291" s="5" t="n"/>
       <c r="C291" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B291,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B291,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D291" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B291,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B291,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E291" s="8" t="n"/>
@@ -6158,11 +6157,11 @@
       <c r="A292" s="5" t="n"/>
       <c r="B292" s="5" t="n"/>
       <c r="C292" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B292,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B292,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D292" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B292,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B292,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E292" s="8" t="n"/>
@@ -6177,11 +6176,11 @@
       <c r="A293" s="5" t="n"/>
       <c r="B293" s="5" t="n"/>
       <c r="C293" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B293,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B293,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D293" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B293,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B293,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E293" s="8" t="n"/>
@@ -6196,11 +6195,11 @@
       <c r="A294" s="5" t="n"/>
       <c r="B294" s="5" t="n"/>
       <c r="C294" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B294,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B294,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D294" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B294,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B294,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E294" s="8" t="n"/>
@@ -6215,11 +6214,11 @@
       <c r="A295" s="5" t="n"/>
       <c r="B295" s="5" t="n"/>
       <c r="C295" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B295,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B295,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D295" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B295,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B295,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E295" s="8" t="n"/>
@@ -6234,11 +6233,11 @@
       <c r="A296" s="5" t="n"/>
       <c r="B296" s="5" t="n"/>
       <c r="C296" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B296,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B296,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D296" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B296,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B296,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E296" s="8" t="n"/>
@@ -6253,11 +6252,11 @@
       <c r="A297" s="5" t="n"/>
       <c r="B297" s="5" t="n"/>
       <c r="C297" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B297,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B297,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D297" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B297,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B297,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E297" s="8" t="n"/>
@@ -6272,11 +6271,11 @@
       <c r="A298" s="5" t="n"/>
       <c r="B298" s="5" t="n"/>
       <c r="C298" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B298,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B298,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D298" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B298,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B298,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E298" s="8" t="n"/>
@@ -6291,11 +6290,11 @@
       <c r="A299" s="5" t="n"/>
       <c r="B299" s="5" t="n"/>
       <c r="C299" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B299,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B299,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D299" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B299,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B299,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E299" s="8" t="n"/>
@@ -6310,11 +6309,11 @@
       <c r="A300" s="5" t="n"/>
       <c r="B300" s="5" t="n"/>
       <c r="C300" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B300,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B300,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D300" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B300,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B300,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E300" s="8" t="n"/>
@@ -6329,11 +6328,11 @@
       <c r="A301" s="5" t="n"/>
       <c r="B301" s="5" t="n"/>
       <c r="C301" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B301,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B301,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D301" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B301,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B301,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E301" s="8" t="n"/>
@@ -6348,11 +6347,11 @@
       <c r="A302" s="5" t="n"/>
       <c r="B302" s="5" t="n"/>
       <c r="C302" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B302,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B302,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D302" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B302,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B302,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E302" s="8" t="n"/>
@@ -6367,11 +6366,11 @@
       <c r="A303" s="5" t="n"/>
       <c r="B303" s="5" t="n"/>
       <c r="C303" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B303,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B303,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D303" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B303,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B303,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E303" s="8" t="n"/>
@@ -6386,11 +6385,11 @@
       <c r="A304" s="5" t="n"/>
       <c r="B304" s="5" t="n"/>
       <c r="C304" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B304,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B304,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D304" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B304,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B304,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E304" s="8" t="n"/>
@@ -6405,11 +6404,11 @@
       <c r="A305" s="5" t="n"/>
       <c r="B305" s="5" t="n"/>
       <c r="C305" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B305,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B305,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D305" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B305,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B305,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E305" s="8" t="n"/>
@@ -6424,11 +6423,11 @@
       <c r="A306" s="5" t="n"/>
       <c r="B306" s="5" t="n"/>
       <c r="C306" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B306,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B306,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D306" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B306,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B306,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E306" s="8" t="n"/>
@@ -6443,11 +6442,11 @@
       <c r="A307" s="5" t="n"/>
       <c r="B307" s="5" t="n"/>
       <c r="C307" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B307,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B307,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D307" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B307,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B307,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E307" s="8" t="n"/>
@@ -6462,11 +6461,11 @@
       <c r="A308" s="5" t="n"/>
       <c r="B308" s="5" t="n"/>
       <c r="C308" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B308,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B308,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D308" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B308,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B308,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E308" s="8" t="n"/>
@@ -6481,11 +6480,11 @@
       <c r="A309" s="5" t="n"/>
       <c r="B309" s="5" t="n"/>
       <c r="C309" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B309,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B309,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D309" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B309,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B309,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E309" s="8" t="n"/>
@@ -6500,11 +6499,11 @@
       <c r="A310" s="5" t="n"/>
       <c r="B310" s="5" t="n"/>
       <c r="C310" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B310,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B310,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D310" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B310,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B310,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E310" s="8" t="n"/>
@@ -6519,11 +6518,11 @@
       <c r="A311" s="5" t="n"/>
       <c r="B311" s="5" t="n"/>
       <c r="C311" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B311,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B311,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D311" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B311,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B311,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E311" s="8" t="n"/>
@@ -6538,11 +6537,11 @@
       <c r="A312" s="5" t="n"/>
       <c r="B312" s="5" t="n"/>
       <c r="C312" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B312,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B312,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D312" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B312,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B312,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E312" s="8" t="n"/>
@@ -6557,11 +6556,11 @@
       <c r="A313" s="5" t="n"/>
       <c r="B313" s="5" t="n"/>
       <c r="C313" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B313,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B313,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D313" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B313,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B313,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E313" s="8" t="n"/>
@@ -6576,11 +6575,11 @@
       <c r="A314" s="5" t="n"/>
       <c r="B314" s="5" t="n"/>
       <c r="C314" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B314,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B314,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D314" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B314,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B314,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E314" s="8" t="n"/>
@@ -6595,11 +6594,11 @@
       <c r="A315" s="5" t="n"/>
       <c r="B315" s="5" t="n"/>
       <c r="C315" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B315,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B315,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D315" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B315,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B315,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E315" s="8" t="n"/>
@@ -6614,11 +6613,11 @@
       <c r="A316" s="5" t="n"/>
       <c r="B316" s="5" t="n"/>
       <c r="C316" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B316,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B316,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D316" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B316,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B316,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E316" s="8" t="n"/>
@@ -6633,11 +6632,11 @@
       <c r="A317" s="5" t="n"/>
       <c r="B317" s="5" t="n"/>
       <c r="C317" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B317,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B317,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D317" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B317,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B317,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E317" s="8" t="n"/>
@@ -6652,11 +6651,11 @@
       <c r="A318" s="5" t="n"/>
       <c r="B318" s="5" t="n"/>
       <c r="C318" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B318,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B318,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D318" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B318,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B318,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E318" s="8" t="n"/>
@@ -6671,11 +6670,11 @@
       <c r="A319" s="5" t="n"/>
       <c r="B319" s="5" t="n"/>
       <c r="C319" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B319,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B319,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D319" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B319,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B319,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E319" s="8" t="n"/>
@@ -6690,11 +6689,11 @@
       <c r="A320" s="5" t="n"/>
       <c r="B320" s="5" t="n"/>
       <c r="C320" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B320,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B320,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D320" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B320,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B320,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E320" s="8" t="n"/>
@@ -6709,11 +6708,11 @@
       <c r="A321" s="5" t="n"/>
       <c r="B321" s="5" t="n"/>
       <c r="C321" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B321,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B321,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D321" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B321,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B321,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E321" s="8" t="n"/>
@@ -6728,11 +6727,11 @@
       <c r="A322" s="5" t="n"/>
       <c r="B322" s="5" t="n"/>
       <c r="C322" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B322,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B322,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D322" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B322,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B322,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E322" s="8" t="n"/>
@@ -6747,11 +6746,11 @@
       <c r="A323" s="5" t="n"/>
       <c r="B323" s="5" t="n"/>
       <c r="C323" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B323,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B323,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D323" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B323,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B323,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E323" s="8" t="n"/>
@@ -6766,11 +6765,11 @@
       <c r="A324" s="5" t="n"/>
       <c r="B324" s="5" t="n"/>
       <c r="C324" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B324,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B324,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D324" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B324,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B324,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E324" s="8" t="n"/>
@@ -6785,11 +6784,11 @@
       <c r="A325" s="5" t="n"/>
       <c r="B325" s="5" t="n"/>
       <c r="C325" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B325,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B325,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D325" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B325,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B325,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E325" s="8" t="n"/>
@@ -6804,11 +6803,11 @@
       <c r="A326" s="5" t="n"/>
       <c r="B326" s="5" t="n"/>
       <c r="C326" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B326,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B326,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D326" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B326,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B326,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E326" s="8" t="n"/>
@@ -6823,11 +6822,11 @@
       <c r="A327" s="5" t="n"/>
       <c r="B327" s="5" t="n"/>
       <c r="C327" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B327,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B327,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D327" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B327,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B327,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E327" s="8" t="n"/>
@@ -6842,11 +6841,11 @@
       <c r="A328" s="5" t="n"/>
       <c r="B328" s="5" t="n"/>
       <c r="C328" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B328,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B328,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D328" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B328,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B328,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E328" s="8" t="n"/>
@@ -6861,11 +6860,11 @@
       <c r="A329" s="5" t="n"/>
       <c r="B329" s="5" t="n"/>
       <c r="C329" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B329,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B329,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D329" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B329,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B329,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E329" s="8" t="n"/>
@@ -6880,11 +6879,11 @@
       <c r="A330" s="5" t="n"/>
       <c r="B330" s="5" t="n"/>
       <c r="C330" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B330,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B330,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D330" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B330,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B330,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E330" s="8" t="n"/>
@@ -6899,11 +6898,11 @@
       <c r="A331" s="5" t="n"/>
       <c r="B331" s="5" t="n"/>
       <c r="C331" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B331,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B331,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D331" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B331,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B331,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E331" s="8" t="n"/>
@@ -6918,11 +6917,11 @@
       <c r="A332" s="5" t="n"/>
       <c r="B332" s="5" t="n"/>
       <c r="C332" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B332,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B332,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D332" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B332,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B332,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E332" s="8" t="n"/>
@@ -6937,11 +6936,11 @@
       <c r="A333" s="5" t="n"/>
       <c r="B333" s="5" t="n"/>
       <c r="C333" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B333,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B333,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D333" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B333,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B333,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E333" s="8" t="n"/>
@@ -6956,11 +6955,11 @@
       <c r="A334" s="5" t="n"/>
       <c r="B334" s="5" t="n"/>
       <c r="C334" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B334,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B334,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D334" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B334,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B334,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E334" s="8" t="n"/>
@@ -6975,11 +6974,11 @@
       <c r="A335" s="5" t="n"/>
       <c r="B335" s="5" t="n"/>
       <c r="C335" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B335,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B335,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D335" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B335,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B335,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E335" s="8" t="n"/>
@@ -6994,11 +6993,11 @@
       <c r="A336" s="5" t="n"/>
       <c r="B336" s="5" t="n"/>
       <c r="C336" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B336,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B336,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D336" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B336,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B336,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E336" s="8" t="n"/>
@@ -7013,11 +7012,11 @@
       <c r="A337" s="5" t="n"/>
       <c r="B337" s="5" t="n"/>
       <c r="C337" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B337,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B337,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D337" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B337,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B337,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E337" s="8" t="n"/>
@@ -7032,11 +7031,11 @@
       <c r="A338" s="5" t="n"/>
       <c r="B338" s="5" t="n"/>
       <c r="C338" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B338,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B338,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D338" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B338,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B338,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E338" s="8" t="n"/>
@@ -7051,11 +7050,11 @@
       <c r="A339" s="5" t="n"/>
       <c r="B339" s="5" t="n"/>
       <c r="C339" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B339,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B339,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D339" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B339,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B339,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E339" s="8" t="n"/>
@@ -7070,11 +7069,11 @@
       <c r="A340" s="5" t="n"/>
       <c r="B340" s="5" t="n"/>
       <c r="C340" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B340,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B340,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D340" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B340,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B340,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E340" s="8" t="n"/>
@@ -7089,11 +7088,11 @@
       <c r="A341" s="5" t="n"/>
       <c r="B341" s="5" t="n"/>
       <c r="C341" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B341,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B341,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D341" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B341,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B341,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E341" s="8" t="n"/>
@@ -7108,11 +7107,11 @@
       <c r="A342" s="5" t="n"/>
       <c r="B342" s="5" t="n"/>
       <c r="C342" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B342,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B342,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D342" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B342,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B342,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E342" s="8" t="n"/>
@@ -7127,11 +7126,11 @@
       <c r="A343" s="5" t="n"/>
       <c r="B343" s="5" t="n"/>
       <c r="C343" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B343,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B343,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D343" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B343,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B343,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E343" s="8" t="n"/>
@@ -7146,11 +7145,11 @@
       <c r="A344" s="5" t="n"/>
       <c r="B344" s="5" t="n"/>
       <c r="C344" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B344,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B344,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D344" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B344,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B344,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E344" s="8" t="n"/>
@@ -7165,11 +7164,11 @@
       <c r="A345" s="5" t="n"/>
       <c r="B345" s="5" t="n"/>
       <c r="C345" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B345,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B345,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D345" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B345,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B345,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E345" s="8" t="n"/>
@@ -7184,11 +7183,11 @@
       <c r="A346" s="5" t="n"/>
       <c r="B346" s="5" t="n"/>
       <c r="C346" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B346,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B346,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D346" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B346,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B346,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E346" s="8" t="n"/>
@@ -7203,11 +7202,11 @@
       <c r="A347" s="5" t="n"/>
       <c r="B347" s="5" t="n"/>
       <c r="C347" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B347,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B347,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D347" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B347,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B347,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E347" s="8" t="n"/>
@@ -7222,11 +7221,11 @@
       <c r="A348" s="5" t="n"/>
       <c r="B348" s="5" t="n"/>
       <c r="C348" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B348,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B348,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D348" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B348,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B348,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E348" s="8" t="n"/>
@@ -7241,11 +7240,11 @@
       <c r="A349" s="5" t="n"/>
       <c r="B349" s="5" t="n"/>
       <c r="C349" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B349,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B349,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D349" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B349,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B349,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E349" s="8" t="n"/>
@@ -7260,11 +7259,11 @@
       <c r="A350" s="5" t="n"/>
       <c r="B350" s="5" t="n"/>
       <c r="C350" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B350,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B350,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D350" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B350,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B350,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E350" s="8" t="n"/>
@@ -7279,11 +7278,11 @@
       <c r="A351" s="5" t="n"/>
       <c r="B351" s="5" t="n"/>
       <c r="C351" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B351,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B351,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D351" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B351,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B351,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E351" s="8" t="n"/>
@@ -7298,11 +7297,11 @@
       <c r="A352" s="5" t="n"/>
       <c r="B352" s="5" t="n"/>
       <c r="C352" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B352,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B352,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D352" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B352,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B352,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E352" s="8" t="n"/>
@@ -7317,11 +7316,11 @@
       <c r="A353" s="5" t="n"/>
       <c r="B353" s="5" t="n"/>
       <c r="C353" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B353,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B353,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D353" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B353,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B353,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E353" s="8" t="n"/>
@@ -7336,11 +7335,11 @@
       <c r="A354" s="5" t="n"/>
       <c r="B354" s="5" t="n"/>
       <c r="C354" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B354,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B354,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D354" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B354,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B354,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E354" s="8" t="n"/>
@@ -7355,11 +7354,11 @@
       <c r="A355" s="5" t="n"/>
       <c r="B355" s="5" t="n"/>
       <c r="C355" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B355,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B355,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D355" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B355,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B355,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E355" s="8" t="n"/>
@@ -7374,11 +7373,11 @@
       <c r="A356" s="5" t="n"/>
       <c r="B356" s="5" t="n"/>
       <c r="C356" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B356,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B356,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D356" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B356,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B356,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E356" s="8" t="n"/>
@@ -7393,11 +7392,11 @@
       <c r="A357" s="5" t="n"/>
       <c r="B357" s="5" t="n"/>
       <c r="C357" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B357,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B357,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D357" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B357,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B357,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E357" s="8" t="n"/>
@@ -7412,11 +7411,11 @@
       <c r="A358" s="5" t="n"/>
       <c r="B358" s="5" t="n"/>
       <c r="C358" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B358,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B358,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D358" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B358,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B358,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E358" s="8" t="n"/>
@@ -7431,11 +7430,11 @@
       <c r="A359" s="5" t="n"/>
       <c r="B359" s="5" t="n"/>
       <c r="C359" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B359,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B359,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D359" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B359,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B359,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E359" s="8" t="n"/>
@@ -7450,11 +7449,11 @@
       <c r="A360" s="5" t="n"/>
       <c r="B360" s="5" t="n"/>
       <c r="C360" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B360,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B360,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D360" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B360,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B360,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E360" s="8" t="n"/>
@@ -7469,11 +7468,11 @@
       <c r="A361" s="5" t="n"/>
       <c r="B361" s="5" t="n"/>
       <c r="C361" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B361,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B361,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D361" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B361,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B361,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E361" s="8" t="n"/>
@@ -7488,11 +7487,11 @@
       <c r="A362" s="5" t="n"/>
       <c r="B362" s="5" t="n"/>
       <c r="C362" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B362,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B362,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D362" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B362,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B362,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E362" s="8" t="n"/>
@@ -7507,11 +7506,11 @@
       <c r="A363" s="5" t="n"/>
       <c r="B363" s="5" t="n"/>
       <c r="C363" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B363,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B363,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D363" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B363,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B363,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E363" s="8" t="n"/>
@@ -7526,11 +7525,11 @@
       <c r="A364" s="5" t="n"/>
       <c r="B364" s="5" t="n"/>
       <c r="C364" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B364,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B364,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D364" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B364,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B364,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E364" s="8" t="n"/>
@@ -7545,11 +7544,11 @@
       <c r="A365" s="5" t="n"/>
       <c r="B365" s="5" t="n"/>
       <c r="C365" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B365,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B365,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D365" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B365,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B365,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E365" s="8" t="n"/>
@@ -7564,11 +7563,11 @@
       <c r="A366" s="5" t="n"/>
       <c r="B366" s="5" t="n"/>
       <c r="C366" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B366,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B366,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D366" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B366,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B366,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E366" s="8" t="n"/>
@@ -7583,11 +7582,11 @@
       <c r="A367" s="5" t="n"/>
       <c r="B367" s="5" t="n"/>
       <c r="C367" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B367,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B367,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D367" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B367,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B367,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E367" s="8" t="n"/>
@@ -7602,11 +7601,11 @@
       <c r="A368" s="5" t="n"/>
       <c r="B368" s="5" t="n"/>
       <c r="C368" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B368,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B368,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D368" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B368,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B368,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E368" s="8" t="n"/>
@@ -7621,11 +7620,11 @@
       <c r="A369" s="5" t="n"/>
       <c r="B369" s="5" t="n"/>
       <c r="C369" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B369,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B369,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D369" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B369,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B369,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E369" s="8" t="n"/>
@@ -7640,11 +7639,11 @@
       <c r="A370" s="5" t="n"/>
       <c r="B370" s="5" t="n"/>
       <c r="C370" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B370,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B370,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D370" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B370,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B370,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E370" s="8" t="n"/>
@@ -7659,11 +7658,11 @@
       <c r="A371" s="5" t="n"/>
       <c r="B371" s="5" t="n"/>
       <c r="C371" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B371,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B371,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D371" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B371,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B371,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E371" s="8" t="n"/>
@@ -7678,11 +7677,11 @@
       <c r="A372" s="5" t="n"/>
       <c r="B372" s="5" t="n"/>
       <c r="C372" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B372,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B372,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D372" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B372,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B372,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E372" s="8" t="n"/>
@@ -7697,11 +7696,11 @@
       <c r="A373" s="5" t="n"/>
       <c r="B373" s="5" t="n"/>
       <c r="C373" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B373,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B373,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D373" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B373,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B373,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E373" s="8" t="n"/>
@@ -7716,11 +7715,11 @@
       <c r="A374" s="5" t="n"/>
       <c r="B374" s="5" t="n"/>
       <c r="C374" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B374,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B374,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D374" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B374,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B374,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E374" s="8" t="n"/>
@@ -7735,11 +7734,11 @@
       <c r="A375" s="5" t="n"/>
       <c r="B375" s="5" t="n"/>
       <c r="C375" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B375,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B375,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D375" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B375,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B375,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E375" s="8" t="n"/>
@@ -7754,11 +7753,11 @@
       <c r="A376" s="5" t="n"/>
       <c r="B376" s="5" t="n"/>
       <c r="C376" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B376,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B376,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D376" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B376,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B376,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E376" s="8" t="n"/>
@@ -7773,11 +7772,11 @@
       <c r="A377" s="5" t="n"/>
       <c r="B377" s="5" t="n"/>
       <c r="C377" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B377,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B377,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D377" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B377,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B377,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E377" s="8" t="n"/>
@@ -7792,11 +7791,11 @@
       <c r="A378" s="5" t="n"/>
       <c r="B378" s="5" t="n"/>
       <c r="C378" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B378,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B378,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D378" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B378,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B378,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E378" s="8" t="n"/>
@@ -7811,11 +7810,11 @@
       <c r="A379" s="5" t="n"/>
       <c r="B379" s="5" t="n"/>
       <c r="C379" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B379,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B379,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D379" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B379,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B379,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E379" s="8" t="n"/>
@@ -7830,11 +7829,11 @@
       <c r="A380" s="5" t="n"/>
       <c r="B380" s="5" t="n"/>
       <c r="C380" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B380,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B380,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D380" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B380,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B380,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E380" s="8" t="n"/>
@@ -7849,11 +7848,11 @@
       <c r="A381" s="5" t="n"/>
       <c r="B381" s="5" t="n"/>
       <c r="C381" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B381,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B381,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D381" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B381,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B381,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E381" s="8" t="n"/>
@@ -7868,11 +7867,11 @@
       <c r="A382" s="5" t="n"/>
       <c r="B382" s="5" t="n"/>
       <c r="C382" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B382,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B382,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D382" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B382,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B382,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E382" s="8" t="n"/>
@@ -7887,11 +7886,11 @@
       <c r="A383" s="5" t="n"/>
       <c r="B383" s="5" t="n"/>
       <c r="C383" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B383,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B383,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D383" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B383,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B383,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E383" s="8" t="n"/>
@@ -7906,11 +7905,11 @@
       <c r="A384" s="5" t="n"/>
       <c r="B384" s="5" t="n"/>
       <c r="C384" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B384,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B384,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D384" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B384,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B384,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E384" s="8" t="n"/>
@@ -7925,11 +7924,11 @@
       <c r="A385" s="5" t="n"/>
       <c r="B385" s="5" t="n"/>
       <c r="C385" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B385,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B385,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D385" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B385,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B385,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E385" s="8" t="n"/>
@@ -7944,11 +7943,11 @@
       <c r="A386" s="5" t="n"/>
       <c r="B386" s="5" t="n"/>
       <c r="C386" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B386,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B386,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D386" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B386,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B386,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E386" s="8" t="n"/>
@@ -7963,11 +7962,11 @@
       <c r="A387" s="5" t="n"/>
       <c r="B387" s="5" t="n"/>
       <c r="C387" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B387,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B387,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D387" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B387,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B387,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E387" s="8" t="n"/>
@@ -7982,11 +7981,11 @@
       <c r="A388" s="5" t="n"/>
       <c r="B388" s="5" t="n"/>
       <c r="C388" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B388,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B388,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D388" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B388,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B388,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E388" s="8" t="n"/>
@@ -8001,11 +8000,11 @@
       <c r="A389" s="5" t="n"/>
       <c r="B389" s="5" t="n"/>
       <c r="C389" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B389,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B389,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D389" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B389,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B389,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E389" s="8" t="n"/>
@@ -8020,11 +8019,11 @@
       <c r="A390" s="5" t="n"/>
       <c r="B390" s="5" t="n"/>
       <c r="C390" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B390,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B390,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D390" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B390,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B390,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E390" s="8" t="n"/>
@@ -8039,11 +8038,11 @@
       <c r="A391" s="5" t="n"/>
       <c r="B391" s="5" t="n"/>
       <c r="C391" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B391,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B391,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D391" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B391,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B391,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E391" s="8" t="n"/>
@@ -8058,11 +8057,11 @@
       <c r="A392" s="5" t="n"/>
       <c r="B392" s="5" t="n"/>
       <c r="C392" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B392,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B392,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D392" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B392,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B392,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E392" s="8" t="n"/>
@@ -8077,11 +8076,11 @@
       <c r="A393" s="5" t="n"/>
       <c r="B393" s="5" t="n"/>
       <c r="C393" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B393,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B393,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D393" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B393,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B393,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E393" s="8" t="n"/>
@@ -8096,11 +8095,11 @@
       <c r="A394" s="5" t="n"/>
       <c r="B394" s="5" t="n"/>
       <c r="C394" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B394,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B394,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D394" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B394,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B394,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E394" s="8" t="n"/>
@@ -8115,11 +8114,11 @@
       <c r="A395" s="5" t="n"/>
       <c r="B395" s="5" t="n"/>
       <c r="C395" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B395,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B395,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D395" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B395,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B395,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E395" s="8" t="n"/>
@@ -8134,11 +8133,11 @@
       <c r="A396" s="5" t="n"/>
       <c r="B396" s="5" t="n"/>
       <c r="C396" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B396,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B396,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D396" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B396,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B396,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E396" s="8" t="n"/>
@@ -8153,11 +8152,11 @@
       <c r="A397" s="5" t="n"/>
       <c r="B397" s="5" t="n"/>
       <c r="C397" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B397,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B397,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D397" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B397,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B397,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E397" s="8" t="n"/>
@@ -8172,11 +8171,11 @@
       <c r="A398" s="5" t="n"/>
       <c r="B398" s="5" t="n"/>
       <c r="C398" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B398,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B398,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D398" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B398,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B398,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E398" s="8" t="n"/>
@@ -8191,11 +8190,11 @@
       <c r="A399" s="5" t="n"/>
       <c r="B399" s="5" t="n"/>
       <c r="C399" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B399,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B399,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D399" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B399,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B399,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E399" s="8" t="n"/>
@@ -8210,11 +8209,11 @@
       <c r="A400" s="5" t="n"/>
       <c r="B400" s="5" t="n"/>
       <c r="C400" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B400,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B400,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D400" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B400,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B400,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E400" s="8" t="n"/>
@@ -8229,11 +8228,11 @@
       <c r="A401" s="5" t="n"/>
       <c r="B401" s="5" t="n"/>
       <c r="C401" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B401,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B401,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D401" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B401,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B401,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E401" s="8" t="n"/>
@@ -8248,11 +8247,11 @@
       <c r="A402" s="5" t="n"/>
       <c r="B402" s="5" t="n"/>
       <c r="C402" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$139,MATCH(B402,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B402,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="D402" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$139,MATCH(B402,Productos!$A$2:$A$139,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B402,Productos!$A$2:$A$135,0)),"")</f>
         <v/>
       </c>
       <c r="E402" s="8" t="n"/>
@@ -8293,7 +8292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK35"/>
+  <dimension ref="A1:AJ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8329,34 +8328,34 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>BROWN'S</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>CAT CHOW</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>CUNIPIC</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>DOG CHOW</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>EMERALD</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ESBILAC</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>EUKANUBA</t>
-        </is>
-      </c>
       <c r="M1" t="inlineStr">
         <is>
           <t>FANCY FEAST</t>
@@ -8414,70 +8413,65 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>OLA</t>
+          <t>PERKY PET</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>PERKY PET</t>
+          <t>PET FACTORY</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>PET FACTORY</t>
+          <t>PRO PET</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>PRO PET</t>
+          <t>PRO PLAN</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>PRO PLAN</t>
+          <t>PURINA</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>PURINA</t>
+          <t>RED BARN</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>RED BARN</t>
+          <t>RUSH DIRECT</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>RUSH DIRECT</t>
+          <t>SMARTBONES</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>SMARTBONES</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPRA</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>TETRA</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>TRIUMPH</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
-        <is>
-          <t>TRIUMPH</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
         <is>
           <t>ZOO MED</t>
         </is>
@@ -8515,34 +8509,34 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>BRW ENCORE CONEJO 2LB · 90739690000</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>CAT CHOW ADULTO HOGARENO 1.5KG · 93520030000</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>D CUNIPIC PERICO AUSTRALIANO 3KG · 93501850000</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>DOG CHOW ADULTO 2KG · 93512370000</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>EP SNACK DENTAL SALMON P/GATO 3OZ · 93509220000</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>ESBILAC LECHE EN POLVO 12 ONZ · 90311050000</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>EUK DOG LARGE ADULT  3 Kg (6.61 lbs) · 90018590000</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>FANCY FEAST CHUNCKY POLLO 3 OZ · 93509350000</t>
@@ -8565,7 +8559,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>HIGGINS ALIM CONURO Y PERIQ 2.5LB · 93510560000</t>
+          <t>HIGGINS SUNBURST ALIM COBAYOS 3LB · 93510430000</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -8600,70 +8594,65 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>OLA CANARIOS 800GRS · 90405520000</t>
+          <t>NECTAR PARA COLIBRI 240 · 93502370000</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>NECTAR PARA COLIBRI 240 · 93502370000</t>
+          <t>PF HUESO/ CARNAZA SABOR M.MANI 8-9IN · 93514280000</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR M.MANI 8-9IN · 93514280000</t>
+          <t>PRO PET 1.5KG ADULTO · 93500000100</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>PRO PET 1.5KG ADULTO · 93500000100</t>
+          <t>PP ADULTO SENSITIVE SKIN  3KG · 93510171000</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>PP ADULTO SENSITIVE SKIN  3KG · 93510171000</t>
+          <t>3 PACK FELIX SURTIDO (3X156G) · 90040920000</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>3 PACK FELIX SURTIDO (3X156G) · 90040920000</t>
+          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
+          <t>D RD SNACK POPN BITES PESCAD P/GATOS · 93513040000</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>D RD SNACK POPN BITES PESCAD P/GATOS · 93513040000</t>
+          <t>D SB SMARTSTICKS DENTAL 5UD · 93519250000</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>D SB SMARTSTICKS DENTAL 5UD · 93519250000</t>
+          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
+          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>D SUPRA CACHORRO 10KG · 93508930000</t>
+          <t>D TETRA REPTOMIN 1.94 OZ · 90410040000</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>D TETRA REPTOMIN 1.94 OZ · 90410040000</t>
+          <t>D TRIUMPH LATA POLLO ARROZ VEG 13.2OZ · 90412960000</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
-        <is>
-          <t>D TRIUMPH LATA POLLO ARROZ VEG 13.2OZ · 90412960000</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
         <is>
           <t>D ZM ALIMENTO EN BLOQUE P TORTUGAS 5 · 93517490000</t>
         </is>
@@ -8694,26 +8683,21 @@
           <t>BILJAC CACHORROS 6LB · 93503120000</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>CAT CHOW DEFENSE PLUS PESCADO 1.5KG · 90408400000</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>DOG CHOW CACHORRO RAZA PEQUENA 2KG · 93512550000</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>ESBILAC PAPILLA P CACHORROS 14 OZ. · 90312680000</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>EUK DOG MEDIUM ADULT  3 Kg (6.61 lbs) · 90018570000</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>FANCY FEAST CHUNKY PAVO 3 OZ · 93509340000</t>
@@ -8736,7 +8720,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>HIGGINS SUNBURST ALIM COBAYOS 3LB · 93510430000</t>
+          <t>HIGGINS SUNBURST ALIM P CONEJOS 3LB · 93510440000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -8759,52 +8743,47 @@
           <t>NS CHOICE CACHORR POLLO CEBADA 5OZ MUEST · 90034110000</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>OLA FINCHES/ PAJAROS EXOTICOS 800 · 90405540000</t>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PF HUESO/ CARNAZA SABOR POLLO 8-9IN · 93514230000</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR POLLO 8-9IN · 93514230000</t>
+          <t>PRO PET 1.5KG CACHORRO · 93500000200</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>PRO PET 1.5KG CACHORRO · 93500000200</t>
+          <t>PP PROPLAN CACHORROS RZ MD OPTI 3KG · 93520130000</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>PP PROPLAN ADULTO CARNE POUCH 85G · 93520280000</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
           <t>4 PACK FELIX SURTIDO (4X85G) · 90040930000</t>
         </is>
       </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>D SB SMARTSTICKS POLLO 5UD · 93519230000</t>
+        </is>
+      </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>D SB SMARTSTICKS POLLO 5UD · 93519230000</t>
+          <t>ROCKY ADULTOS 1KG · 93500000342</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 1KG · 93500000342</t>
+          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
           <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>ZM CALCIO GDE CON VEGETALES P/AVES · 93503050000</t>
         </is>
@@ -8830,7 +8809,7 @@
           <t>ASCAN ADULTOS 1KG · 93513390000</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>DOG CHOW CACHORROS POLLO POUCH 100G MX · 90038330000</t>
         </is>
@@ -8842,7 +8821,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>FELIX GATITOS 500G MX · 90038510000</t>
+          <t>FELIX MEGAMIX ADULTO 500G MX · 90038550000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -8855,11 +8834,6 @@
           <t>SEMILLAS DE GIRASOL JUMBO 454GR · 90426190000</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>HIGGINS SUNBURST ALIM P CONEJOS 3LB · 93510440000</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>MIMADOS ADULTOS 4KG · 93513340000</t>
@@ -8880,42 +8854,42 @@
           <t>NS CHOICE CARNE Y CEBADA 5LB · 90033960000</t>
         </is>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PF HUESO/CARNAZA SABOR CARNE 4IN-5IN · 93514210000</t>
+        </is>
+      </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>PF HUESO/CARNAZA SABOR CARNE 4IN-5IN · 93514210000</t>
+          <t>PRO PET 4KG ADULTO · 93500000300</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>PRO PET 4KG ADULTO · 93500000300</t>
+          <t>PROPLAN ADULTO BOCADOS PEQUENOS 1KG MX · 90038590000</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORROS RZ MD OPTI 3KG · 93520130000</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
           <t>CATCHOW GATITO DEFENSE PLUS 1.5KG · 93520020000</t>
         </is>
       </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>ROCKY ADULTOS 500G · 93500000341</t>
+        </is>
+      </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 500G · 93500000341</t>
+          <t>SUPRA ADULTO 18KG · 93508890000</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
           <t>TETRA BETTAMIN .81OZ  23GR · 90410310000</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>ZM CALCIO PQNO CON VEGETALES P/AVES · 93503060000</t>
         </is>
@@ -8924,7 +8898,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAT CHOW</t>
+          <t>BROWN'S</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -8941,14 +8915,14 @@
           <t>ASCAN CACHORROS 1KG · 93513380000</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>DOG CHOW CARNE POUCH 100G MX · 90038300000</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>FELIX MEGAMIX ADULTO 500G MX · 90038550000</t>
+          <t>FELIX PATE PESCADO Y ATUN 156G · 93502640000</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -8973,7 +8947,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 16KG · 93505950000</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -8981,42 +8955,42 @@
           <t>NS CHOICE CARNE Y CEBADA 5OZ MUESTRA · 90033980000</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PF HUESO/CARNAZA SABOR POLLO 4IN-5IN · 93514260000</t>
+        </is>
+      </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>PF HUESO/CARNAZA SABOR POLLO 4IN-5IN · 93514260000</t>
+          <t>PRO PET 4KG CACHORRO · 93500000400</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>PRO PET 4KG CACHORRO · 93500000400</t>
+          <t>PROPLAN ADULTO RZ MED OPTIHEALTH 3 · 93520000000</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>PROPLAN ADULTO BOCADOS PEQUENOS 1KG MX · 90038590000</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
           <t>PRO PLAN CACHORRO RAZA PEQUEÑA 4x3.5kgMX · 90026950000</t>
         </is>
       </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
+        </is>
+      </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
+          <t>SUPRA ADULTO 30KG · 93508900000</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 18KG · 93508890000</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
           <t>TETRA HOJUELA GOLDFISH 2.2OZ · 90409670000</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>ZM MICRO PELLET P/BETTA 0.12OZ · 93514830000</t>
         </is>
@@ -9025,7 +8999,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CUNIPIC</t>
+          <t>CAT CHOW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -9035,7 +9009,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>FELIX PATE PESCADO Y ATUN 156G · 93502640000</t>
+          <t>FELIX PATE SALMON 156G · 93502650000</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -9045,7 +9019,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -9053,27 +9027,22 @@
           <t>NS CHOICE LATA CACHOR POLLO ARROZ 12.3OZ · 90034200000</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>PF ROLLO/ CARNAZA SABOR POLLO 10IN · 93514240000</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>PROPLAN ADULTO RZ MED OPTIHEALTH 3 · 93520000000</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
           <t>PURINA FELIX ATUN EN SALSA 85G · 93516230000</t>
         </is>
       </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>SUPRA ADULTO 4KG · 93508870000</t>
+        </is>
+      </c>
       <c r="AH6" t="inlineStr">
-        <is>
-          <t>SUPRA ADULTO 30KG · 93508900000</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
         <is>
           <t>TETRA HOJUELAS GOLDFISH .42OZ · 90409900000</t>
         </is>
@@ -9082,7 +9051,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DOG CHOW</t>
+          <t>CUNIPIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -9090,14 +9059,9 @@
           <t>MARCA_6</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>FELIX PATE SALMON 156G · 93502650000</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -9105,22 +9069,22 @@
           <t>NS CHOICE LATA CARNE Y CEBADA 12.3OZ · 90034180000</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>PF TRENZA/CARNAZA SABOR NATURAL 7IN · 93517760000</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>PURINA FELIX PAVO EN SALSA 85G · 93516200000</t>
         </is>
       </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>SUPRA CACHORRO 1.5KG · 93508910000</t>
+        </is>
+      </c>
       <c r="AH7" t="inlineStr">
-        <is>
-          <t>SUPRA ADULTO 4KG · 93508870000</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
         <is>
           <t>TETRA HOJUELAS GOLDFISH 3.53OZ · 90409910000</t>
         </is>
@@ -9129,7 +9093,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EMERALD</t>
+          <t>DOG CHOW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -9139,7 +9103,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 8KG · 93505940000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -9147,17 +9111,17 @@
           <t>NS CHOICE LATA PAVO Y CEBADA 12.3OZ · 90034290000</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>PURINA FELIX PESCADO EN SALSA 85G · 93516210000</t>
         </is>
       </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>SUPRA CACHORRO 18KG · 93508940000</t>
+        </is>
+      </c>
       <c r="AH8" t="inlineStr">
-        <is>
-          <t>SUPRA CACHORRO 1.5KG · 93508910000</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
         <is>
           <t>TETRA HOJUELAS TROPICAL 0.42OZ · 90409920000</t>
         </is>
@@ -9166,7 +9130,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ESBILAC</t>
+          <t>EMERALD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -9176,7 +9140,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 8KG · 93505940000</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -9184,12 +9148,12 @@
           <t>NS CHOICE LATA POLLO Y CEBADA 12.3OZ · 90034190000</t>
         </is>
       </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>SUPRA CACHORRO 30KG · 93508950000</t>
+        </is>
+      </c>
       <c r="AH9" t="inlineStr">
-        <is>
-          <t>SUPRA CACHORRO 18KG · 93508940000</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
         <is>
           <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
         </is>
@@ -9198,7 +9162,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EUKANUBA</t>
+          <t>ESBILAC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -9208,7 +9172,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
+          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -9216,9 +9180,9 @@
           <t>NS CHOICE PAVO Y CEBADA 5LB · 90034130000</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>SUPRA CACHORRO 30KG · 93508950000</t>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>SUPRA CACHORRO 4KG · 93508920000</t>
         </is>
       </c>
     </row>
@@ -9235,17 +9199,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
+          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>NS CHOICE PESCADO Y ARROZ 5LB · 90034160000</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>SUPRA CACHORRO 4KG · 93508920000</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9221,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 16KG · 90410820000</t>
+          <t>SOLLA NUTRECAN BABIES 8 KG · 90410970000</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -9284,7 +9243,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 2KG · 90415960000</t>
+          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -9306,7 +9265,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
+          <t>SOLLA NUTRECAN CAMPO 16KG · 90410820000</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -9328,7 +9287,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
+          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -9350,7 +9309,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
+          <t>SOLLA NUTRECAN CAMPO 2KG · 90415960000</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -9370,6 +9329,11 @@
           <t>MARCA_16</t>
         </is>
       </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr">
         <is>
           <t>NS CHOICE SNACK GRILLERS POLLO 12OZ · 90034230000</t>
@@ -9387,6 +9351,11 @@
           <t>MARCA_17</t>
         </is>
       </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>NS LATA GF PERRO POLLO 13OZ · 93500000472</t>
@@ -9404,6 +9373,11 @@
           <t>MARCA_18</t>
         </is>
       </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9432,7 +9406,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OLA</t>
+          <t>PERKY PET</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9444,7 +9418,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PERKY PET</t>
+          <t>PET FACTORY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9456,7 +9430,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PET FACTORY</t>
+          <t>PRO PET</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -9468,7 +9442,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PRO PET</t>
+          <t>PRO PLAN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -9480,7 +9454,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PRO PLAN</t>
+          <t>PURINA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -9492,7 +9466,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PURINA</t>
+          <t>RED BARN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -9504,7 +9478,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RED BARN</t>
+          <t>RUSH DIRECT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -9516,7 +9490,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RUSH DIRECT</t>
+          <t>SMARTBONES</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -9528,7 +9502,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SMARTBONES</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -9540,7 +9514,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPRA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -9552,7 +9526,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>TETRA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -9564,7 +9538,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>TRIUMPH</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -9576,24 +9550,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TRIUMPH</t>
+          <t>ZOO MED</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>MARCA_33</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>ZOO MED</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>MARCA_34</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D143"/>
+  <dimension ref="A1:D139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9776,36 +9738,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAT CHOW ADULTO HOGARENO 1.5KG · 93520030000</t>
+          <t>BRW ENCORE CONEJO 2LB · 90739690000</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>93520030000</t>
+          <t>90739690000</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CAT CHOW</t>
+          <t>BROWN'S</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAT CHOW DEFENSE PLUS PESCADO 1.5KG · 90408400000</t>
+          <t>CAT CHOW ADULTO HOGARENO 1.5KG · 93520030000</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90408400000</t>
+          <t>93520030000</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -9816,56 +9778,56 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D CUNIPIC PERICO AUSTRALIANO 3KG · 93501850000</t>
+          <t>CAT CHOW DEFENSE PLUS PESCADO 1.5KG · 90408400000</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>93501850000</t>
+          <t>90408400000</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CUNIPIC</t>
+          <t>CAT CHOW</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DOG CHOW ADULTO 2KG · 93512370000</t>
+          <t>D CUNIPIC PERICO AUSTRALIANO 3KG · 93501850000</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>93512370000</t>
+          <t>93501850000</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DOG CHOW</t>
+          <t>CUNIPIC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DOG CHOW CACHORRO RAZA PEQUENA 2KG · 93512550000</t>
+          <t>DOG CHOW ADULTO 2KG · 93512370000</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>93512550000</t>
+          <t>93512370000</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9876,16 +9838,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DOG CHOW CACHORROS POLLO POUCH 100G MX · 90038330000</t>
+          <t>DOG CHOW CACHORRO RAZA PEQUENA 2KG · 93512550000</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90038330000</t>
+          <t>93512550000</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -9896,12 +9858,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DOG CHOW CARNE POUCH 100G MX · 90038300000</t>
+          <t>DOG CHOW CACHORROS POLLO POUCH 100G MX · 90038330000</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90038300000</t>
+          <t>90038330000</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -9916,56 +9878,56 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EP SNACK DENTAL SALMON P/GATO 3OZ · 93509220000</t>
+          <t>DOG CHOW CARNE POUCH 100G MX · 90038300000</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>93509220000</t>
+          <t>90038300000</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EMERALD</t>
+          <t>DOG CHOW</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ESBILAC LECHE EN POLVO 12 ONZ · 90311050000</t>
+          <t>EP SNACK DENTAL SALMON P/GATO 3OZ · 93509220000</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90311050000</t>
+          <t>93509220000</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ESBILAC</t>
+          <t>EMERALD</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ESBILAC PAPILLA P CACHORROS 14 OZ. · 90312680000</t>
+          <t>ESBILAC LECHE EN POLVO 12 ONZ · 90311050000</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90312680000</t>
+          <t>90311050000</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -9976,56 +9938,56 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EUK DOG LARGE ADULT  3 Kg (6.61 lbs) · 90018590000</t>
+          <t>ESBILAC PAPILLA P CACHORROS 14 OZ. · 90312680000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90018590000</t>
+          <t>90312680000</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EUKANUBA</t>
+          <t>ESBILAC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EUK DOG MEDIUM ADULT  3 Kg (6.61 lbs) · 90018570000</t>
+          <t>FANCY FEAST CHUNCKY POLLO 3 OZ · 93509350000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90018570000</t>
+          <t>93509350000</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EUKANUBA</t>
+          <t>FANCY FEAST</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FANCY FEAST CHUNCKY POLLO 3 OZ · 93509350000</t>
+          <t>FANCY FEAST CHUNKY PAVO 3 OZ · 93509340000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>93509350000</t>
+          <t>93509340000</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -10036,16 +9998,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FANCY FEAST CHUNKY PAVO 3 OZ · 93509340000</t>
+          <t>FANCY FEAST TRUCHA 3 OZ · 93509370000</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>93509340000</t>
+          <t>93509370000</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -10056,36 +10018,36 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FANCY FEAST TRUCHA 3 OZ · 93509370000</t>
+          <t>FELIX CARNE GATITOS 85G MX · 90038450000</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>93509370000</t>
+          <t>90038450000</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FANCY FEAST</t>
+          <t>FELIX</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FELIX CARNE GATITOS 85G MX · 90038450000</t>
+          <t>FELIX DELICIAS DE LA GRANJA ADULTO 1KG M · 90038530000</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>90038450000</t>
+          <t>90038530000</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -10096,16 +10058,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FELIX DELICIAS DE LA GRANJA ADULTO 1KG M · 90038530000</t>
+          <t>FELIX MEGAMIX ADULTO 500G MX · 90038550000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90038530000</t>
+          <t>90038550000</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -10116,16 +10078,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FELIX GATITOS 500G MX · 90038510000</t>
+          <t>FELIX PATE PESCADO Y ATUN 156G · 93502640000</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90038510000</t>
+          <t>93502640000</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -10136,16 +10098,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FELIX MEGAMIX ADULTO 500G MX · 90038550000</t>
+          <t>FELIX PATE SALMON 156G · 93502650000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>90038550000</t>
+          <t>93502650000</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -10156,56 +10118,56 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FELIX PATE PESCADO Y ATUN 156G · 93502640000</t>
+          <t>GATI ATUN 2.2LB · 93519180000</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>93502640000</t>
+          <t>93519180000</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>GATI</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FELIX PATE SALMON 156G · 93502650000</t>
+          <t>GATI GATITOS 2.2LB · 93519200000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>93502650000</t>
+          <t>93519200000</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>GATI</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GATI ATUN 2.2LB · 93519180000</t>
+          <t>GATI PESCADO 2.2LB · 93519140000</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>93519180000</t>
+          <t>93519140000</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -10216,16 +10178,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GATI GATITOS 2.2LB · 93519200000</t>
+          <t>GATI POLLO 2.2LB · 93519130000</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>93519200000</t>
+          <t>93519130000</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -10236,56 +10198,56 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GATI PESCADO 2.2LB · 93519140000</t>
+          <t>SEM ALPISTE  1 LB · 90426180000</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>93519140000</t>
+          <t>90426180000</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GATI</t>
+          <t>GENÉRICO (reempaque)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GATI POLLO 2.2LB · 93519130000</t>
+          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>93519130000</t>
+          <t>90402150000</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GATI</t>
+          <t>GENÉRICO (reempaque)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SEM ALPISTE  1 LB · 90426180000</t>
+          <t>SEMILLAS DE GIRASOL JUMBO 454GR · 90426190000</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>90426180000</t>
+          <t>90426190000</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -10296,16 +10258,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
+          <t>SEMILLAS DE GIRASOL JUMBO 5 LB · 90426200000</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>90402150000</t>
+          <t>90426200000</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -10316,16 +10278,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SEMILLAS DE GIRASOL JUMBO 454GR · 90426190000</t>
+          <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>90426190000</t>
+          <t>93500750000</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -10336,72 +10298,72 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SEMILLAS DE GIRASOL JUMBO 5 LB · 90426200000</t>
+          <t>HIGGINS SUNBURST ALIM COBAYOS 3LB · 93510430000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>90426200000</t>
+          <t>93510430000</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>GENÉRICO (reempaque)</t>
+          <t>HIGGINS</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
+          <t>HIGGINS SUNBURST ALIM P CONEJOS 3LB · 93510440000</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>93500750000</t>
+          <t>93510440000</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>GENÉRICO (reempaque)</t>
+          <t>HIGGINS</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HIGGINS ALIM CONURO Y PERIQ 2.5LB · 93510560000</t>
+          <t>KT ALIM. SUPREME CONEJO 5 LB · 90405210000</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>93510560000</t>
+          <t>90405210000</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>HIGGINS</t>
+          <t>KAYTEE</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HIGGINS SUNBURST ALIM COBAYOS 3LB · 93510430000</t>
+          <t>KORDON VITAMINAS AVES GRANDES 2 OZ · 90720740000</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>93510430000</t>
+          <t>90720740000</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -10409,39 +10371,39 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>HIGGINS</t>
+          <t>KORDON</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HIGGINS SUNBURST ALIM P CONEJOS 3LB · 93510440000</t>
+          <t>MIMADOS ADULTO 18KG · 90409680000</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>93510440000</t>
+          <t>90409680000</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>HIGGINS</t>
+          <t>MIMADOS</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KT ALIM. SUPREME CONEJO 5 LB · 90405210000</t>
+          <t>MIMADOS ADULTO 2KG · 90400360000</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>90405210000</t>
+          <t>90400360000</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -10449,43 +10411,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>KAYTEE</t>
+          <t>MIMADOS</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KORDON VITAMINAS AVES GRANDES 2 OZ · 90720740000</t>
+          <t>MIMADOS ADULTOS 4KG · 93513340000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>90720740000</t>
+          <t>93513340000</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KORDON</t>
+          <t>MIMADOS</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTO 18KG · 90409680000</t>
+          <t>MIMADOS CACHORROS 4KG · 93513280000</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>90409680000</t>
+          <t>93513280000</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -10496,76 +10458,76 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTO 2KG · 90400360000</t>
+          <t>MIRRAPEL CACHORROS 120 ML · 90322660000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>90400360000</t>
+          <t>90322660000</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MIMADOS</t>
+          <t>MIRRAPEL</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTOS 4KG · 93513340000</t>
+          <t>MIRRAPEL CACHORROS 236 ML · 90322670000</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>93513340000</t>
+          <t>90322670000</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MIMADOS</t>
+          <t>MIRRAPEL</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MIMADOS CACHORROS 4KG · 93513280000</t>
+          <t>MIRRAPEL OLEOSO 120 ML · 90322650000</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>93513280000</t>
+          <t>90322650000</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MIMADOS</t>
+          <t>MIRRAPEL</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MIRRAPEL CACHORROS 120 ML · 90322660000</t>
+          <t>MIRRAPEL PET POLVO 300 g · 90301720000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>90322660000</t>
+          <t>90301720000</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -10576,76 +10538,76 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MIRRAPEL CACHORROS 236 ML · 90322670000</t>
+          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 2KG · 93510820000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>90322670000</t>
+          <t>93510820000</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MIRRAPEL</t>
+          <t>NUTRECAN</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MIRRAPEL OLEOSO 120 ML · 90322650000</t>
+          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>90322650000</t>
+          <t>93510810000</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>MIRRAPEL</t>
+          <t>NUTRECAN</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MIRRAPEL PET POLVO 300 g · 90301720000</t>
+          <t>SOLLA NUTRECAN ADULTO RM Y RG 800GR · 93505910000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>90301720000</t>
+          <t>93505910000</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>134</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>MIRRAPEL</t>
+          <t>NUTRECAN</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 2KG · 93510820000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 16KG · 93505950000</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>93510820000</t>
+          <t>93505950000</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -10656,16 +10618,16 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>93510810000</t>
+          <t>93505960000</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -10676,16 +10638,16 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTO RM Y RG 800GR · 93505910000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>93505910000</t>
+          <t>93505920000</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>134</v>
+        <v>7</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -10696,16 +10658,16 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>93505960000</t>
+          <t>93505930000</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -10716,16 +10678,16 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 8KG · 93505940000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>93505920000</t>
+          <t>93505940000</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -10736,16 +10698,16 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
+          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>93505930000</t>
+          <t>90410720000</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -10756,16 +10718,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 8KG · 93505940000</t>
+          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>93505940000</t>
+          <t>90410730000</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -10776,16 +10738,16 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
+          <t>SOLLA NUTRECAN BABIES 8 KG · 90410970000</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>90410720000</t>
+          <t>90410970000</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -10796,16 +10758,16 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
+          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>90410730000</t>
+          <t>90410800000</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -10816,16 +10778,16 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
+          <t>SOLLA NUTRECAN CAMPO 16KG · 90410820000</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>90410800000</t>
+          <t>90410820000</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -10836,12 +10798,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 16KG · 90410820000</t>
+          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>90410820000</t>
+          <t>90410830000</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -10865,7 +10827,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -11276,76 +11238,76 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>OLA CANARIOS 800GRS · 90405520000</t>
+          <t>NECTAR PARA COLIBRI 240 · 93502370000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>90405520000</t>
+          <t>93502370000</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>OLA</t>
+          <t>PERKY PET</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>OLA FINCHES/ PAJAROS EXOTICOS 800 · 90405540000</t>
+          <t>PF HUESO/ CARNAZA SABOR M.MANI 8-9IN · 93514280000</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>90405540000</t>
+          <t>93514280000</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>OLA</t>
+          <t>PET FACTORY</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>NECTAR PARA COLIBRI 240 · 93502370000</t>
+          <t>PF HUESO/ CARNAZA SABOR POLLO 8-9IN · 93514230000</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>93502370000</t>
+          <t>93514230000</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>PERKY PET</t>
+          <t>PET FACTORY</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR M.MANI 8-9IN · 93514280000</t>
+          <t>PF HUESO/CARNAZA SABOR CARNE 4IN-5IN · 93514210000</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>93514280000</t>
+          <t>93514210000</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11356,16 +11318,16 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR POLLO 8-9IN · 93514230000</t>
+          <t>PF HUESO/CARNAZA SABOR POLLO 4IN-5IN · 93514260000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>93514230000</t>
+          <t>93514260000</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11376,16 +11338,16 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PF HUESO/CARNAZA SABOR CARNE 4IN-5IN · 93514210000</t>
+          <t>PF ROLLO/ CARNAZA SABOR POLLO 10IN · 93514240000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>93514210000</t>
+          <t>93514240000</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11396,16 +11358,16 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PF HUESO/CARNAZA SABOR POLLO 4IN-5IN · 93514260000</t>
+          <t>PF TRENZA/CARNAZA SABOR NATURAL 7IN · 93517760000</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>93514260000</t>
+          <t>93517760000</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11416,56 +11378,56 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PF ROLLO/ CARNAZA SABOR POLLO 10IN · 93514240000</t>
+          <t>PRO PET 1.5KG ADULTO · 93500000100</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>93514240000</t>
+          <t>93500000100</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>PET FACTORY</t>
+          <t>PRO PET</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PF TRENZA/CARNAZA SABOR NATURAL 7IN · 93517760000</t>
+          <t>PRO PET 1.5KG CACHORRO · 93500000200</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>93517760000</t>
+          <t>93500000200</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>PET FACTORY</t>
+          <t>PRO PET</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PRO PET 1.5KG ADULTO · 93500000100</t>
+          <t>PRO PET 4KG ADULTO · 93500000300</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>93500000100</t>
+          <t>93500000300</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11476,16 +11438,16 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PRO PET 1.5KG CACHORRO · 93500000200</t>
+          <t>PRO PET 4KG CACHORRO · 93500000400</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>93500000200</t>
+          <t>93500000400</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11496,56 +11458,56 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PRO PET 4KG ADULTO · 93500000300</t>
+          <t>PP ADULTO SENSITIVE SKIN  3KG · 93510171000</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>93500000300</t>
+          <t>93510171000</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>PRO PET</t>
+          <t>PRO PLAN</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PRO PET 4KG CACHORRO · 93500000400</t>
+          <t>PP PROPLAN CACHORROS RZ MD OPTI 3KG · 93520130000</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>93500000400</t>
+          <t>93520130000</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>PRO PET</t>
+          <t>PRO PLAN</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PP ADULTO SENSITIVE SKIN  3KG · 93510171000</t>
+          <t>PROPLAN ADULTO BOCADOS PEQUENOS 1KG MX · 90038590000</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>93510171000</t>
+          <t>90038590000</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11556,16 +11518,16 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PP PROPLAN ADULTO CARNE POUCH 85G · 93520280000</t>
+          <t>PROPLAN ADULTO RZ MED OPTIHEALTH 3 · 93520000000</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>93520280000</t>
+          <t>93520000000</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11576,12 +11538,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORROS RZ MD OPTI 3KG · 93520130000</t>
+          <t>3 PACK FELIX SURTIDO (3X156G) · 90040920000</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>93520130000</t>
+          <t>90040920000</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11589,63 +11551,63 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>PRO PLAN</t>
+          <t>PURINA</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PROPLAN ADULTO BOCADOS PEQUENOS 1KG MX · 90038590000</t>
+          <t>4 PACK FELIX SURTIDO (4X85G) · 90040930000</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>90038590000</t>
+          <t>90040930000</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>PRO PLAN</t>
+          <t>PURINA</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PROPLAN ADULTO RZ MED OPTIHEALTH 3 · 93520000000</t>
+          <t>CATCHOW GATITO DEFENSE PLUS 1.5KG · 93520020000</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>93520000000</t>
+          <t>93520020000</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>PRO PLAN</t>
+          <t>PURINA</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3 PACK FELIX SURTIDO (3X156G) · 90040920000</t>
+          <t>PRO PLAN CACHORRO RAZA PEQUEÑA 4x3.5kgMX · 90026950000</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>90040920000</t>
+          <t>90026950000</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11656,16 +11618,16 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>4 PACK FELIX SURTIDO (4X85G) · 90040930000</t>
+          <t>PURINA FELIX ATUN EN SALSA 85G · 93516230000</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>90040930000</t>
+          <t>93516230000</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11676,16 +11638,16 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CATCHOW GATITO DEFENSE PLUS 1.5KG · 93520020000</t>
+          <t>PURINA FELIX PAVO EN SALSA 85G · 93516200000</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>93520020000</t>
+          <t>93516200000</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11696,16 +11658,16 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PRO PLAN CACHORRO RAZA PEQUEÑA 4x3.5kgMX · 90026950000</t>
+          <t>PURINA FELIX PESCADO EN SALSA 85G · 93516210000</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>90026950000</t>
+          <t>93516210000</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11716,156 +11678,156 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PURINA FELIX ATUN EN SALSA 85G · 93516230000</t>
+          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>93516230000</t>
+          <t>93512180000</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>PURINA</t>
+          <t>RED BARN</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PURINA FELIX PAVO EN SALSA 85G · 93516200000</t>
+          <t>D RD SNACK POPN BITES PESCAD P/GATOS · 93513040000</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>93516200000</t>
+          <t>93513040000</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>PURINA</t>
+          <t>RUSH DIRECT</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PURINA FELIX PESCADO EN SALSA 85G · 93516210000</t>
+          <t>D SB SMARTSTICKS DENTAL 5UD · 93519250000</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>93516210000</t>
+          <t>93519250000</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>PURINA</t>
+          <t>SMARTBONES</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
+          <t>D SB SMARTSTICKS POLLO 5UD · 93519230000</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>93512180000</t>
+          <t>93519230000</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>RED BARN</t>
+          <t>SMARTBONES</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>D RD SNACK POPN BITES PESCAD P/GATOS · 93513040000</t>
+          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>93513040000</t>
+          <t>90022370000</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>RUSH DIRECT</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>D SB SMARTSTICKS DENTAL 5UD · 93519250000</t>
+          <t>ROCKY ADULTOS 1KG · 93500000342</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>93519250000</t>
+          <t>93500000342</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>SMARTBONES</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>D SB SMARTSTICKS POLLO 5UD · 93519230000</t>
+          <t>ROCKY ADULTOS 500G · 93500000341</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>93519230000</t>
+          <t>93500000341</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>SMARTBONES</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
+          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>90022370000</t>
+          <t>93511670000</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11876,76 +11838,76 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 1KG · 93500000342</t>
+          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>93500000342</t>
+          <t>93509320000</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPRA</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 500G · 93500000341</t>
+          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>93500000341</t>
+          <t>93508860000</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPRA</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
+          <t>SUPRA ADULTO 18KG · 93508890000</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>93511670000</t>
+          <t>93508890000</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPRA</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>D SUPRA CACHORRO 10KG · 93508930000</t>
+          <t>SUPRA ADULTO 30KG · 93508900000</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>93508930000</t>
+          <t>93508900000</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11956,16 +11918,16 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
+          <t>SUPRA ADULTO 4KG · 93508870000</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>93509320000</t>
+          <t>93508870000</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11976,16 +11938,16 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
+          <t>SUPRA CACHORRO 1.5KG · 93508910000</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>93508860000</t>
+          <t>93508910000</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11996,16 +11958,16 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 18KG · 93508890000</t>
+          <t>SUPRA CACHORRO 18KG · 93508940000</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>93508890000</t>
+          <t>93508940000</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12016,16 +11978,16 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 30KG · 93508900000</t>
+          <t>SUPRA CACHORRO 30KG · 93508950000</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>93508900000</t>
+          <t>93508950000</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12036,12 +11998,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 4KG · 93508870000</t>
+          <t>SUPRA CACHORRO 4KG · 93508920000</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>93508870000</t>
+          <t>93508920000</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -12056,96 +12018,96 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 1.5KG · 93508910000</t>
+          <t>D TETRA REPTOMIN 1.94 OZ · 90410040000</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>93508910000</t>
+          <t>90410040000</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>TETRA</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 18KG · 93508940000</t>
+          <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>93508940000</t>
+          <t>90409640000</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>TETRA</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 30KG · 93508950000</t>
+          <t>TETRA BETTAMIN .81OZ  23GR · 90410310000</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>93508950000</t>
+          <t>90410310000</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>TETRA</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 4KG · 93508920000</t>
+          <t>TETRA HOJUELA GOLDFISH 2.2OZ · 90409670000</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>93508920000</t>
+          <t>90409670000</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>TETRA</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>D TETRA REPTOMIN 1.94 OZ · 90410040000</t>
+          <t>TETRA HOJUELAS GOLDFISH .42OZ · 90409900000</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>90410040000</t>
+          <t>90409900000</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12156,16 +12118,16 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
+          <t>TETRA HOJUELAS GOLDFISH 3.53OZ · 90409910000</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>90409640000</t>
+          <t>90409910000</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12176,16 +12138,16 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TETRA BETTAMIN .81OZ  23GR · 90410310000</t>
+          <t>TETRA HOJUELAS TROPICAL 0.42OZ · 90409920000</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>90410310000</t>
+          <t>90409920000</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12196,16 +12158,16 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TETRA HOJUELA GOLDFISH 2.2OZ · 90409670000</t>
+          <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>90409670000</t>
+          <t>90410990000</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12216,118 +12178,98 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TETRA HOJUELAS GOLDFISH .42OZ · 90409900000</t>
+          <t>D TRIUMPH LATA POLLO ARROZ VEG 13.2OZ · 90412960000</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>90409900000</t>
+          <t>90412960000</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>TRIUMPH</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>TETRA HOJUELAS GOLDFISH 3.53OZ · 90409910000</t>
+          <t>D ZM ALIMENTO EN BLOQUE P TORTUGAS 5 · 93517490000</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>90409910000</t>
+          <t>93517490000</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>ZOO MED</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>TETRA HOJUELAS TROPICAL 0.42OZ · 90409920000</t>
+          <t>ZM CALCIO GDE CON VEGETALES P/AVES · 93503050000</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>90409920000</t>
+          <t>93503050000</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>ZOO MED</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
+          <t>ZM CALCIO PQNO CON VEGETALES P/AVES · 93503060000</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>90410990000</t>
+          <t>93503060000</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>ZOO MED</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>D TRIUMPH LATA POLLO ARROZ VEG 13.2OZ · 90412960000</t>
+          <t>ZM MICRO PELLET P/BETTA 0.12OZ · 93514830000</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>90412960000</t>
+          <t>93514830000</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D135" t="inlineStr">
-        <is>
-          <t>TRIUMPH</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>D ZM ALIMENTO EN BLOQUE P TORTUGAS 5 · 93517490000</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>93517490000</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>1</v>
-      </c>
-      <c r="D136" t="inlineStr">
         <is>
           <t>ZOO MED</t>
         </is>
@@ -12336,94 +12278,34 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ZM CALCIO GDE CON VEGETALES P/AVES · 93503050000</t>
+          <t>Sucursal</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>93503050000</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>10</v>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>ZOO MED</t>
+          <t>MELO &amp; CIA. | SAN VICENTE</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ZM CALCIO PQNO CON VEGETALES P/AVES · 93503060000</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>93503060000</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>2</v>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>ZOO MED</t>
-        </is>
+          <t>Índice</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ZM MICRO PELLET P/BETTA 0.12OZ · 93514830000</t>
+          <t>Inventario al</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>93514830000</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>8</v>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>ZOO MED</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Sucursal</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>MELO &amp; CIA. | SAN VICENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Índice</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Inventario al</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>24.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/20.xlsx
+++ b/plantillas/20.xlsx
@@ -17,36 +17,35 @@
     <definedName name="MARCA_3">Listas!$F$2:$F$3</definedName>
     <definedName name="MARCA_4">Listas!$G$2:$G$2</definedName>
     <definedName name="MARCA_5">Listas!$H$2:$H$3</definedName>
-    <definedName name="MARCA_6">Listas!$I$2:$I$2</definedName>
-    <definedName name="MARCA_7">Listas!$J$2:$J$5</definedName>
-    <definedName name="MARCA_8">Listas!$K$2:$K$2</definedName>
-    <definedName name="MARCA_9">Listas!$L$2:$L$3</definedName>
-    <definedName name="MARCA_10">Listas!$M$2:$M$4</definedName>
-    <definedName name="MARCA_11">Listas!$N$2:$N$6</definedName>
-    <definedName name="MARCA_12">Listas!$O$2:$O$5</definedName>
-    <definedName name="MARCA_13">Listas!$P$2:$P$6</definedName>
-    <definedName name="MARCA_14">Listas!$Q$2:$Q$3</definedName>
+    <definedName name="MARCA_6">Listas!$I$2:$I$5</definedName>
+    <definedName name="MARCA_7">Listas!$J$2:$J$2</definedName>
+    <definedName name="MARCA_8">Listas!$K$2:$K$3</definedName>
+    <definedName name="MARCA_9">Listas!$L$2:$L$4</definedName>
+    <definedName name="MARCA_10">Listas!$M$2:$M$9</definedName>
+    <definedName name="MARCA_11">Listas!$N$2:$N$5</definedName>
+    <definedName name="MARCA_12">Listas!$O$2:$O$6</definedName>
+    <definedName name="MARCA_13">Listas!$P$2:$P$3</definedName>
+    <definedName name="MARCA_14">Listas!$Q$2:$Q$2</definedName>
     <definedName name="MARCA_15">Listas!$R$2:$R$2</definedName>
-    <definedName name="MARCA_16">Listas!$S$2:$S$2</definedName>
+    <definedName name="MARCA_16">Listas!$S$2:$S$5</definedName>
     <definedName name="MARCA_17">Listas!$T$2:$T$5</definedName>
-    <definedName name="MARCA_18">Listas!$U$2:$U$5</definedName>
-    <definedName name="MARCA_19">Listas!$V$2:$V$19</definedName>
-    <definedName name="MARCA_20">Listas!$W$2:$W$18</definedName>
-    <definedName name="MARCA_21">Listas!$X$2:$X$2</definedName>
-    <definedName name="MARCA_22">Listas!$Y$2:$Y$7</definedName>
-    <definedName name="MARCA_23">Listas!$Z$2:$Z$5</definedName>
-    <definedName name="MARCA_24">Listas!$AA$2:$AA$5</definedName>
-    <definedName name="MARCA_25">Listas!$AB$2:$AB$8</definedName>
+    <definedName name="MARCA_18">Listas!$U$2:$U$19</definedName>
+    <definedName name="MARCA_19">Listas!$V$2:$V$18</definedName>
+    <definedName name="MARCA_20">Listas!$W$2:$W$2</definedName>
+    <definedName name="MARCA_21">Listas!$X$2:$X$7</definedName>
+    <definedName name="MARCA_22">Listas!$Y$2:$Y$5</definedName>
+    <definedName name="MARCA_23">Listas!$Z$2:$Z$6</definedName>
+    <definedName name="MARCA_24">Listas!$AA$2:$AA$8</definedName>
+    <definedName name="MARCA_25">Listas!$AB$2:$AB$2</definedName>
     <definedName name="MARCA_26">Listas!$AC$2:$AC$2</definedName>
-    <definedName name="MARCA_27">Listas!$AD$2:$AD$2</definedName>
-    <definedName name="MARCA_28">Listas!$AE$2:$AE$3</definedName>
-    <definedName name="MARCA_29">Listas!$AF$2:$AF$5</definedName>
-    <definedName name="MARCA_30">Listas!$AG$2:$AG$10</definedName>
-    <definedName name="MARCA_31">Listas!$AH$2:$AH$9</definedName>
-    <definedName name="MARCA_32">Listas!$AI$2:$AI$2</definedName>
-    <definedName name="MARCA_33">Listas!$AJ$2:$AJ$5</definedName>
+    <definedName name="MARCA_27">Listas!$AD$2:$AD$3</definedName>
+    <definedName name="MARCA_28">Listas!$AE$2:$AE$5</definedName>
+    <definedName name="MARCA_29">Listas!$AF$2:$AF$10</definedName>
+    <definedName name="MARCA_30">Listas!$AG$2:$AG$9</definedName>
+    <definedName name="MARCA_31">Listas!$AH$2:$AH$2</definedName>
+    <definedName name="MARCA_32">Listas!$AI$2:$AI$5</definedName>
     <definedName name="MESES">Listas!$C$2:$C$5</definedName>
-    <definedName name="MARCAS">Listas!$A$2:$A$34</definedName>
+    <definedName name="MARCAS">Listas!$A$2:$A$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -651,11 +650,11 @@
       <c r="A3" s="5" t="n"/>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B3,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B3,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D3" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B3,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B3,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E3" s="8" t="n"/>
@@ -675,11 +674,11 @@
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B4,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B4,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D4" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B4,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B4,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E4" s="8" t="n"/>
@@ -699,11 +698,11 @@
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B5,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B5,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B5,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B5,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E5" s="8" t="n"/>
@@ -723,11 +722,11 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B6,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B6,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B6,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B6,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E6" s="8" t="n"/>
@@ -742,11 +741,11 @@
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B7,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B7,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B7,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B7,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -761,11 +760,11 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B8,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B8,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B8,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B8,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E8" s="8" t="n"/>
@@ -780,11 +779,11 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B9,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B9,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B9,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B9,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E9" s="8" t="n"/>
@@ -799,11 +798,11 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B10,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B10,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B10,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B10,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E10" s="8" t="n"/>
@@ -818,11 +817,11 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B11,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B11,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B11,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B11,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E11" s="8" t="n"/>
@@ -837,11 +836,11 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B12,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B12,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B12,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B12,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -856,11 +855,11 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B13,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B13,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B13,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B13,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E13" s="8" t="n"/>
@@ -875,11 +874,11 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B14,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B14,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B14,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B14,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E14" s="8" t="n"/>
@@ -894,11 +893,11 @@
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B15,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B15,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B15,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B15,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E15" s="8" t="n"/>
@@ -913,11 +912,11 @@
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B16,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B16,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B16,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B16,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E16" s="8" t="n"/>
@@ -932,11 +931,11 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B17,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B17,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B17,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B17,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E17" s="8" t="n"/>
@@ -951,11 +950,11 @@
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B18,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B18,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B18,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B18,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E18" s="8" t="n"/>
@@ -970,11 +969,11 @@
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B19,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B19,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B19,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B19,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E19" s="8" t="n"/>
@@ -989,11 +988,11 @@
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B20,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B20,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D20" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B20,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B20,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -1008,11 +1007,11 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B21,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B21,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B21,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B21,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E21" s="8" t="n"/>
@@ -1027,11 +1026,11 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B22,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B22,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B22,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B22,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E22" s="8" t="n"/>
@@ -1046,11 +1045,11 @@
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B23,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B23,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B23,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B23,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E23" s="8" t="n"/>
@@ -1065,11 +1064,11 @@
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B24,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B24,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B24,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B24,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E24" s="8" t="n"/>
@@ -1084,11 +1083,11 @@
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B25,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B25,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B25,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B25,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="8" t="n"/>
@@ -1103,11 +1102,11 @@
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B26,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B26,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B26,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B26,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -1122,11 +1121,11 @@
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B27,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B27,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B27,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B27,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -1141,11 +1140,11 @@
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B28,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B28,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B28,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B28,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E28" s="8" t="n"/>
@@ -1160,11 +1159,11 @@
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B29,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B29,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B29,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B29,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -1179,11 +1178,11 @@
       <c r="A30" s="5" t="n"/>
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B30,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B30,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B30,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B30,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -1198,11 +1197,11 @@
       <c r="A31" s="5" t="n"/>
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B31,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B31,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B31,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B31,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -1217,11 +1216,11 @@
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B32,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B32,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B32,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B32,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -1236,11 +1235,11 @@
       <c r="A33" s="5" t="n"/>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B33,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B33,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B33,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B33,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -1255,11 +1254,11 @@
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B34,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B34,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B34,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B34,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -1274,11 +1273,11 @@
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B35,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B35,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B35,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B35,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -1293,11 +1292,11 @@
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B36,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B36,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B36,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B36,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -1312,11 +1311,11 @@
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B37,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B37,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B37,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B37,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -1331,11 +1330,11 @@
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B38,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B38,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B38,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B38,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E38" s="8" t="n"/>
@@ -1350,11 +1349,11 @@
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B39,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B39,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B39,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B39,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -1369,11 +1368,11 @@
       <c r="A40" s="5" t="n"/>
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B40,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B40,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B40,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B40,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E40" s="8" t="n"/>
@@ -1388,11 +1387,11 @@
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B41,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B41,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B41,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B41,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -1407,11 +1406,11 @@
       <c r="A42" s="5" t="n"/>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B42,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B42,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B42,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B42,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -1426,11 +1425,11 @@
       <c r="A43" s="5" t="n"/>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B43,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B43,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B43,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B43,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -1445,11 +1444,11 @@
       <c r="A44" s="5" t="n"/>
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B44,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B44,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B44,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B44,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -1464,11 +1463,11 @@
       <c r="A45" s="5" t="n"/>
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B45,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B45,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B45,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B45,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -1483,11 +1482,11 @@
       <c r="A46" s="5" t="n"/>
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B46,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B46,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B46,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B46,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -1502,11 +1501,11 @@
       <c r="A47" s="5" t="n"/>
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B47,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B47,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B47,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B47,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -1521,11 +1520,11 @@
       <c r="A48" s="5" t="n"/>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B48,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B48,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B48,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B48,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -1540,11 +1539,11 @@
       <c r="A49" s="5" t="n"/>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B49,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B49,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B49,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B49,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -1559,11 +1558,11 @@
       <c r="A50" s="5" t="n"/>
       <c r="B50" s="5" t="n"/>
       <c r="C50" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B50,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B50,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B50,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B50,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -1578,11 +1577,11 @@
       <c r="A51" s="5" t="n"/>
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B51,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B51,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B51,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B51,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E51" s="8" t="n"/>
@@ -1597,11 +1596,11 @@
       <c r="A52" s="5" t="n"/>
       <c r="B52" s="5" t="n"/>
       <c r="C52" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B52,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B52,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D52" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B52,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B52,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E52" s="8" t="n"/>
@@ -1616,11 +1615,11 @@
       <c r="A53" s="5" t="n"/>
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B53,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B53,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D53" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B53,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B53,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E53" s="8" t="n"/>
@@ -1635,11 +1634,11 @@
       <c r="A54" s="5" t="n"/>
       <c r="B54" s="5" t="n"/>
       <c r="C54" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B54,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B54,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D54" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B54,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B54,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E54" s="8" t="n"/>
@@ -1654,11 +1653,11 @@
       <c r="A55" s="5" t="n"/>
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B55,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B55,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D55" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B55,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B55,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -1673,11 +1672,11 @@
       <c r="A56" s="5" t="n"/>
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B56,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B56,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D56" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B56,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B56,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E56" s="8" t="n"/>
@@ -1692,11 +1691,11 @@
       <c r="A57" s="5" t="n"/>
       <c r="B57" s="5" t="n"/>
       <c r="C57" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B57,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B57,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D57" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B57,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B57,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E57" s="8" t="n"/>
@@ -1711,11 +1710,11 @@
       <c r="A58" s="5" t="n"/>
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B58,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B58,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D58" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B58,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B58,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -1730,11 +1729,11 @@
       <c r="A59" s="5" t="n"/>
       <c r="B59" s="5" t="n"/>
       <c r="C59" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B59,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B59,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D59" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B59,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B59,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -1749,11 +1748,11 @@
       <c r="A60" s="5" t="n"/>
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B60,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B60,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D60" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B60,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B60,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -1768,11 +1767,11 @@
       <c r="A61" s="5" t="n"/>
       <c r="B61" s="5" t="n"/>
       <c r="C61" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B61,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B61,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D61" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B61,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B61,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -1787,11 +1786,11 @@
       <c r="A62" s="5" t="n"/>
       <c r="B62" s="5" t="n"/>
       <c r="C62" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B62,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B62,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D62" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B62,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B62,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E62" s="8" t="n"/>
@@ -1806,11 +1805,11 @@
       <c r="A63" s="5" t="n"/>
       <c r="B63" s="5" t="n"/>
       <c r="C63" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B63,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B63,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D63" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B63,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B63,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -1825,11 +1824,11 @@
       <c r="A64" s="5" t="n"/>
       <c r="B64" s="5" t="n"/>
       <c r="C64" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B64,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B64,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D64" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B64,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B64,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -1844,11 +1843,11 @@
       <c r="A65" s="5" t="n"/>
       <c r="B65" s="5" t="n"/>
       <c r="C65" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B65,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B65,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D65" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B65,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B65,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -1863,11 +1862,11 @@
       <c r="A66" s="5" t="n"/>
       <c r="B66" s="5" t="n"/>
       <c r="C66" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B66,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B66,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D66" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B66,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B66,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E66" s="8" t="n"/>
@@ -1882,11 +1881,11 @@
       <c r="A67" s="5" t="n"/>
       <c r="B67" s="5" t="n"/>
       <c r="C67" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B67,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B67,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D67" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B67,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B67,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E67" s="8" t="n"/>
@@ -1901,11 +1900,11 @@
       <c r="A68" s="5" t="n"/>
       <c r="B68" s="5" t="n"/>
       <c r="C68" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B68,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B68,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D68" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B68,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B68,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -1920,11 +1919,11 @@
       <c r="A69" s="5" t="n"/>
       <c r="B69" s="5" t="n"/>
       <c r="C69" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B69,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B69,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D69" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B69,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B69,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -1939,11 +1938,11 @@
       <c r="A70" s="5" t="n"/>
       <c r="B70" s="5" t="n"/>
       <c r="C70" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B70,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B70,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D70" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B70,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B70,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -1958,11 +1957,11 @@
       <c r="A71" s="5" t="n"/>
       <c r="B71" s="5" t="n"/>
       <c r="C71" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B71,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B71,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D71" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B71,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B71,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E71" s="8" t="n"/>
@@ -1977,11 +1976,11 @@
       <c r="A72" s="5" t="n"/>
       <c r="B72" s="5" t="n"/>
       <c r="C72" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B72,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B72,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D72" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B72,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B72,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -1996,11 +1995,11 @@
       <c r="A73" s="5" t="n"/>
       <c r="B73" s="5" t="n"/>
       <c r="C73" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B73,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B73,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D73" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B73,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B73,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E73" s="8" t="n"/>
@@ -2015,11 +2014,11 @@
       <c r="A74" s="5" t="n"/>
       <c r="B74" s="5" t="n"/>
       <c r="C74" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B74,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B74,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D74" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B74,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B74,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -2034,11 +2033,11 @@
       <c r="A75" s="5" t="n"/>
       <c r="B75" s="5" t="n"/>
       <c r="C75" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B75,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B75,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D75" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B75,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B75,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -2053,11 +2052,11 @@
       <c r="A76" s="5" t="n"/>
       <c r="B76" s="5" t="n"/>
       <c r="C76" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B76,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B76,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D76" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B76,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B76,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E76" s="8" t="n"/>
@@ -2072,11 +2071,11 @@
       <c r="A77" s="5" t="n"/>
       <c r="B77" s="5" t="n"/>
       <c r="C77" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B77,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B77,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D77" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B77,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B77,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -2091,11 +2090,11 @@
       <c r="A78" s="5" t="n"/>
       <c r="B78" s="5" t="n"/>
       <c r="C78" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B78,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B78,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D78" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B78,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B78,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E78" s="8" t="n"/>
@@ -2110,11 +2109,11 @@
       <c r="A79" s="5" t="n"/>
       <c r="B79" s="5" t="n"/>
       <c r="C79" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B79,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B79,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D79" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B79,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B79,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E79" s="8" t="n"/>
@@ -2129,11 +2128,11 @@
       <c r="A80" s="5" t="n"/>
       <c r="B80" s="5" t="n"/>
       <c r="C80" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B80,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B80,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D80" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B80,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B80,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E80" s="8" t="n"/>
@@ -2148,11 +2147,11 @@
       <c r="A81" s="5" t="n"/>
       <c r="B81" s="5" t="n"/>
       <c r="C81" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B81,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B81,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D81" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B81,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B81,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E81" s="8" t="n"/>
@@ -2167,11 +2166,11 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="5" t="n"/>
       <c r="C82" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B82,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B82,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D82" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B82,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B82,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -2186,11 +2185,11 @@
       <c r="A83" s="5" t="n"/>
       <c r="B83" s="5" t="n"/>
       <c r="C83" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B83,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B83,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D83" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B83,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B83,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -2205,11 +2204,11 @@
       <c r="A84" s="5" t="n"/>
       <c r="B84" s="5" t="n"/>
       <c r="C84" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B84,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B84,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D84" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B84,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B84,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -2224,11 +2223,11 @@
       <c r="A85" s="5" t="n"/>
       <c r="B85" s="5" t="n"/>
       <c r="C85" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B85,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B85,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D85" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B85,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B85,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -2243,11 +2242,11 @@
       <c r="A86" s="5" t="n"/>
       <c r="B86" s="5" t="n"/>
       <c r="C86" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B86,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B86,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D86" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B86,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B86,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -2262,11 +2261,11 @@
       <c r="A87" s="5" t="n"/>
       <c r="B87" s="5" t="n"/>
       <c r="C87" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B87,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B87,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D87" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B87,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B87,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -2281,11 +2280,11 @@
       <c r="A88" s="5" t="n"/>
       <c r="B88" s="5" t="n"/>
       <c r="C88" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B88,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B88,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D88" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B88,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B88,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E88" s="8" t="n"/>
@@ -2300,11 +2299,11 @@
       <c r="A89" s="5" t="n"/>
       <c r="B89" s="5" t="n"/>
       <c r="C89" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B89,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B89,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D89" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B89,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B89,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E89" s="8" t="n"/>
@@ -2319,11 +2318,11 @@
       <c r="A90" s="5" t="n"/>
       <c r="B90" s="5" t="n"/>
       <c r="C90" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B90,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B90,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D90" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B90,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B90,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E90" s="8" t="n"/>
@@ -2338,11 +2337,11 @@
       <c r="A91" s="5" t="n"/>
       <c r="B91" s="5" t="n"/>
       <c r="C91" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B91,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B91,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D91" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B91,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B91,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E91" s="8" t="n"/>
@@ -2357,11 +2356,11 @@
       <c r="A92" s="5" t="n"/>
       <c r="B92" s="5" t="n"/>
       <c r="C92" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B92,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B92,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D92" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B92,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B92,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -2376,11 +2375,11 @@
       <c r="A93" s="5" t="n"/>
       <c r="B93" s="5" t="n"/>
       <c r="C93" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B93,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B93,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D93" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B93,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B93,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -2395,11 +2394,11 @@
       <c r="A94" s="5" t="n"/>
       <c r="B94" s="5" t="n"/>
       <c r="C94" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B94,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B94,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D94" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B94,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B94,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -2414,11 +2413,11 @@
       <c r="A95" s="5" t="n"/>
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B95,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B95,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D95" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B95,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B95,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -2433,11 +2432,11 @@
       <c r="A96" s="5" t="n"/>
       <c r="B96" s="5" t="n"/>
       <c r="C96" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B96,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B96,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D96" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B96,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B96,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -2452,11 +2451,11 @@
       <c r="A97" s="5" t="n"/>
       <c r="B97" s="5" t="n"/>
       <c r="C97" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B97,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B97,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D97" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B97,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B97,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -2471,11 +2470,11 @@
       <c r="A98" s="5" t="n"/>
       <c r="B98" s="5" t="n"/>
       <c r="C98" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B98,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B98,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D98" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B98,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B98,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E98" s="8" t="n"/>
@@ -2490,11 +2489,11 @@
       <c r="A99" s="5" t="n"/>
       <c r="B99" s="5" t="n"/>
       <c r="C99" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B99,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B99,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D99" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B99,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B99,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E99" s="8" t="n"/>
@@ -2509,11 +2508,11 @@
       <c r="A100" s="5" t="n"/>
       <c r="B100" s="5" t="n"/>
       <c r="C100" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B100,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B100,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D100" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B100,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B100,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E100" s="8" t="n"/>
@@ -2528,11 +2527,11 @@
       <c r="A101" s="5" t="n"/>
       <c r="B101" s="5" t="n"/>
       <c r="C101" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B101,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B101,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D101" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B101,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B101,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -2547,11 +2546,11 @@
       <c r="A102" s="5" t="n"/>
       <c r="B102" s="5" t="n"/>
       <c r="C102" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B102,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B102,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D102" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B102,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B102,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -2566,11 +2565,11 @@
       <c r="A103" s="5" t="n"/>
       <c r="B103" s="5" t="n"/>
       <c r="C103" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B103,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B103,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D103" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B103,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B103,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E103" s="8" t="n"/>
@@ -2585,11 +2584,11 @@
       <c r="A104" s="5" t="n"/>
       <c r="B104" s="5" t="n"/>
       <c r="C104" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B104,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B104,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D104" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B104,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B104,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E104" s="8" t="n"/>
@@ -2604,11 +2603,11 @@
       <c r="A105" s="5" t="n"/>
       <c r="B105" s="5" t="n"/>
       <c r="C105" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B105,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B105,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D105" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B105,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B105,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E105" s="8" t="n"/>
@@ -2623,11 +2622,11 @@
       <c r="A106" s="5" t="n"/>
       <c r="B106" s="5" t="n"/>
       <c r="C106" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B106,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B106,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D106" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B106,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B106,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E106" s="8" t="n"/>
@@ -2642,11 +2641,11 @@
       <c r="A107" s="5" t="n"/>
       <c r="B107" s="5" t="n"/>
       <c r="C107" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B107,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B107,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D107" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B107,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B107,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E107" s="8" t="n"/>
@@ -2661,11 +2660,11 @@
       <c r="A108" s="5" t="n"/>
       <c r="B108" s="5" t="n"/>
       <c r="C108" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B108,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B108,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D108" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B108,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B108,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E108" s="8" t="n"/>
@@ -2680,11 +2679,11 @@
       <c r="A109" s="5" t="n"/>
       <c r="B109" s="5" t="n"/>
       <c r="C109" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B109,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B109,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D109" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B109,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B109,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E109" s="8" t="n"/>
@@ -2699,11 +2698,11 @@
       <c r="A110" s="5" t="n"/>
       <c r="B110" s="5" t="n"/>
       <c r="C110" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B110,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B110,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D110" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B110,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B110,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E110" s="8" t="n"/>
@@ -2718,11 +2717,11 @@
       <c r="A111" s="5" t="n"/>
       <c r="B111" s="5" t="n"/>
       <c r="C111" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B111,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B111,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D111" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B111,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B111,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E111" s="8" t="n"/>
@@ -2737,11 +2736,11 @@
       <c r="A112" s="5" t="n"/>
       <c r="B112" s="5" t="n"/>
       <c r="C112" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B112,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B112,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D112" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B112,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B112,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E112" s="8" t="n"/>
@@ -2756,11 +2755,11 @@
       <c r="A113" s="5" t="n"/>
       <c r="B113" s="5" t="n"/>
       <c r="C113" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B113,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B113,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D113" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B113,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B113,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E113" s="8" t="n"/>
@@ -2775,11 +2774,11 @@
       <c r="A114" s="5" t="n"/>
       <c r="B114" s="5" t="n"/>
       <c r="C114" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B114,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B114,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D114" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B114,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B114,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E114" s="8" t="n"/>
@@ -2794,11 +2793,11 @@
       <c r="A115" s="5" t="n"/>
       <c r="B115" s="5" t="n"/>
       <c r="C115" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B115,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B115,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D115" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B115,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B115,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E115" s="8" t="n"/>
@@ -2813,11 +2812,11 @@
       <c r="A116" s="5" t="n"/>
       <c r="B116" s="5" t="n"/>
       <c r="C116" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B116,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B116,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D116" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B116,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B116,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E116" s="8" t="n"/>
@@ -2832,11 +2831,11 @@
       <c r="A117" s="5" t="n"/>
       <c r="B117" s="5" t="n"/>
       <c r="C117" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B117,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B117,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D117" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B117,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B117,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E117" s="8" t="n"/>
@@ -2851,11 +2850,11 @@
       <c r="A118" s="5" t="n"/>
       <c r="B118" s="5" t="n"/>
       <c r="C118" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B118,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B118,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D118" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B118,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B118,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E118" s="8" t="n"/>
@@ -2870,11 +2869,11 @@
       <c r="A119" s="5" t="n"/>
       <c r="B119" s="5" t="n"/>
       <c r="C119" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B119,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B119,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D119" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B119,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B119,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E119" s="8" t="n"/>
@@ -2889,11 +2888,11 @@
       <c r="A120" s="5" t="n"/>
       <c r="B120" s="5" t="n"/>
       <c r="C120" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B120,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B120,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D120" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B120,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B120,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E120" s="8" t="n"/>
@@ -2908,11 +2907,11 @@
       <c r="A121" s="5" t="n"/>
       <c r="B121" s="5" t="n"/>
       <c r="C121" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B121,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B121,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D121" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B121,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B121,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E121" s="8" t="n"/>
@@ -2927,11 +2926,11 @@
       <c r="A122" s="5" t="n"/>
       <c r="B122" s="5" t="n"/>
       <c r="C122" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B122,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B122,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D122" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B122,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B122,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E122" s="8" t="n"/>
@@ -2946,11 +2945,11 @@
       <c r="A123" s="5" t="n"/>
       <c r="B123" s="5" t="n"/>
       <c r="C123" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B123,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B123,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D123" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B123,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B123,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E123" s="8" t="n"/>
@@ -2965,11 +2964,11 @@
       <c r="A124" s="5" t="n"/>
       <c r="B124" s="5" t="n"/>
       <c r="C124" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B124,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B124,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D124" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B124,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B124,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E124" s="8" t="n"/>
@@ -2984,11 +2983,11 @@
       <c r="A125" s="5" t="n"/>
       <c r="B125" s="5" t="n"/>
       <c r="C125" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B125,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B125,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D125" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B125,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B125,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E125" s="8" t="n"/>
@@ -3003,11 +3002,11 @@
       <c r="A126" s="5" t="n"/>
       <c r="B126" s="5" t="n"/>
       <c r="C126" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B126,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B126,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D126" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B126,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B126,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E126" s="8" t="n"/>
@@ -3022,11 +3021,11 @@
       <c r="A127" s="5" t="n"/>
       <c r="B127" s="5" t="n"/>
       <c r="C127" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B127,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B127,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D127" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B127,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B127,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E127" s="8" t="n"/>
@@ -3041,11 +3040,11 @@
       <c r="A128" s="5" t="n"/>
       <c r="B128" s="5" t="n"/>
       <c r="C128" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B128,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B128,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D128" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B128,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B128,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E128" s="8" t="n"/>
@@ -3060,11 +3059,11 @@
       <c r="A129" s="5" t="n"/>
       <c r="B129" s="5" t="n"/>
       <c r="C129" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B129,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B129,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D129" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B129,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B129,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E129" s="8" t="n"/>
@@ -3079,11 +3078,11 @@
       <c r="A130" s="5" t="n"/>
       <c r="B130" s="5" t="n"/>
       <c r="C130" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B130,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B130,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D130" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B130,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B130,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E130" s="8" t="n"/>
@@ -3098,11 +3097,11 @@
       <c r="A131" s="5" t="n"/>
       <c r="B131" s="5" t="n"/>
       <c r="C131" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B131,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B131,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D131" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B131,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B131,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E131" s="8" t="n"/>
@@ -3117,11 +3116,11 @@
       <c r="A132" s="5" t="n"/>
       <c r="B132" s="5" t="n"/>
       <c r="C132" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B132,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B132,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D132" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B132,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B132,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E132" s="8" t="n"/>
@@ -3136,11 +3135,11 @@
       <c r="A133" s="5" t="n"/>
       <c r="B133" s="5" t="n"/>
       <c r="C133" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B133,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B133,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D133" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B133,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B133,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E133" s="8" t="n"/>
@@ -3155,11 +3154,11 @@
       <c r="A134" s="5" t="n"/>
       <c r="B134" s="5" t="n"/>
       <c r="C134" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B134,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B134,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D134" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B134,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B134,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E134" s="8" t="n"/>
@@ -3174,11 +3173,11 @@
       <c r="A135" s="5" t="n"/>
       <c r="B135" s="5" t="n"/>
       <c r="C135" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B135,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B135,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D135" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B135,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B135,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E135" s="8" t="n"/>
@@ -3193,11 +3192,11 @@
       <c r="A136" s="5" t="n"/>
       <c r="B136" s="5" t="n"/>
       <c r="C136" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B136,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B136,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D136" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B136,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B136,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E136" s="8" t="n"/>
@@ -3212,11 +3211,11 @@
       <c r="A137" s="5" t="n"/>
       <c r="B137" s="5" t="n"/>
       <c r="C137" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B137,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B137,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D137" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B137,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B137,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E137" s="8" t="n"/>
@@ -3231,11 +3230,11 @@
       <c r="A138" s="5" t="n"/>
       <c r="B138" s="5" t="n"/>
       <c r="C138" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B138,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B138,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D138" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B138,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B138,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E138" s="8" t="n"/>
@@ -3250,11 +3249,11 @@
       <c r="A139" s="5" t="n"/>
       <c r="B139" s="5" t="n"/>
       <c r="C139" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B139,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B139,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D139" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B139,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B139,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E139" s="8" t="n"/>
@@ -3269,11 +3268,11 @@
       <c r="A140" s="5" t="n"/>
       <c r="B140" s="5" t="n"/>
       <c r="C140" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B140,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B140,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D140" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B140,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B140,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E140" s="8" t="n"/>
@@ -3288,11 +3287,11 @@
       <c r="A141" s="5" t="n"/>
       <c r="B141" s="5" t="n"/>
       <c r="C141" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B141,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B141,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D141" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B141,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B141,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E141" s="8" t="n"/>
@@ -3307,11 +3306,11 @@
       <c r="A142" s="5" t="n"/>
       <c r="B142" s="5" t="n"/>
       <c r="C142" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B142,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B142,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D142" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B142,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B142,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E142" s="8" t="n"/>
@@ -3326,11 +3325,11 @@
       <c r="A143" s="5" t="n"/>
       <c r="B143" s="5" t="n"/>
       <c r="C143" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B143,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B143,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D143" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B143,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B143,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E143" s="8" t="n"/>
@@ -3345,11 +3344,11 @@
       <c r="A144" s="5" t="n"/>
       <c r="B144" s="5" t="n"/>
       <c r="C144" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B144,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B144,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D144" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B144,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B144,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E144" s="8" t="n"/>
@@ -3364,11 +3363,11 @@
       <c r="A145" s="5" t="n"/>
       <c r="B145" s="5" t="n"/>
       <c r="C145" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B145,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B145,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D145" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B145,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B145,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E145" s="8" t="n"/>
@@ -3383,11 +3382,11 @@
       <c r="A146" s="5" t="n"/>
       <c r="B146" s="5" t="n"/>
       <c r="C146" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B146,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B146,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D146" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B146,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B146,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E146" s="8" t="n"/>
@@ -3402,11 +3401,11 @@
       <c r="A147" s="5" t="n"/>
       <c r="B147" s="5" t="n"/>
       <c r="C147" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B147,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B147,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D147" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B147,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B147,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E147" s="8" t="n"/>
@@ -3421,11 +3420,11 @@
       <c r="A148" s="5" t="n"/>
       <c r="B148" s="5" t="n"/>
       <c r="C148" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B148,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B148,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D148" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B148,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B148,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E148" s="8" t="n"/>
@@ -3440,11 +3439,11 @@
       <c r="A149" s="5" t="n"/>
       <c r="B149" s="5" t="n"/>
       <c r="C149" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B149,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B149,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D149" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B149,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B149,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E149" s="8" t="n"/>
@@ -3459,11 +3458,11 @@
       <c r="A150" s="5" t="n"/>
       <c r="B150" s="5" t="n"/>
       <c r="C150" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B150,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B150,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D150" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B150,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B150,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E150" s="8" t="n"/>
@@ -3478,11 +3477,11 @@
       <c r="A151" s="5" t="n"/>
       <c r="B151" s="5" t="n"/>
       <c r="C151" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B151,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B151,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D151" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B151,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B151,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E151" s="8" t="n"/>
@@ -3497,11 +3496,11 @@
       <c r="A152" s="5" t="n"/>
       <c r="B152" s="5" t="n"/>
       <c r="C152" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B152,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B152,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D152" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B152,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B152,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E152" s="8" t="n"/>
@@ -3516,11 +3515,11 @@
       <c r="A153" s="5" t="n"/>
       <c r="B153" s="5" t="n"/>
       <c r="C153" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B153,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B153,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D153" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B153,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B153,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E153" s="8" t="n"/>
@@ -3535,11 +3534,11 @@
       <c r="A154" s="5" t="n"/>
       <c r="B154" s="5" t="n"/>
       <c r="C154" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B154,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B154,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D154" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B154,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B154,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E154" s="8" t="n"/>
@@ -3554,11 +3553,11 @@
       <c r="A155" s="5" t="n"/>
       <c r="B155" s="5" t="n"/>
       <c r="C155" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B155,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B155,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D155" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B155,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B155,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E155" s="8" t="n"/>
@@ -3573,11 +3572,11 @@
       <c r="A156" s="5" t="n"/>
       <c r="B156" s="5" t="n"/>
       <c r="C156" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B156,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B156,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D156" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B156,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B156,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E156" s="8" t="n"/>
@@ -3592,11 +3591,11 @@
       <c r="A157" s="5" t="n"/>
       <c r="B157" s="5" t="n"/>
       <c r="C157" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B157,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B157,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D157" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B157,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B157,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E157" s="8" t="n"/>
@@ -3611,11 +3610,11 @@
       <c r="A158" s="5" t="n"/>
       <c r="B158" s="5" t="n"/>
       <c r="C158" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B158,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B158,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D158" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B158,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B158,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E158" s="8" t="n"/>
@@ -3630,11 +3629,11 @@
       <c r="A159" s="5" t="n"/>
       <c r="B159" s="5" t="n"/>
       <c r="C159" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B159,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B159,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D159" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B159,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B159,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E159" s="8" t="n"/>
@@ -3649,11 +3648,11 @@
       <c r="A160" s="5" t="n"/>
       <c r="B160" s="5" t="n"/>
       <c r="C160" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B160,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B160,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D160" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B160,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B160,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E160" s="8" t="n"/>
@@ -3668,11 +3667,11 @@
       <c r="A161" s="5" t="n"/>
       <c r="B161" s="5" t="n"/>
       <c r="C161" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B161,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B161,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D161" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B161,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B161,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E161" s="8" t="n"/>
@@ -3687,11 +3686,11 @@
       <c r="A162" s="5" t="n"/>
       <c r="B162" s="5" t="n"/>
       <c r="C162" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B162,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B162,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D162" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B162,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B162,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E162" s="8" t="n"/>
@@ -3706,11 +3705,11 @@
       <c r="A163" s="5" t="n"/>
       <c r="B163" s="5" t="n"/>
       <c r="C163" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B163,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B163,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D163" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B163,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B163,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E163" s="8" t="n"/>
@@ -3725,11 +3724,11 @@
       <c r="A164" s="5" t="n"/>
       <c r="B164" s="5" t="n"/>
       <c r="C164" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B164,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B164,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D164" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B164,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B164,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E164" s="8" t="n"/>
@@ -3744,11 +3743,11 @@
       <c r="A165" s="5" t="n"/>
       <c r="B165" s="5" t="n"/>
       <c r="C165" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B165,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B165,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D165" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B165,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B165,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E165" s="8" t="n"/>
@@ -3763,11 +3762,11 @@
       <c r="A166" s="5" t="n"/>
       <c r="B166" s="5" t="n"/>
       <c r="C166" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B166,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B166,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D166" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B166,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B166,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E166" s="8" t="n"/>
@@ -3782,11 +3781,11 @@
       <c r="A167" s="5" t="n"/>
       <c r="B167" s="5" t="n"/>
       <c r="C167" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B167,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B167,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D167" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B167,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B167,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E167" s="8" t="n"/>
@@ -3801,11 +3800,11 @@
       <c r="A168" s="5" t="n"/>
       <c r="B168" s="5" t="n"/>
       <c r="C168" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B168,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B168,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D168" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B168,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B168,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E168" s="8" t="n"/>
@@ -3820,11 +3819,11 @@
       <c r="A169" s="5" t="n"/>
       <c r="B169" s="5" t="n"/>
       <c r="C169" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B169,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B169,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D169" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B169,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B169,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E169" s="8" t="n"/>
@@ -3839,11 +3838,11 @@
       <c r="A170" s="5" t="n"/>
       <c r="B170" s="5" t="n"/>
       <c r="C170" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B170,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B170,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D170" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B170,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B170,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E170" s="8" t="n"/>
@@ -3858,11 +3857,11 @@
       <c r="A171" s="5" t="n"/>
       <c r="B171" s="5" t="n"/>
       <c r="C171" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B171,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B171,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D171" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B171,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B171,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E171" s="8" t="n"/>
@@ -3877,11 +3876,11 @@
       <c r="A172" s="5" t="n"/>
       <c r="B172" s="5" t="n"/>
       <c r="C172" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B172,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B172,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D172" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B172,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B172,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E172" s="8" t="n"/>
@@ -3896,11 +3895,11 @@
       <c r="A173" s="5" t="n"/>
       <c r="B173" s="5" t="n"/>
       <c r="C173" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B173,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B173,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D173" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B173,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B173,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E173" s="8" t="n"/>
@@ -3915,11 +3914,11 @@
       <c r="A174" s="5" t="n"/>
       <c r="B174" s="5" t="n"/>
       <c r="C174" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B174,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B174,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D174" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B174,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B174,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E174" s="8" t="n"/>
@@ -3934,11 +3933,11 @@
       <c r="A175" s="5" t="n"/>
       <c r="B175" s="5" t="n"/>
       <c r="C175" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B175,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B175,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D175" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B175,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B175,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E175" s="8" t="n"/>
@@ -3953,11 +3952,11 @@
       <c r="A176" s="5" t="n"/>
       <c r="B176" s="5" t="n"/>
       <c r="C176" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B176,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B176,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D176" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B176,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B176,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E176" s="8" t="n"/>
@@ -3972,11 +3971,11 @@
       <c r="A177" s="5" t="n"/>
       <c r="B177" s="5" t="n"/>
       <c r="C177" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B177,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B177,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D177" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B177,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B177,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E177" s="8" t="n"/>
@@ -3991,11 +3990,11 @@
       <c r="A178" s="5" t="n"/>
       <c r="B178" s="5" t="n"/>
       <c r="C178" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B178,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B178,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D178" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B178,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B178,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E178" s="8" t="n"/>
@@ -4010,11 +4009,11 @@
       <c r="A179" s="5" t="n"/>
       <c r="B179" s="5" t="n"/>
       <c r="C179" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B179,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B179,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D179" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B179,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B179,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E179" s="8" t="n"/>
@@ -4029,11 +4028,11 @@
       <c r="A180" s="5" t="n"/>
       <c r="B180" s="5" t="n"/>
       <c r="C180" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B180,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B180,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D180" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B180,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B180,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E180" s="8" t="n"/>
@@ -4048,11 +4047,11 @@
       <c r="A181" s="5" t="n"/>
       <c r="B181" s="5" t="n"/>
       <c r="C181" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B181,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B181,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D181" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B181,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B181,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E181" s="8" t="n"/>
@@ -4067,11 +4066,11 @@
       <c r="A182" s="5" t="n"/>
       <c r="B182" s="5" t="n"/>
       <c r="C182" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B182,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B182,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D182" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B182,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B182,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E182" s="8" t="n"/>
@@ -4086,11 +4085,11 @@
       <c r="A183" s="5" t="n"/>
       <c r="B183" s="5" t="n"/>
       <c r="C183" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B183,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B183,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D183" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B183,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B183,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E183" s="8" t="n"/>
@@ -4105,11 +4104,11 @@
       <c r="A184" s="5" t="n"/>
       <c r="B184" s="5" t="n"/>
       <c r="C184" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B184,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B184,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D184" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B184,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B184,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E184" s="8" t="n"/>
@@ -4124,11 +4123,11 @@
       <c r="A185" s="5" t="n"/>
       <c r="B185" s="5" t="n"/>
       <c r="C185" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B185,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B185,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D185" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B185,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B185,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E185" s="8" t="n"/>
@@ -4143,11 +4142,11 @@
       <c r="A186" s="5" t="n"/>
       <c r="B186" s="5" t="n"/>
       <c r="C186" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B186,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B186,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D186" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B186,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B186,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E186" s="8" t="n"/>
@@ -4162,11 +4161,11 @@
       <c r="A187" s="5" t="n"/>
       <c r="B187" s="5" t="n"/>
       <c r="C187" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B187,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B187,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D187" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B187,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B187,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E187" s="8" t="n"/>
@@ -4181,11 +4180,11 @@
       <c r="A188" s="5" t="n"/>
       <c r="B188" s="5" t="n"/>
       <c r="C188" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B188,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B188,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D188" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B188,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B188,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E188" s="8" t="n"/>
@@ -4200,11 +4199,11 @@
       <c r="A189" s="5" t="n"/>
       <c r="B189" s="5" t="n"/>
       <c r="C189" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B189,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B189,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D189" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B189,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B189,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E189" s="8" t="n"/>
@@ -4219,11 +4218,11 @@
       <c r="A190" s="5" t="n"/>
       <c r="B190" s="5" t="n"/>
       <c r="C190" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B190,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B190,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D190" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B190,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B190,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E190" s="8" t="n"/>
@@ -4238,11 +4237,11 @@
       <c r="A191" s="5" t="n"/>
       <c r="B191" s="5" t="n"/>
       <c r="C191" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B191,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B191,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D191" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B191,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B191,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E191" s="8" t="n"/>
@@ -4257,11 +4256,11 @@
       <c r="A192" s="5" t="n"/>
       <c r="B192" s="5" t="n"/>
       <c r="C192" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B192,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B192,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D192" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B192,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B192,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E192" s="8" t="n"/>
@@ -4276,11 +4275,11 @@
       <c r="A193" s="5" t="n"/>
       <c r="B193" s="5" t="n"/>
       <c r="C193" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B193,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B193,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D193" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B193,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B193,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E193" s="8" t="n"/>
@@ -4295,11 +4294,11 @@
       <c r="A194" s="5" t="n"/>
       <c r="B194" s="5" t="n"/>
       <c r="C194" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B194,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B194,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D194" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B194,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B194,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E194" s="8" t="n"/>
@@ -4314,11 +4313,11 @@
       <c r="A195" s="5" t="n"/>
       <c r="B195" s="5" t="n"/>
       <c r="C195" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B195,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B195,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D195" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B195,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B195,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E195" s="8" t="n"/>
@@ -4333,11 +4332,11 @@
       <c r="A196" s="5" t="n"/>
       <c r="B196" s="5" t="n"/>
       <c r="C196" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B196,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B196,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D196" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B196,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B196,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E196" s="8" t="n"/>
@@ -4352,11 +4351,11 @@
       <c r="A197" s="5" t="n"/>
       <c r="B197" s="5" t="n"/>
       <c r="C197" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B197,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B197,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D197" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B197,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B197,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E197" s="8" t="n"/>
@@ -4371,11 +4370,11 @@
       <c r="A198" s="5" t="n"/>
       <c r="B198" s="5" t="n"/>
       <c r="C198" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B198,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B198,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D198" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B198,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B198,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E198" s="8" t="n"/>
@@ -4390,11 +4389,11 @@
       <c r="A199" s="5" t="n"/>
       <c r="B199" s="5" t="n"/>
       <c r="C199" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B199,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B199,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D199" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B199,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B199,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E199" s="8" t="n"/>
@@ -4409,11 +4408,11 @@
       <c r="A200" s="5" t="n"/>
       <c r="B200" s="5" t="n"/>
       <c r="C200" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B200,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B200,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D200" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B200,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B200,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E200" s="8" t="n"/>
@@ -4428,11 +4427,11 @@
       <c r="A201" s="5" t="n"/>
       <c r="B201" s="5" t="n"/>
       <c r="C201" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B201,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B201,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D201" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B201,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B201,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E201" s="8" t="n"/>
@@ -4447,11 +4446,11 @@
       <c r="A202" s="5" t="n"/>
       <c r="B202" s="5" t="n"/>
       <c r="C202" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B202,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B202,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D202" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B202,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B202,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E202" s="8" t="n"/>
@@ -4466,11 +4465,11 @@
       <c r="A203" s="5" t="n"/>
       <c r="B203" s="5" t="n"/>
       <c r="C203" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B203,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B203,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D203" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B203,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B203,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E203" s="8" t="n"/>
@@ -4485,11 +4484,11 @@
       <c r="A204" s="5" t="n"/>
       <c r="B204" s="5" t="n"/>
       <c r="C204" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B204,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B204,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D204" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B204,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B204,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E204" s="8" t="n"/>
@@ -4504,11 +4503,11 @@
       <c r="A205" s="5" t="n"/>
       <c r="B205" s="5" t="n"/>
       <c r="C205" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B205,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B205,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D205" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B205,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B205,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E205" s="8" t="n"/>
@@ -4523,11 +4522,11 @@
       <c r="A206" s="5" t="n"/>
       <c r="B206" s="5" t="n"/>
       <c r="C206" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B206,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B206,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D206" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B206,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B206,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E206" s="8" t="n"/>
@@ -4542,11 +4541,11 @@
       <c r="A207" s="5" t="n"/>
       <c r="B207" s="5" t="n"/>
       <c r="C207" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B207,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B207,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D207" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B207,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B207,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E207" s="8" t="n"/>
@@ -4561,11 +4560,11 @@
       <c r="A208" s="5" t="n"/>
       <c r="B208" s="5" t="n"/>
       <c r="C208" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B208,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B208,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D208" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B208,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B208,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E208" s="8" t="n"/>
@@ -4580,11 +4579,11 @@
       <c r="A209" s="5" t="n"/>
       <c r="B209" s="5" t="n"/>
       <c r="C209" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B209,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B209,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D209" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B209,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B209,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E209" s="8" t="n"/>
@@ -4599,11 +4598,11 @@
       <c r="A210" s="5" t="n"/>
       <c r="B210" s="5" t="n"/>
       <c r="C210" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B210,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B210,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D210" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B210,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B210,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E210" s="8" t="n"/>
@@ -4618,11 +4617,11 @@
       <c r="A211" s="5" t="n"/>
       <c r="B211" s="5" t="n"/>
       <c r="C211" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B211,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B211,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D211" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B211,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B211,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E211" s="8" t="n"/>
@@ -4637,11 +4636,11 @@
       <c r="A212" s="5" t="n"/>
       <c r="B212" s="5" t="n"/>
       <c r="C212" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B212,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B212,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D212" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B212,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B212,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E212" s="8" t="n"/>
@@ -4656,11 +4655,11 @@
       <c r="A213" s="5" t="n"/>
       <c r="B213" s="5" t="n"/>
       <c r="C213" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B213,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B213,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D213" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B213,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B213,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E213" s="8" t="n"/>
@@ -4675,11 +4674,11 @@
       <c r="A214" s="5" t="n"/>
       <c r="B214" s="5" t="n"/>
       <c r="C214" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B214,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B214,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D214" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B214,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B214,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E214" s="8" t="n"/>
@@ -4694,11 +4693,11 @@
       <c r="A215" s="5" t="n"/>
       <c r="B215" s="5" t="n"/>
       <c r="C215" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B215,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B215,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D215" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B215,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B215,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E215" s="8" t="n"/>
@@ -4713,11 +4712,11 @@
       <c r="A216" s="5" t="n"/>
       <c r="B216" s="5" t="n"/>
       <c r="C216" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B216,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B216,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D216" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B216,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B216,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E216" s="8" t="n"/>
@@ -4732,11 +4731,11 @@
       <c r="A217" s="5" t="n"/>
       <c r="B217" s="5" t="n"/>
       <c r="C217" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B217,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B217,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D217" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B217,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B217,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E217" s="8" t="n"/>
@@ -4751,11 +4750,11 @@
       <c r="A218" s="5" t="n"/>
       <c r="B218" s="5" t="n"/>
       <c r="C218" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B218,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B218,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D218" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B218,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B218,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E218" s="8" t="n"/>
@@ -4770,11 +4769,11 @@
       <c r="A219" s="5" t="n"/>
       <c r="B219" s="5" t="n"/>
       <c r="C219" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B219,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B219,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D219" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B219,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B219,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E219" s="8" t="n"/>
@@ -4789,11 +4788,11 @@
       <c r="A220" s="5" t="n"/>
       <c r="B220" s="5" t="n"/>
       <c r="C220" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B220,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B220,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D220" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B220,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B220,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E220" s="8" t="n"/>
@@ -4808,11 +4807,11 @@
       <c r="A221" s="5" t="n"/>
       <c r="B221" s="5" t="n"/>
       <c r="C221" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B221,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B221,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D221" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B221,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B221,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E221" s="8" t="n"/>
@@ -4827,11 +4826,11 @@
       <c r="A222" s="5" t="n"/>
       <c r="B222" s="5" t="n"/>
       <c r="C222" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B222,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B222,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D222" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B222,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B222,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E222" s="8" t="n"/>
@@ -4846,11 +4845,11 @@
       <c r="A223" s="5" t="n"/>
       <c r="B223" s="5" t="n"/>
       <c r="C223" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B223,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B223,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D223" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B223,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B223,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E223" s="8" t="n"/>
@@ -4865,11 +4864,11 @@
       <c r="A224" s="5" t="n"/>
       <c r="B224" s="5" t="n"/>
       <c r="C224" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B224,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B224,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D224" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B224,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B224,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E224" s="8" t="n"/>
@@ -4884,11 +4883,11 @@
       <c r="A225" s="5" t="n"/>
       <c r="B225" s="5" t="n"/>
       <c r="C225" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B225,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B225,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D225" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B225,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B225,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E225" s="8" t="n"/>
@@ -4903,11 +4902,11 @@
       <c r="A226" s="5" t="n"/>
       <c r="B226" s="5" t="n"/>
       <c r="C226" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B226,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B226,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D226" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B226,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B226,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E226" s="8" t="n"/>
@@ -4922,11 +4921,11 @@
       <c r="A227" s="5" t="n"/>
       <c r="B227" s="5" t="n"/>
       <c r="C227" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B227,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B227,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D227" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B227,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B227,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E227" s="8" t="n"/>
@@ -4941,11 +4940,11 @@
       <c r="A228" s="5" t="n"/>
       <c r="B228" s="5" t="n"/>
       <c r="C228" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B228,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B228,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D228" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B228,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B228,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E228" s="8" t="n"/>
@@ -4960,11 +4959,11 @@
       <c r="A229" s="5" t="n"/>
       <c r="B229" s="5" t="n"/>
       <c r="C229" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B229,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B229,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D229" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B229,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B229,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E229" s="8" t="n"/>
@@ -4979,11 +4978,11 @@
       <c r="A230" s="5" t="n"/>
       <c r="B230" s="5" t="n"/>
       <c r="C230" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B230,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B230,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D230" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B230,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B230,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E230" s="8" t="n"/>
@@ -4998,11 +4997,11 @@
       <c r="A231" s="5" t="n"/>
       <c r="B231" s="5" t="n"/>
       <c r="C231" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B231,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B231,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D231" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B231,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B231,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E231" s="8" t="n"/>
@@ -5017,11 +5016,11 @@
       <c r="A232" s="5" t="n"/>
       <c r="B232" s="5" t="n"/>
       <c r="C232" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B232,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B232,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D232" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B232,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B232,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E232" s="8" t="n"/>
@@ -5036,11 +5035,11 @@
       <c r="A233" s="5" t="n"/>
       <c r="B233" s="5" t="n"/>
       <c r="C233" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B233,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B233,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D233" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B233,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B233,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E233" s="8" t="n"/>
@@ -5055,11 +5054,11 @@
       <c r="A234" s="5" t="n"/>
       <c r="B234" s="5" t="n"/>
       <c r="C234" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B234,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B234,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D234" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B234,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B234,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E234" s="8" t="n"/>
@@ -5074,11 +5073,11 @@
       <c r="A235" s="5" t="n"/>
       <c r="B235" s="5" t="n"/>
       <c r="C235" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B235,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B235,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D235" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B235,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B235,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E235" s="8" t="n"/>
@@ -5093,11 +5092,11 @@
       <c r="A236" s="5" t="n"/>
       <c r="B236" s="5" t="n"/>
       <c r="C236" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B236,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B236,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D236" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B236,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B236,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E236" s="8" t="n"/>
@@ -5112,11 +5111,11 @@
       <c r="A237" s="5" t="n"/>
       <c r="B237" s="5" t="n"/>
       <c r="C237" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B237,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B237,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D237" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B237,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B237,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E237" s="8" t="n"/>
@@ -5131,11 +5130,11 @@
       <c r="A238" s="5" t="n"/>
       <c r="B238" s="5" t="n"/>
       <c r="C238" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B238,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B238,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D238" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B238,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B238,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E238" s="8" t="n"/>
@@ -5150,11 +5149,11 @@
       <c r="A239" s="5" t="n"/>
       <c r="B239" s="5" t="n"/>
       <c r="C239" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B239,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B239,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D239" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B239,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B239,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E239" s="8" t="n"/>
@@ -5169,11 +5168,11 @@
       <c r="A240" s="5" t="n"/>
       <c r="B240" s="5" t="n"/>
       <c r="C240" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B240,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B240,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D240" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B240,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B240,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E240" s="8" t="n"/>
@@ -5188,11 +5187,11 @@
       <c r="A241" s="5" t="n"/>
       <c r="B241" s="5" t="n"/>
       <c r="C241" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B241,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B241,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D241" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B241,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B241,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E241" s="8" t="n"/>
@@ -5207,11 +5206,11 @@
       <c r="A242" s="5" t="n"/>
       <c r="B242" s="5" t="n"/>
       <c r="C242" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B242,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B242,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D242" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B242,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B242,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E242" s="8" t="n"/>
@@ -5226,11 +5225,11 @@
       <c r="A243" s="5" t="n"/>
       <c r="B243" s="5" t="n"/>
       <c r="C243" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B243,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B243,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D243" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B243,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B243,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E243" s="8" t="n"/>
@@ -5245,11 +5244,11 @@
       <c r="A244" s="5" t="n"/>
       <c r="B244" s="5" t="n"/>
       <c r="C244" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B244,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B244,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D244" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B244,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B244,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E244" s="8" t="n"/>
@@ -5264,11 +5263,11 @@
       <c r="A245" s="5" t="n"/>
       <c r="B245" s="5" t="n"/>
       <c r="C245" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B245,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B245,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D245" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B245,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B245,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E245" s="8" t="n"/>
@@ -5283,11 +5282,11 @@
       <c r="A246" s="5" t="n"/>
       <c r="B246" s="5" t="n"/>
       <c r="C246" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B246,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B246,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D246" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B246,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B246,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E246" s="8" t="n"/>
@@ -5302,11 +5301,11 @@
       <c r="A247" s="5" t="n"/>
       <c r="B247" s="5" t="n"/>
       <c r="C247" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B247,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B247,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D247" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B247,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B247,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E247" s="8" t="n"/>
@@ -5321,11 +5320,11 @@
       <c r="A248" s="5" t="n"/>
       <c r="B248" s="5" t="n"/>
       <c r="C248" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B248,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B248,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D248" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B248,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B248,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E248" s="8" t="n"/>
@@ -5340,11 +5339,11 @@
       <c r="A249" s="5" t="n"/>
       <c r="B249" s="5" t="n"/>
       <c r="C249" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B249,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B249,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D249" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B249,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B249,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E249" s="8" t="n"/>
@@ -5359,11 +5358,11 @@
       <c r="A250" s="5" t="n"/>
       <c r="B250" s="5" t="n"/>
       <c r="C250" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B250,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B250,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D250" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B250,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B250,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E250" s="8" t="n"/>
@@ -5378,11 +5377,11 @@
       <c r="A251" s="5" t="n"/>
       <c r="B251" s="5" t="n"/>
       <c r="C251" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B251,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B251,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D251" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B251,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B251,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E251" s="8" t="n"/>
@@ -5397,11 +5396,11 @@
       <c r="A252" s="5" t="n"/>
       <c r="B252" s="5" t="n"/>
       <c r="C252" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B252,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B252,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D252" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B252,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B252,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E252" s="8" t="n"/>
@@ -5416,11 +5415,11 @@
       <c r="A253" s="5" t="n"/>
       <c r="B253" s="5" t="n"/>
       <c r="C253" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B253,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B253,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D253" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B253,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B253,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E253" s="8" t="n"/>
@@ -5435,11 +5434,11 @@
       <c r="A254" s="5" t="n"/>
       <c r="B254" s="5" t="n"/>
       <c r="C254" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B254,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B254,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D254" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B254,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B254,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E254" s="8" t="n"/>
@@ -5454,11 +5453,11 @@
       <c r="A255" s="5" t="n"/>
       <c r="B255" s="5" t="n"/>
       <c r="C255" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B255,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B255,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D255" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B255,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B255,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E255" s="8" t="n"/>
@@ -5473,11 +5472,11 @@
       <c r="A256" s="5" t="n"/>
       <c r="B256" s="5" t="n"/>
       <c r="C256" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B256,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B256,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D256" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B256,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B256,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E256" s="8" t="n"/>
@@ -5492,11 +5491,11 @@
       <c r="A257" s="5" t="n"/>
       <c r="B257" s="5" t="n"/>
       <c r="C257" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B257,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B257,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D257" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B257,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B257,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E257" s="8" t="n"/>
@@ -5511,11 +5510,11 @@
       <c r="A258" s="5" t="n"/>
       <c r="B258" s="5" t="n"/>
       <c r="C258" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B258,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B258,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D258" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B258,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B258,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E258" s="8" t="n"/>
@@ -5530,11 +5529,11 @@
       <c r="A259" s="5" t="n"/>
       <c r="B259" s="5" t="n"/>
       <c r="C259" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B259,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B259,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D259" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B259,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B259,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E259" s="8" t="n"/>
@@ -5549,11 +5548,11 @@
       <c r="A260" s="5" t="n"/>
       <c r="B260" s="5" t="n"/>
       <c r="C260" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B260,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B260,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D260" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B260,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B260,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E260" s="8" t="n"/>
@@ -5568,11 +5567,11 @@
       <c r="A261" s="5" t="n"/>
       <c r="B261" s="5" t="n"/>
       <c r="C261" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B261,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B261,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D261" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B261,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B261,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E261" s="8" t="n"/>
@@ -5587,11 +5586,11 @@
       <c r="A262" s="5" t="n"/>
       <c r="B262" s="5" t="n"/>
       <c r="C262" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B262,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B262,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D262" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B262,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B262,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E262" s="8" t="n"/>
@@ -5606,11 +5605,11 @@
       <c r="A263" s="5" t="n"/>
       <c r="B263" s="5" t="n"/>
       <c r="C263" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B263,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B263,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D263" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B263,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B263,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E263" s="8" t="n"/>
@@ -5625,11 +5624,11 @@
       <c r="A264" s="5" t="n"/>
       <c r="B264" s="5" t="n"/>
       <c r="C264" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B264,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B264,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D264" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B264,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B264,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E264" s="8" t="n"/>
@@ -5644,11 +5643,11 @@
       <c r="A265" s="5" t="n"/>
       <c r="B265" s="5" t="n"/>
       <c r="C265" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B265,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B265,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D265" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B265,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B265,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E265" s="8" t="n"/>
@@ -5663,11 +5662,11 @@
       <c r="A266" s="5" t="n"/>
       <c r="B266" s="5" t="n"/>
       <c r="C266" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B266,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B266,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D266" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B266,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B266,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E266" s="8" t="n"/>
@@ -5682,11 +5681,11 @@
       <c r="A267" s="5" t="n"/>
       <c r="B267" s="5" t="n"/>
       <c r="C267" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B267,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B267,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D267" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B267,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B267,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E267" s="8" t="n"/>
@@ -5701,11 +5700,11 @@
       <c r="A268" s="5" t="n"/>
       <c r="B268" s="5" t="n"/>
       <c r="C268" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B268,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B268,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D268" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B268,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B268,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E268" s="8" t="n"/>
@@ -5720,11 +5719,11 @@
       <c r="A269" s="5" t="n"/>
       <c r="B269" s="5" t="n"/>
       <c r="C269" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B269,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B269,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D269" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B269,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B269,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E269" s="8" t="n"/>
@@ -5739,11 +5738,11 @@
       <c r="A270" s="5" t="n"/>
       <c r="B270" s="5" t="n"/>
       <c r="C270" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B270,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B270,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D270" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B270,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B270,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E270" s="8" t="n"/>
@@ -5758,11 +5757,11 @@
       <c r="A271" s="5" t="n"/>
       <c r="B271" s="5" t="n"/>
       <c r="C271" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B271,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B271,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D271" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B271,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B271,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E271" s="8" t="n"/>
@@ -5777,11 +5776,11 @@
       <c r="A272" s="5" t="n"/>
       <c r="B272" s="5" t="n"/>
       <c r="C272" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B272,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B272,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D272" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B272,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B272,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E272" s="8" t="n"/>
@@ -5796,11 +5795,11 @@
       <c r="A273" s="5" t="n"/>
       <c r="B273" s="5" t="n"/>
       <c r="C273" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B273,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B273,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D273" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B273,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B273,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E273" s="8" t="n"/>
@@ -5815,11 +5814,11 @@
       <c r="A274" s="5" t="n"/>
       <c r="B274" s="5" t="n"/>
       <c r="C274" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B274,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B274,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D274" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B274,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B274,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E274" s="8" t="n"/>
@@ -5834,11 +5833,11 @@
       <c r="A275" s="5" t="n"/>
       <c r="B275" s="5" t="n"/>
       <c r="C275" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B275,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B275,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D275" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B275,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B275,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E275" s="8" t="n"/>
@@ -5853,11 +5852,11 @@
       <c r="A276" s="5" t="n"/>
       <c r="B276" s="5" t="n"/>
       <c r="C276" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B276,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B276,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D276" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B276,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B276,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E276" s="8" t="n"/>
@@ -5872,11 +5871,11 @@
       <c r="A277" s="5" t="n"/>
       <c r="B277" s="5" t="n"/>
       <c r="C277" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B277,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B277,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D277" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B277,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B277,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E277" s="8" t="n"/>
@@ -5891,11 +5890,11 @@
       <c r="A278" s="5" t="n"/>
       <c r="B278" s="5" t="n"/>
       <c r="C278" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B278,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B278,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D278" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B278,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B278,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E278" s="8" t="n"/>
@@ -5910,11 +5909,11 @@
       <c r="A279" s="5" t="n"/>
       <c r="B279" s="5" t="n"/>
       <c r="C279" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B279,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B279,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D279" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B279,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B279,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E279" s="8" t="n"/>
@@ -5929,11 +5928,11 @@
       <c r="A280" s="5" t="n"/>
       <c r="B280" s="5" t="n"/>
       <c r="C280" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B280,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B280,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D280" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B280,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B280,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E280" s="8" t="n"/>
@@ -5948,11 +5947,11 @@
       <c r="A281" s="5" t="n"/>
       <c r="B281" s="5" t="n"/>
       <c r="C281" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B281,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B281,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D281" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B281,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B281,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E281" s="8" t="n"/>
@@ -5967,11 +5966,11 @@
       <c r="A282" s="5" t="n"/>
       <c r="B282" s="5" t="n"/>
       <c r="C282" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B282,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B282,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D282" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B282,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B282,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E282" s="8" t="n"/>
@@ -5986,11 +5985,11 @@
       <c r="A283" s="5" t="n"/>
       <c r="B283" s="5" t="n"/>
       <c r="C283" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B283,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B283,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D283" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B283,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B283,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E283" s="8" t="n"/>
@@ -6005,11 +6004,11 @@
       <c r="A284" s="5" t="n"/>
       <c r="B284" s="5" t="n"/>
       <c r="C284" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B284,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B284,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D284" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B284,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B284,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E284" s="8" t="n"/>
@@ -6024,11 +6023,11 @@
       <c r="A285" s="5" t="n"/>
       <c r="B285" s="5" t="n"/>
       <c r="C285" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B285,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B285,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D285" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B285,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B285,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E285" s="8" t="n"/>
@@ -6043,11 +6042,11 @@
       <c r="A286" s="5" t="n"/>
       <c r="B286" s="5" t="n"/>
       <c r="C286" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B286,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B286,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D286" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B286,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B286,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E286" s="8" t="n"/>
@@ -6062,11 +6061,11 @@
       <c r="A287" s="5" t="n"/>
       <c r="B287" s="5" t="n"/>
       <c r="C287" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B287,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B287,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D287" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B287,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B287,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E287" s="8" t="n"/>
@@ -6081,11 +6080,11 @@
       <c r="A288" s="5" t="n"/>
       <c r="B288" s="5" t="n"/>
       <c r="C288" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B288,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B288,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D288" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B288,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B288,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E288" s="8" t="n"/>
@@ -6100,11 +6099,11 @@
       <c r="A289" s="5" t="n"/>
       <c r="B289" s="5" t="n"/>
       <c r="C289" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B289,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B289,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D289" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B289,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B289,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E289" s="8" t="n"/>
@@ -6119,11 +6118,11 @@
       <c r="A290" s="5" t="n"/>
       <c r="B290" s="5" t="n"/>
       <c r="C290" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B290,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B290,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D290" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B290,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B290,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E290" s="8" t="n"/>
@@ -6138,11 +6137,11 @@
       <c r="A291" s="5" t="n"/>
       <c r="B291" s="5" t="n"/>
       <c r="C291" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B291,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B291,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D291" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B291,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B291,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E291" s="8" t="n"/>
@@ -6157,11 +6156,11 @@
       <c r="A292" s="5" t="n"/>
       <c r="B292" s="5" t="n"/>
       <c r="C292" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B292,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B292,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D292" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B292,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B292,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E292" s="8" t="n"/>
@@ -6176,11 +6175,11 @@
       <c r="A293" s="5" t="n"/>
       <c r="B293" s="5" t="n"/>
       <c r="C293" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B293,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B293,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D293" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B293,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B293,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E293" s="8" t="n"/>
@@ -6195,11 +6194,11 @@
       <c r="A294" s="5" t="n"/>
       <c r="B294" s="5" t="n"/>
       <c r="C294" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B294,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B294,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D294" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B294,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B294,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E294" s="8" t="n"/>
@@ -6214,11 +6213,11 @@
       <c r="A295" s="5" t="n"/>
       <c r="B295" s="5" t="n"/>
       <c r="C295" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B295,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B295,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D295" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B295,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B295,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E295" s="8" t="n"/>
@@ -6233,11 +6232,11 @@
       <c r="A296" s="5" t="n"/>
       <c r="B296" s="5" t="n"/>
       <c r="C296" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B296,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B296,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D296" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B296,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B296,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E296" s="8" t="n"/>
@@ -6252,11 +6251,11 @@
       <c r="A297" s="5" t="n"/>
       <c r="B297" s="5" t="n"/>
       <c r="C297" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B297,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B297,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D297" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B297,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B297,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E297" s="8" t="n"/>
@@ -6271,11 +6270,11 @@
       <c r="A298" s="5" t="n"/>
       <c r="B298" s="5" t="n"/>
       <c r="C298" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B298,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B298,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D298" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B298,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B298,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E298" s="8" t="n"/>
@@ -6290,11 +6289,11 @@
       <c r="A299" s="5" t="n"/>
       <c r="B299" s="5" t="n"/>
       <c r="C299" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B299,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B299,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D299" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B299,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B299,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E299" s="8" t="n"/>
@@ -6309,11 +6308,11 @@
       <c r="A300" s="5" t="n"/>
       <c r="B300" s="5" t="n"/>
       <c r="C300" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B300,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B300,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D300" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B300,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B300,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E300" s="8" t="n"/>
@@ -6328,11 +6327,11 @@
       <c r="A301" s="5" t="n"/>
       <c r="B301" s="5" t="n"/>
       <c r="C301" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B301,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B301,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D301" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B301,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B301,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E301" s="8" t="n"/>
@@ -6347,11 +6346,11 @@
       <c r="A302" s="5" t="n"/>
       <c r="B302" s="5" t="n"/>
       <c r="C302" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B302,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B302,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D302" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B302,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B302,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E302" s="8" t="n"/>
@@ -6366,11 +6365,11 @@
       <c r="A303" s="5" t="n"/>
       <c r="B303" s="5" t="n"/>
       <c r="C303" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B303,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B303,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D303" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B303,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B303,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E303" s="8" t="n"/>
@@ -6385,11 +6384,11 @@
       <c r="A304" s="5" t="n"/>
       <c r="B304" s="5" t="n"/>
       <c r="C304" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B304,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B304,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D304" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B304,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B304,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E304" s="8" t="n"/>
@@ -6404,11 +6403,11 @@
       <c r="A305" s="5" t="n"/>
       <c r="B305" s="5" t="n"/>
       <c r="C305" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B305,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B305,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D305" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B305,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B305,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E305" s="8" t="n"/>
@@ -6423,11 +6422,11 @@
       <c r="A306" s="5" t="n"/>
       <c r="B306" s="5" t="n"/>
       <c r="C306" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B306,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B306,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D306" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B306,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B306,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E306" s="8" t="n"/>
@@ -6442,11 +6441,11 @@
       <c r="A307" s="5" t="n"/>
       <c r="B307" s="5" t="n"/>
       <c r="C307" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B307,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B307,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D307" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B307,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B307,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E307" s="8" t="n"/>
@@ -6461,11 +6460,11 @@
       <c r="A308" s="5" t="n"/>
       <c r="B308" s="5" t="n"/>
       <c r="C308" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B308,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B308,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D308" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B308,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B308,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E308" s="8" t="n"/>
@@ -6480,11 +6479,11 @@
       <c r="A309" s="5" t="n"/>
       <c r="B309" s="5" t="n"/>
       <c r="C309" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B309,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B309,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D309" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B309,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B309,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E309" s="8" t="n"/>
@@ -6499,11 +6498,11 @@
       <c r="A310" s="5" t="n"/>
       <c r="B310" s="5" t="n"/>
       <c r="C310" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B310,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B310,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D310" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B310,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B310,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E310" s="8" t="n"/>
@@ -6518,11 +6517,11 @@
       <c r="A311" s="5" t="n"/>
       <c r="B311" s="5" t="n"/>
       <c r="C311" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B311,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B311,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D311" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B311,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B311,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E311" s="8" t="n"/>
@@ -6537,11 +6536,11 @@
       <c r="A312" s="5" t="n"/>
       <c r="B312" s="5" t="n"/>
       <c r="C312" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B312,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B312,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D312" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B312,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B312,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E312" s="8" t="n"/>
@@ -6556,11 +6555,11 @@
       <c r="A313" s="5" t="n"/>
       <c r="B313" s="5" t="n"/>
       <c r="C313" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B313,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B313,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D313" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B313,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B313,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E313" s="8" t="n"/>
@@ -6575,11 +6574,11 @@
       <c r="A314" s="5" t="n"/>
       <c r="B314" s="5" t="n"/>
       <c r="C314" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B314,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B314,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D314" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B314,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B314,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E314" s="8" t="n"/>
@@ -6594,11 +6593,11 @@
       <c r="A315" s="5" t="n"/>
       <c r="B315" s="5" t="n"/>
       <c r="C315" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B315,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B315,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D315" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B315,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B315,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E315" s="8" t="n"/>
@@ -6613,11 +6612,11 @@
       <c r="A316" s="5" t="n"/>
       <c r="B316" s="5" t="n"/>
       <c r="C316" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B316,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B316,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D316" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B316,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B316,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E316" s="8" t="n"/>
@@ -6632,11 +6631,11 @@
       <c r="A317" s="5" t="n"/>
       <c r="B317" s="5" t="n"/>
       <c r="C317" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B317,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B317,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D317" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B317,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B317,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E317" s="8" t="n"/>
@@ -6651,11 +6650,11 @@
       <c r="A318" s="5" t="n"/>
       <c r="B318" s="5" t="n"/>
       <c r="C318" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B318,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B318,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D318" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B318,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B318,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E318" s="8" t="n"/>
@@ -6670,11 +6669,11 @@
       <c r="A319" s="5" t="n"/>
       <c r="B319" s="5" t="n"/>
       <c r="C319" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B319,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B319,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D319" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B319,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B319,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E319" s="8" t="n"/>
@@ -6689,11 +6688,11 @@
       <c r="A320" s="5" t="n"/>
       <c r="B320" s="5" t="n"/>
       <c r="C320" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B320,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B320,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D320" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B320,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B320,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E320" s="8" t="n"/>
@@ -6708,11 +6707,11 @@
       <c r="A321" s="5" t="n"/>
       <c r="B321" s="5" t="n"/>
       <c r="C321" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B321,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B321,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D321" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B321,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B321,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E321" s="8" t="n"/>
@@ -6727,11 +6726,11 @@
       <c r="A322" s="5" t="n"/>
       <c r="B322" s="5" t="n"/>
       <c r="C322" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B322,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B322,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D322" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B322,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B322,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E322" s="8" t="n"/>
@@ -6746,11 +6745,11 @@
       <c r="A323" s="5" t="n"/>
       <c r="B323" s="5" t="n"/>
       <c r="C323" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B323,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B323,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D323" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B323,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B323,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E323" s="8" t="n"/>
@@ -6765,11 +6764,11 @@
       <c r="A324" s="5" t="n"/>
       <c r="B324" s="5" t="n"/>
       <c r="C324" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B324,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B324,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D324" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B324,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B324,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E324" s="8" t="n"/>
@@ -6784,11 +6783,11 @@
       <c r="A325" s="5" t="n"/>
       <c r="B325" s="5" t="n"/>
       <c r="C325" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B325,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B325,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D325" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B325,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B325,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E325" s="8" t="n"/>
@@ -6803,11 +6802,11 @@
       <c r="A326" s="5" t="n"/>
       <c r="B326" s="5" t="n"/>
       <c r="C326" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B326,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B326,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D326" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B326,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B326,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E326" s="8" t="n"/>
@@ -6822,11 +6821,11 @@
       <c r="A327" s="5" t="n"/>
       <c r="B327" s="5" t="n"/>
       <c r="C327" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B327,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B327,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D327" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B327,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B327,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E327" s="8" t="n"/>
@@ -6841,11 +6840,11 @@
       <c r="A328" s="5" t="n"/>
       <c r="B328" s="5" t="n"/>
       <c r="C328" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B328,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B328,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D328" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B328,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B328,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E328" s="8" t="n"/>
@@ -6860,11 +6859,11 @@
       <c r="A329" s="5" t="n"/>
       <c r="B329" s="5" t="n"/>
       <c r="C329" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B329,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B329,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D329" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B329,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B329,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E329" s="8" t="n"/>
@@ -6879,11 +6878,11 @@
       <c r="A330" s="5" t="n"/>
       <c r="B330" s="5" t="n"/>
       <c r="C330" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B330,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B330,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D330" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B330,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B330,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E330" s="8" t="n"/>
@@ -6898,11 +6897,11 @@
       <c r="A331" s="5" t="n"/>
       <c r="B331" s="5" t="n"/>
       <c r="C331" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B331,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B331,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D331" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B331,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B331,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E331" s="8" t="n"/>
@@ -6917,11 +6916,11 @@
       <c r="A332" s="5" t="n"/>
       <c r="B332" s="5" t="n"/>
       <c r="C332" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B332,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B332,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D332" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B332,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B332,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E332" s="8" t="n"/>
@@ -6936,11 +6935,11 @@
       <c r="A333" s="5" t="n"/>
       <c r="B333" s="5" t="n"/>
       <c r="C333" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B333,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B333,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D333" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B333,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B333,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E333" s="8" t="n"/>
@@ -6955,11 +6954,11 @@
       <c r="A334" s="5" t="n"/>
       <c r="B334" s="5" t="n"/>
       <c r="C334" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B334,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B334,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D334" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B334,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B334,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E334" s="8" t="n"/>
@@ -6974,11 +6973,11 @@
       <c r="A335" s="5" t="n"/>
       <c r="B335" s="5" t="n"/>
       <c r="C335" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B335,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B335,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D335" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B335,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B335,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E335" s="8" t="n"/>
@@ -6993,11 +6992,11 @@
       <c r="A336" s="5" t="n"/>
       <c r="B336" s="5" t="n"/>
       <c r="C336" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B336,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B336,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D336" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B336,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B336,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E336" s="8" t="n"/>
@@ -7012,11 +7011,11 @@
       <c r="A337" s="5" t="n"/>
       <c r="B337" s="5" t="n"/>
       <c r="C337" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B337,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B337,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D337" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B337,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B337,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E337" s="8" t="n"/>
@@ -7031,11 +7030,11 @@
       <c r="A338" s="5" t="n"/>
       <c r="B338" s="5" t="n"/>
       <c r="C338" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B338,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B338,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D338" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B338,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B338,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E338" s="8" t="n"/>
@@ -7050,11 +7049,11 @@
       <c r="A339" s="5" t="n"/>
       <c r="B339" s="5" t="n"/>
       <c r="C339" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B339,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B339,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D339" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B339,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B339,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E339" s="8" t="n"/>
@@ -7069,11 +7068,11 @@
       <c r="A340" s="5" t="n"/>
       <c r="B340" s="5" t="n"/>
       <c r="C340" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B340,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B340,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D340" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B340,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B340,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E340" s="8" t="n"/>
@@ -7088,11 +7087,11 @@
       <c r="A341" s="5" t="n"/>
       <c r="B341" s="5" t="n"/>
       <c r="C341" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B341,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B341,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D341" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B341,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B341,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E341" s="8" t="n"/>
@@ -7107,11 +7106,11 @@
       <c r="A342" s="5" t="n"/>
       <c r="B342" s="5" t="n"/>
       <c r="C342" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B342,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B342,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D342" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B342,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B342,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E342" s="8" t="n"/>
@@ -7126,11 +7125,11 @@
       <c r="A343" s="5" t="n"/>
       <c r="B343" s="5" t="n"/>
       <c r="C343" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B343,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B343,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D343" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B343,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B343,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E343" s="8" t="n"/>
@@ -7145,11 +7144,11 @@
       <c r="A344" s="5" t="n"/>
       <c r="B344" s="5" t="n"/>
       <c r="C344" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B344,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B344,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D344" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B344,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B344,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E344" s="8" t="n"/>
@@ -7164,11 +7163,11 @@
       <c r="A345" s="5" t="n"/>
       <c r="B345" s="5" t="n"/>
       <c r="C345" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B345,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B345,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D345" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B345,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B345,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E345" s="8" t="n"/>
@@ -7183,11 +7182,11 @@
       <c r="A346" s="5" t="n"/>
       <c r="B346" s="5" t="n"/>
       <c r="C346" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B346,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B346,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D346" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B346,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B346,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E346" s="8" t="n"/>
@@ -7202,11 +7201,11 @@
       <c r="A347" s="5" t="n"/>
       <c r="B347" s="5" t="n"/>
       <c r="C347" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B347,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B347,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D347" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B347,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B347,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E347" s="8" t="n"/>
@@ -7221,11 +7220,11 @@
       <c r="A348" s="5" t="n"/>
       <c r="B348" s="5" t="n"/>
       <c r="C348" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B348,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B348,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D348" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B348,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B348,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E348" s="8" t="n"/>
@@ -7240,11 +7239,11 @@
       <c r="A349" s="5" t="n"/>
       <c r="B349" s="5" t="n"/>
       <c r="C349" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B349,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B349,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D349" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B349,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B349,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E349" s="8" t="n"/>
@@ -7259,11 +7258,11 @@
       <c r="A350" s="5" t="n"/>
       <c r="B350" s="5" t="n"/>
       <c r="C350" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B350,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B350,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D350" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B350,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B350,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E350" s="8" t="n"/>
@@ -7278,11 +7277,11 @@
       <c r="A351" s="5" t="n"/>
       <c r="B351" s="5" t="n"/>
       <c r="C351" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B351,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B351,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D351" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B351,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B351,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E351" s="8" t="n"/>
@@ -7297,11 +7296,11 @@
       <c r="A352" s="5" t="n"/>
       <c r="B352" s="5" t="n"/>
       <c r="C352" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B352,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B352,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D352" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B352,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B352,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E352" s="8" t="n"/>
@@ -7316,11 +7315,11 @@
       <c r="A353" s="5" t="n"/>
       <c r="B353" s="5" t="n"/>
       <c r="C353" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B353,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B353,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D353" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B353,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B353,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E353" s="8" t="n"/>
@@ -7335,11 +7334,11 @@
       <c r="A354" s="5" t="n"/>
       <c r="B354" s="5" t="n"/>
       <c r="C354" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B354,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B354,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D354" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B354,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B354,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E354" s="8" t="n"/>
@@ -7354,11 +7353,11 @@
       <c r="A355" s="5" t="n"/>
       <c r="B355" s="5" t="n"/>
       <c r="C355" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B355,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B355,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D355" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B355,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B355,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E355" s="8" t="n"/>
@@ -7373,11 +7372,11 @@
       <c r="A356" s="5" t="n"/>
       <c r="B356" s="5" t="n"/>
       <c r="C356" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B356,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B356,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D356" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B356,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B356,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E356" s="8" t="n"/>
@@ -7392,11 +7391,11 @@
       <c r="A357" s="5" t="n"/>
       <c r="B357" s="5" t="n"/>
       <c r="C357" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B357,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B357,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D357" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B357,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B357,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E357" s="8" t="n"/>
@@ -7411,11 +7410,11 @@
       <c r="A358" s="5" t="n"/>
       <c r="B358" s="5" t="n"/>
       <c r="C358" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B358,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B358,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D358" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B358,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B358,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E358" s="8" t="n"/>
@@ -7430,11 +7429,11 @@
       <c r="A359" s="5" t="n"/>
       <c r="B359" s="5" t="n"/>
       <c r="C359" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B359,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B359,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D359" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B359,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B359,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E359" s="8" t="n"/>
@@ -7449,11 +7448,11 @@
       <c r="A360" s="5" t="n"/>
       <c r="B360" s="5" t="n"/>
       <c r="C360" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B360,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B360,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D360" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B360,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B360,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E360" s="8" t="n"/>
@@ -7468,11 +7467,11 @@
       <c r="A361" s="5" t="n"/>
       <c r="B361" s="5" t="n"/>
       <c r="C361" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B361,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B361,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D361" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B361,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B361,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E361" s="8" t="n"/>
@@ -7487,11 +7486,11 @@
       <c r="A362" s="5" t="n"/>
       <c r="B362" s="5" t="n"/>
       <c r="C362" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B362,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B362,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D362" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B362,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B362,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E362" s="8" t="n"/>
@@ -7506,11 +7505,11 @@
       <c r="A363" s="5" t="n"/>
       <c r="B363" s="5" t="n"/>
       <c r="C363" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B363,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B363,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D363" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B363,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B363,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E363" s="8" t="n"/>
@@ -7525,11 +7524,11 @@
       <c r="A364" s="5" t="n"/>
       <c r="B364" s="5" t="n"/>
       <c r="C364" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B364,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B364,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D364" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B364,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B364,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E364" s="8" t="n"/>
@@ -7544,11 +7543,11 @@
       <c r="A365" s="5" t="n"/>
       <c r="B365" s="5" t="n"/>
       <c r="C365" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B365,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B365,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D365" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B365,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B365,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E365" s="8" t="n"/>
@@ -7563,11 +7562,11 @@
       <c r="A366" s="5" t="n"/>
       <c r="B366" s="5" t="n"/>
       <c r="C366" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B366,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B366,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D366" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B366,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B366,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E366" s="8" t="n"/>
@@ -7582,11 +7581,11 @@
       <c r="A367" s="5" t="n"/>
       <c r="B367" s="5" t="n"/>
       <c r="C367" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B367,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B367,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D367" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B367,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B367,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E367" s="8" t="n"/>
@@ -7601,11 +7600,11 @@
       <c r="A368" s="5" t="n"/>
       <c r="B368" s="5" t="n"/>
       <c r="C368" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B368,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B368,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D368" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B368,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B368,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E368" s="8" t="n"/>
@@ -7620,11 +7619,11 @@
       <c r="A369" s="5" t="n"/>
       <c r="B369" s="5" t="n"/>
       <c r="C369" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B369,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B369,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D369" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B369,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B369,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E369" s="8" t="n"/>
@@ -7639,11 +7638,11 @@
       <c r="A370" s="5" t="n"/>
       <c r="B370" s="5" t="n"/>
       <c r="C370" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B370,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B370,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D370" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B370,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B370,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E370" s="8" t="n"/>
@@ -7658,11 +7657,11 @@
       <c r="A371" s="5" t="n"/>
       <c r="B371" s="5" t="n"/>
       <c r="C371" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B371,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B371,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D371" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B371,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B371,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E371" s="8" t="n"/>
@@ -7677,11 +7676,11 @@
       <c r="A372" s="5" t="n"/>
       <c r="B372" s="5" t="n"/>
       <c r="C372" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B372,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B372,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D372" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B372,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B372,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E372" s="8" t="n"/>
@@ -7696,11 +7695,11 @@
       <c r="A373" s="5" t="n"/>
       <c r="B373" s="5" t="n"/>
       <c r="C373" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B373,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B373,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D373" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B373,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B373,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E373" s="8" t="n"/>
@@ -7715,11 +7714,11 @@
       <c r="A374" s="5" t="n"/>
       <c r="B374" s="5" t="n"/>
       <c r="C374" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B374,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B374,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D374" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B374,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B374,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E374" s="8" t="n"/>
@@ -7734,11 +7733,11 @@
       <c r="A375" s="5" t="n"/>
       <c r="B375" s="5" t="n"/>
       <c r="C375" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B375,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B375,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D375" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B375,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B375,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E375" s="8" t="n"/>
@@ -7753,11 +7752,11 @@
       <c r="A376" s="5" t="n"/>
       <c r="B376" s="5" t="n"/>
       <c r="C376" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B376,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B376,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D376" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B376,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B376,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E376" s="8" t="n"/>
@@ -7772,11 +7771,11 @@
       <c r="A377" s="5" t="n"/>
       <c r="B377" s="5" t="n"/>
       <c r="C377" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B377,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B377,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D377" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B377,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B377,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E377" s="8" t="n"/>
@@ -7791,11 +7790,11 @@
       <c r="A378" s="5" t="n"/>
       <c r="B378" s="5" t="n"/>
       <c r="C378" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B378,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B378,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D378" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B378,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B378,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E378" s="8" t="n"/>
@@ -7810,11 +7809,11 @@
       <c r="A379" s="5" t="n"/>
       <c r="B379" s="5" t="n"/>
       <c r="C379" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B379,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B379,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D379" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B379,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B379,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E379" s="8" t="n"/>
@@ -7829,11 +7828,11 @@
       <c r="A380" s="5" t="n"/>
       <c r="B380" s="5" t="n"/>
       <c r="C380" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B380,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B380,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D380" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B380,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B380,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E380" s="8" t="n"/>
@@ -7848,11 +7847,11 @@
       <c r="A381" s="5" t="n"/>
       <c r="B381" s="5" t="n"/>
       <c r="C381" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B381,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B381,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D381" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B381,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B381,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E381" s="8" t="n"/>
@@ -7867,11 +7866,11 @@
       <c r="A382" s="5" t="n"/>
       <c r="B382" s="5" t="n"/>
       <c r="C382" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B382,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B382,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D382" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B382,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B382,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E382" s="8" t="n"/>
@@ -7886,11 +7885,11 @@
       <c r="A383" s="5" t="n"/>
       <c r="B383" s="5" t="n"/>
       <c r="C383" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B383,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B383,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D383" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B383,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B383,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E383" s="8" t="n"/>
@@ -7905,11 +7904,11 @@
       <c r="A384" s="5" t="n"/>
       <c r="B384" s="5" t="n"/>
       <c r="C384" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B384,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B384,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D384" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B384,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B384,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E384" s="8" t="n"/>
@@ -7924,11 +7923,11 @@
       <c r="A385" s="5" t="n"/>
       <c r="B385" s="5" t="n"/>
       <c r="C385" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B385,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B385,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D385" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B385,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B385,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E385" s="8" t="n"/>
@@ -7943,11 +7942,11 @@
       <c r="A386" s="5" t="n"/>
       <c r="B386" s="5" t="n"/>
       <c r="C386" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B386,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B386,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D386" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B386,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B386,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E386" s="8" t="n"/>
@@ -7962,11 +7961,11 @@
       <c r="A387" s="5" t="n"/>
       <c r="B387" s="5" t="n"/>
       <c r="C387" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B387,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B387,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D387" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B387,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B387,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E387" s="8" t="n"/>
@@ -7981,11 +7980,11 @@
       <c r="A388" s="5" t="n"/>
       <c r="B388" s="5" t="n"/>
       <c r="C388" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B388,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B388,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D388" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B388,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B388,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E388" s="8" t="n"/>
@@ -8000,11 +7999,11 @@
       <c r="A389" s="5" t="n"/>
       <c r="B389" s="5" t="n"/>
       <c r="C389" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B389,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B389,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D389" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B389,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B389,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E389" s="8" t="n"/>
@@ -8019,11 +8018,11 @@
       <c r="A390" s="5" t="n"/>
       <c r="B390" s="5" t="n"/>
       <c r="C390" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B390,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B390,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D390" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B390,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B390,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E390" s="8" t="n"/>
@@ -8038,11 +8037,11 @@
       <c r="A391" s="5" t="n"/>
       <c r="B391" s="5" t="n"/>
       <c r="C391" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B391,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B391,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D391" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B391,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B391,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E391" s="8" t="n"/>
@@ -8057,11 +8056,11 @@
       <c r="A392" s="5" t="n"/>
       <c r="B392" s="5" t="n"/>
       <c r="C392" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B392,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B392,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D392" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B392,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B392,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E392" s="8" t="n"/>
@@ -8076,11 +8075,11 @@
       <c r="A393" s="5" t="n"/>
       <c r="B393" s="5" t="n"/>
       <c r="C393" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B393,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B393,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D393" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B393,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B393,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E393" s="8" t="n"/>
@@ -8095,11 +8094,11 @@
       <c r="A394" s="5" t="n"/>
       <c r="B394" s="5" t="n"/>
       <c r="C394" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B394,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B394,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D394" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B394,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B394,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E394" s="8" t="n"/>
@@ -8114,11 +8113,11 @@
       <c r="A395" s="5" t="n"/>
       <c r="B395" s="5" t="n"/>
       <c r="C395" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B395,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B395,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D395" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B395,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B395,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E395" s="8" t="n"/>
@@ -8133,11 +8132,11 @@
       <c r="A396" s="5" t="n"/>
       <c r="B396" s="5" t="n"/>
       <c r="C396" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B396,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B396,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D396" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B396,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B396,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E396" s="8" t="n"/>
@@ -8152,11 +8151,11 @@
       <c r="A397" s="5" t="n"/>
       <c r="B397" s="5" t="n"/>
       <c r="C397" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B397,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B397,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D397" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B397,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B397,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E397" s="8" t="n"/>
@@ -8171,11 +8170,11 @@
       <c r="A398" s="5" t="n"/>
       <c r="B398" s="5" t="n"/>
       <c r="C398" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B398,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B398,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D398" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B398,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B398,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E398" s="8" t="n"/>
@@ -8190,11 +8189,11 @@
       <c r="A399" s="5" t="n"/>
       <c r="B399" s="5" t="n"/>
       <c r="C399" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B399,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B399,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D399" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B399,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B399,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E399" s="8" t="n"/>
@@ -8209,11 +8208,11 @@
       <c r="A400" s="5" t="n"/>
       <c r="B400" s="5" t="n"/>
       <c r="C400" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B400,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B400,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D400" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B400,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B400,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E400" s="8" t="n"/>
@@ -8228,11 +8227,11 @@
       <c r="A401" s="5" t="n"/>
       <c r="B401" s="5" t="n"/>
       <c r="C401" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B401,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B401,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D401" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B401,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B401,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E401" s="8" t="n"/>
@@ -8247,11 +8246,11 @@
       <c r="A402" s="5" t="n"/>
       <c r="B402" s="5" t="n"/>
       <c r="C402" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$135,MATCH(B402,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$138,MATCH(B402,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="D402" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$135,MATCH(B402,Productos!$A$2:$A$135,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$138,MATCH(B402,Productos!$A$2:$A$138,0)),"")</f>
         <v/>
       </c>
       <c r="E402" s="8" t="n"/>
@@ -8292,7 +8291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ34"/>
+  <dimension ref="A1:AI33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8338,140 +8337,135 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>CUNIPIC</t>
+          <t>DOG CHOW</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>DOG CHOW</t>
+          <t>EMERALD</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>EMERALD</t>
+          <t>ESBILAC</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>ESBILAC</t>
+          <t>FANCY FEAST</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>FANCY FEAST</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>GATI</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>GATI</t>
+          <t>GENÉRICO (reempaque)</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>GENÉRICO (reempaque)</t>
+          <t>HIGGINS</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>HIGGINS</t>
+          <t>KAYTEE</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>KAYTEE</t>
+          <t>KORDON</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>KORDON</t>
+          <t>MIMADOS</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>MIMADOS</t>
+          <t>MIRRAPEL</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>MIRRAPEL</t>
+          <t>NUTRECAN</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>NUTRECAN</t>
+          <t>NUTRISOURCE</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>NUTRISOURCE</t>
+          <t>PERKY PET</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>PERKY PET</t>
+          <t>PET FACTORY</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>PET FACTORY</t>
+          <t>PRO PET</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>PRO PET</t>
+          <t>PRO PLAN</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>PRO PLAN</t>
+          <t>PURINA</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>PURINA</t>
+          <t>RED BARN</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>RED BARN</t>
+          <t>RUSH DIRECT</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>RUSH DIRECT</t>
+          <t>SMARTBONES</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>SMARTBONES</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPRA</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>TETRA</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>TRIUMPH</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
-        <is>
-          <t>TRIUMPH</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
         <is>
           <t>ZOO MED</t>
         </is>
@@ -8519,140 +8513,135 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>D CUNIPIC PERICO AUSTRALIANO 3KG · 93501850000</t>
+          <t>DOG CHOW ADULTO 2KG · 93512370000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>DOG CHOW ADULTO 2KG · 93512370000</t>
+          <t>EP SNACK DENTAL SALMON P/GATO 3OZ · 93509220000</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>EP SNACK DENTAL SALMON P/GATO 3OZ · 93509220000</t>
+          <t>ESBILAC LECHE EN POLVO 12 ONZ · 90311050000</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ESBILAC LECHE EN POLVO 12 ONZ · 90311050000</t>
+          <t>FANCY FEAST CHUNCKY POLLO 3 OZ · 93509350000</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>FANCY FEAST CHUNCKY POLLO 3 OZ · 93509350000</t>
+          <t>FELIX CARNE GATITOS 85G MX · 90038450000</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>FELIX CARNE GATITOS 85G MX · 90038450000</t>
+          <t>GATI ATUN 2.2LB · 93519180000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GATI ATUN 2.2LB · 93519180000</t>
+          <t>SEM ALPISTE  1 LB · 90426180000</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SEM ALPISTE  1 LB · 90426180000</t>
+          <t>HIGGINS SUNBURST ALIM COBAYOS 3LB · 93510430000</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>HIGGINS SUNBURST ALIM COBAYOS 3LB · 93510430000</t>
+          <t>KT ALIM. SUPREME CONEJO 5 LB · 90405210000</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>KT ALIM. SUPREME CONEJO 5 LB · 90405210000</t>
+          <t>KORDON VITAMINAS AVES GRANDES 2 OZ · 90720740000</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>KORDON VITAMINAS AVES GRANDES 2 OZ · 90720740000</t>
+          <t>MIMADOS ADULTO 18KG · 90409680000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTO 18KG · 90409680000</t>
+          <t>MIRRAPEL CACHORROS 120 ML · 90322660000</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>MIRRAPEL CACHORROS 120 ML · 90322660000</t>
+          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 2KG · 93510820000</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 2KG · 93510820000</t>
+          <t>NS CHOICE CACHORR POLLO CEBADA 5LB · 90034090000</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>NS CHOICE CACHORR POLLO CEBADA 5LB · 90034090000</t>
+          <t>NECTAR PARA COLIBRI 240 · 93502370000</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>NECTAR PARA COLIBRI 240 · 93502370000</t>
+          <t>PF HUESO/ CARNAZA SABOR M.MANI 8-9IN · 93514280000</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR M.MANI 8-9IN · 93514280000</t>
+          <t>PRO PET 1.5KG ADULTO · 93500000100</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>PRO PET 1.5KG ADULTO · 93500000100</t>
+          <t>PP ADULTO SENSITIVE SKIN  3KG · 93510171000</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>PP ADULTO SENSITIVE SKIN  3KG · 93510171000</t>
+          <t>3 PACK FELIX SURTIDO (3X156G) · 90040920000</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>3 PACK FELIX SURTIDO (3X156G) · 90040920000</t>
+          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
+          <t>D RD SNACK POPN BITES PESCAD P/GATOS · 93513040000</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>D RD SNACK POPN BITES PESCAD P/GATOS · 93513040000</t>
+          <t>D SB SMARTSTICKS DENTAL 5UD · 93519250000</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>D SB SMARTSTICKS DENTAL 5UD · 93519250000</t>
+          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
+          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
+          <t>D TETRA REPTOMIN 1.94 OZ · 90410040000</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>D TETRA REPTOMIN 1.94 OZ · 90410040000</t>
+          <t>D TRIUMPH LATA POLLO ARROZ VEG 13.2OZ · 90412960000</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
-        <is>
-          <t>D TRIUMPH LATA POLLO ARROZ VEG 13.2OZ · 90412960000</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
         <is>
           <t>D ZM ALIMENTO EN BLOQUE P TORTUGAS 5 · 93517490000</t>
         </is>
@@ -8688,102 +8677,102 @@
           <t>CAT CHOW DEFENSE PLUS PESCADO 1.5KG · 90408400000</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>DOG CHOW CACHORRO RAZA PEQUENA 2KG · 93512550000</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ESBILAC PAPILLA P CACHORROS 14 OZ. · 90312680000</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ESBILAC PAPILLA P CACHORROS 14 OZ. · 90312680000</t>
+          <t>FANCY FEAST CHUNKY PAVO 3 OZ · 93509340000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>FANCY FEAST CHUNKY PAVO 3 OZ · 93509340000</t>
+          <t>FELIX DELICIAS DE LA GRANJA ADULTO 1KG M · 90038530000</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>FELIX DELICIAS DE LA GRANJA ADULTO 1KG M · 90038530000</t>
+          <t>GATI GATITOS 2.2LB · 93519200000</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GATI GATITOS 2.2LB · 93519200000</t>
+          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
           <t>HIGGINS SUNBURST ALIM P CONEJOS 3LB · 93510440000</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>MIMADOS ADULTO 2KG · 90400360000</t>
+        </is>
+      </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTO 2KG · 90400360000</t>
+          <t>MIRRAPEL CACHORROS 236 ML · 90322670000</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>MIRRAPEL CACHORROS 236 ML · 90322670000</t>
+          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
           <t>NS CHOICE CACHORR POLLO CEBADA 5OZ MUEST · 90034110000</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>PF HUESO/ CARNAZA SABOR POLLO 8-9IN · 93514230000</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR POLLO 8-9IN · 93514230000</t>
+          <t>PRO PET 1.5KG CACHORRO · 93500000200</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>PRO PET 1.5KG CACHORRO · 93500000200</t>
+          <t>PP PROPLAN CACHORRO RZ PQNA 1KG · 93520160000</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORROS RZ MD OPTI 3KG · 93520130000</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
           <t>4 PACK FELIX SURTIDO (4X85G) · 90040930000</t>
         </is>
       </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>D SB SMARTSTICKS POLLO 5UD · 93519230000</t>
+        </is>
+      </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>D SB SMARTSTICKS POLLO 5UD · 93519230000</t>
+          <t>ROCKY ADULTOS 1KG · 93500000342</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 1KG · 93500000342</t>
+          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
           <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>ZM CALCIO GDE CON VEGETALES P/AVES · 93503050000</t>
         </is>
@@ -8809,87 +8798,87 @@
           <t>ASCAN ADULTOS 1KG · 93513390000</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>DOG CHOW CACHORROS POLLO POUCH 100G MX · 90038330000</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>FANCY FEAST TRUCHA 3 OZ · 93509370000</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>FANCY FEAST TRUCHA 3 OZ · 93509370000</t>
+          <t>FELIX DELICIAS DEL MAR ADULTO 1KG MX · 90038540000</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>FELIX MEGAMIX ADULTO 500G MX · 90038550000</t>
+          <t>GATI PESCADO 2.2LB · 93519140000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>GATI PESCADO 2.2LB · 93519140000</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
           <t>SEMILLAS DE GIRASOL JUMBO 454GR · 90426190000</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>MIMADOS ADULTOS 4KG · 93513340000</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTOS 4KG · 93513340000</t>
+          <t>MIRRAPEL OLEOSO 120 ML · 90322650000</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>MIRRAPEL OLEOSO 120 ML · 90322650000</t>
+          <t>SOLLA NUTRECAN ADULTO RM Y RG 800GR · 93505910000</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTO RM Y RG 800GR · 93505910000</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
           <t>NS CHOICE CARNE Y CEBADA 5LB · 90033960000</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>PF HUESO/CARNAZA SABOR CARNE 4IN-5IN · 93514210000</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>PF HUESO/CARNAZA SABOR CARNE 4IN-5IN · 93514210000</t>
+          <t>PRO PET 4KG ADULTO · 93500000300</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>PRO PET 4KG ADULTO · 93500000300</t>
+          <t>PP PROPLAN CACHORROS RZ MD OPTI 3KG · 93520130000</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>PROPLAN ADULTO BOCADOS PEQUENOS 1KG MX · 90038590000</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
           <t>CATCHOW GATITO DEFENSE PLUS 1.5KG · 93520020000</t>
         </is>
       </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>ROCKY ADULTOS 500G · 93500000341</t>
+        </is>
+      </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 500G · 93500000341</t>
+          <t>SUPRA ADULTO 18KG · 93508890000</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 18KG · 93508890000</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
           <t>TETRA BETTAMIN .81OZ  23GR · 90410310000</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>ZM CALCIO PQNO CON VEGETALES P/AVES · 93503060000</t>
         </is>
@@ -8915,82 +8904,82 @@
           <t>ASCAN CACHORROS 1KG · 93513380000</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>DOG CHOW CARNE POUCH 100G MX · 90038300000</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>FELIX GATITOS 500G MX · 90038510000</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>FELIX PATE PESCADO Y ATUN 156G · 93502640000</t>
+          <t>GATI POLLO 2.2LB · 93519130000</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GATI POLLO 2.2LB · 93519130000</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
           <t>SEMILLAS DE GIRASOL JUMBO 5 LB · 90426200000</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>MIMADOS CACHORROS 4KG · 93513280000</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>MIMADOS CACHORROS 4KG · 93513280000</t>
+          <t>MIRRAPEL PET POLVO 300 g · 90301720000</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>MIRRAPEL PET POLVO 300 g · 90301720000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 16KG · 93505950000</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 16KG · 93505950000</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
           <t>NS CHOICE CARNE Y CEBADA 5OZ MUESTRA · 90033980000</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>PF HUESO/CARNAZA SABOR POLLO 4IN-5IN · 93514260000</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>PF HUESO/CARNAZA SABOR POLLO 4IN-5IN · 93514260000</t>
+          <t>PRO PET 4KG CACHORRO · 93500000400</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>PRO PET 4KG CACHORRO · 93500000400</t>
+          <t>PROPLAN ADULTO BOCADOS PEQUENOS 1KG MX · 90038590000</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>PROPLAN ADULTO RZ MED OPTIHEALTH 3 · 93520000000</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
           <t>PRO PLAN CACHORRO RAZA PEQUEÑA 4x3.5kgMX · 90026950000</t>
         </is>
       </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
+        </is>
+      </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
+          <t>SUPRA ADULTO 30KG · 93508900000</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 30KG · 93508900000</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
           <t>TETRA HOJUELA GOLDFISH 2.2OZ · 90409670000</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>ZM MICRO PELLET P/BETTA 0.12OZ · 93514830000</t>
         </is>
@@ -9007,42 +8996,47 @@
           <t>MARCA_5</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>FELIX PATE SALMON 156G · 93502650000</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>FELIX MEGAMIX ADULTO 1KG MX · 90038520000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
+        </is>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
           <t>NS CHOICE LATA CACHOR POLLO ARROZ 12.3OZ · 90034200000</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>PF ROLLO/ CARNAZA SABOR POLLO 10IN · 93514240000</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>PROPLAN ADULTO RZ MED OPTIHEALTH 3 · 93520000000</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
         <is>
           <t>PURINA FELIX ATUN EN SALSA 85G · 93516230000</t>
         </is>
       </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>SUPRA ADULTO 4KG · 93508870000</t>
+        </is>
+      </c>
       <c r="AG6" t="inlineStr">
-        <is>
-          <t>SUPRA ADULTO 4KG · 93508870000</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
         <is>
           <t>TETRA HOJUELAS GOLDFISH .42OZ · 90409900000</t>
         </is>
@@ -9051,7 +9045,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CUNIPIC</t>
+          <t>DOG CHOW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -9059,32 +9053,37 @@
           <t>MARCA_6</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>FELIX MEGAMIX ADULTO 500G MX · 90038550000</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
           <t>NS CHOICE LATA CARNE Y CEBADA 12.3OZ · 90034180000</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>PF TRENZA/CARNAZA SABOR NATURAL 7IN · 93517760000</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>PURINA FELIX PAVO EN SALSA 85G · 93516200000</t>
         </is>
       </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>SUPRA CACHORRO 1.5KG · 93508910000</t>
+        </is>
+      </c>
       <c r="AG7" t="inlineStr">
-        <is>
-          <t>SUPRA CACHORRO 1.5KG · 93508910000</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
         <is>
           <t>TETRA HOJUELAS GOLDFISH 3.53OZ · 90409910000</t>
         </is>
@@ -9093,7 +9092,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DOG CHOW</t>
+          <t>EMERALD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -9101,27 +9100,32 @@
           <t>MARCA_7</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>FELIX PATE PESCADO Y ATUN 156G · 93502640000</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
           <t>NS CHOICE LATA PAVO Y CEBADA 12.3OZ · 90034290000</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>PURINA FELIX PESCADO EN SALSA 85G · 93516210000</t>
         </is>
       </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>SUPRA CACHORRO 18KG · 93508940000</t>
+        </is>
+      </c>
       <c r="AG8" t="inlineStr">
-        <is>
-          <t>SUPRA CACHORRO 18KG · 93508940000</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
         <is>
           <t>TETRA HOJUELAS TROPICAL 0.42OZ · 90409920000</t>
         </is>
@@ -9130,7 +9134,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EMERALD</t>
+          <t>ESBILAC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -9138,22 +9142,27 @@
           <t>MARCA_8</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>FELIX PATE SALMON 156G · 93502650000</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 8KG · 93505940000</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 8KG · 93505940000</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
           <t>NS CHOICE LATA POLLO Y CEBADA 12.3OZ · 90034190000</t>
         </is>
       </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>SUPRA CACHORRO 30KG · 93508950000</t>
+        </is>
+      </c>
       <c r="AG9" t="inlineStr">
-        <is>
-          <t>SUPRA CACHORRO 30KG · 93508950000</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
         <is>
           <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
         </is>
@@ -9162,7 +9171,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ESBILAC</t>
+          <t>FANCY FEAST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -9170,17 +9179,17 @@
           <t>MARCA_9</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
           <t>NS CHOICE PAVO Y CEBADA 5LB · 90034130000</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>SUPRA CACHORRO 4KG · 93508920000</t>
         </is>
@@ -9189,7 +9198,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FANCY FEAST</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -9197,12 +9206,12 @@
           <t>MARCA_10</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
         <is>
           <t>NS CHOICE PESCADO Y ARROZ 5LB · 90034160000</t>
         </is>
@@ -9211,7 +9220,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>GATI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -9219,12 +9228,12 @@
           <t>MARCA_11</t>
         </is>
       </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN BABIES 8 KG · 90410970000</t>
+        </is>
+      </c>
       <c r="V12" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN BABIES 8 KG · 90410970000</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
         <is>
           <t>NS CHOICE POLLO Y CEBADA 5LB · 90033990000</t>
         </is>
@@ -9233,7 +9242,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GATI</t>
+          <t>GENÉRICO (reempaque)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -9241,12 +9250,12 @@
           <t>MARCA_12</t>
         </is>
       </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
+        </is>
+      </c>
       <c r="V13" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
         <is>
           <t>NS CHOICE POLLO Y CEBADA 5OZ MUESTRA · 90034020000</t>
         </is>
@@ -9255,7 +9264,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GENÉRICO (reempaque)</t>
+          <t>HIGGINS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -9263,12 +9272,12 @@
           <t>MARCA_13</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN CAMPO 16KG · 90410820000</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN CAMPO 16KG · 90410820000</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
         <is>
           <t>NS CHOICE R GDE POLLO Y CEBADA 5OZ MUEST · 90034060000</t>
         </is>
@@ -9277,7 +9286,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HIGGINS</t>
+          <t>KAYTEE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9285,12 +9294,12 @@
           <t>MARCA_14</t>
         </is>
       </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
         <is>
           <t>NS CHOICE SNACK GRILLERS CARNE 12OZ · 90034210000</t>
         </is>
@@ -9299,7 +9308,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KAYTEE</t>
+          <t>KORDON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -9307,12 +9316,12 @@
           <t>MARCA_15</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN CAMPO 2KG · 90415960000</t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN CAMPO 2KG · 90415960000</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
         <is>
           <t>NS CHOICE SNACK GRILLERS PAVO 12OZ · 90034250000</t>
         </is>
@@ -9321,7 +9330,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KORDON</t>
+          <t>MIMADOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -9329,12 +9338,12 @@
           <t>MARCA_16</t>
         </is>
       </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
         <is>
           <t>NS CHOICE SNACK GRILLERS POLLO 12OZ · 90034230000</t>
         </is>
@@ -9343,7 +9352,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MIMADOS</t>
+          <t>MIRRAPEL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -9351,12 +9360,12 @@
           <t>MARCA_17</t>
         </is>
       </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
+        </is>
+      </c>
       <c r="V18" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
         <is>
           <t>NS LATA GF PERRO POLLO 13OZ · 93500000472</t>
         </is>
@@ -9365,7 +9374,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MIRRAPEL</t>
+          <t>NUTRECAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9373,7 +9382,7 @@
           <t>MARCA_18</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
         </is>
@@ -9382,7 +9391,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NUTRECAN</t>
+          <t>NUTRISOURCE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9394,7 +9403,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NUTRISOURCE</t>
+          <t>PERKY PET</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9406,7 +9415,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PERKY PET</t>
+          <t>PET FACTORY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9418,7 +9427,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PET FACTORY</t>
+          <t>PRO PET</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9430,7 +9439,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PRO PET</t>
+          <t>PRO PLAN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -9442,7 +9451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PRO PLAN</t>
+          <t>PURINA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -9454,7 +9463,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PURINA</t>
+          <t>RED BARN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -9466,7 +9475,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RED BARN</t>
+          <t>RUSH DIRECT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -9478,7 +9487,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RUSH DIRECT</t>
+          <t>SMARTBONES</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -9490,7 +9499,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SMARTBONES</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -9502,7 +9511,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPRA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -9514,7 +9523,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>TETRA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -9526,7 +9535,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>TRIUMPH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -9538,24 +9547,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TRIUMPH</t>
+          <t>ZOO MED</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>MARCA_32</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>ZOO MED</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>MARCA_33</t>
         </is>
       </c>
     </row>
@@ -9570,7 +9567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D139"/>
+  <dimension ref="A1:D142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9798,32 +9795,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D CUNIPIC PERICO AUSTRALIANO 3KG · 93501850000</t>
+          <t>DOG CHOW ADULTO 2KG · 93512370000</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>93501850000</t>
+          <t>93512370000</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CUNIPIC</t>
+          <t>DOG CHOW</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DOG CHOW ADULTO 2KG · 93512370000</t>
+          <t>DOG CHOW CACHORRO RAZA PEQUENA 2KG · 93512550000</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>93512370000</t>
+          <t>93512550000</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -9838,16 +9835,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DOG CHOW CACHORRO RAZA PEQUENA 2KG · 93512550000</t>
+          <t>DOG CHOW CACHORROS POLLO POUCH 100G MX · 90038330000</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>93512550000</t>
+          <t>90038330000</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -9858,12 +9855,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DOG CHOW CACHORROS POLLO POUCH 100G MX · 90038330000</t>
+          <t>DOG CHOW CARNE POUCH 100G MX · 90038300000</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90038330000</t>
+          <t>90038300000</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -9878,56 +9875,56 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DOG CHOW CARNE POUCH 100G MX · 90038300000</t>
+          <t>EP SNACK DENTAL SALMON P/GATO 3OZ · 93509220000</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90038300000</t>
+          <t>93509220000</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DOG CHOW</t>
+          <t>EMERALD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EP SNACK DENTAL SALMON P/GATO 3OZ · 93509220000</t>
+          <t>ESBILAC LECHE EN POLVO 12 ONZ · 90311050000</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>93509220000</t>
+          <t>90311050000</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EMERALD</t>
+          <t>ESBILAC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ESBILAC LECHE EN POLVO 12 ONZ · 90311050000</t>
+          <t>ESBILAC PAPILLA P CACHORROS 14 OZ. · 90312680000</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90311050000</t>
+          <t>90312680000</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -9938,36 +9935,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ESBILAC PAPILLA P CACHORROS 14 OZ. · 90312680000</t>
+          <t>FANCY FEAST CHUNCKY POLLO 3 OZ · 93509350000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90312680000</t>
+          <t>93509350000</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ESBILAC</t>
+          <t>FANCY FEAST</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FANCY FEAST CHUNCKY POLLO 3 OZ · 93509350000</t>
+          <t>FANCY FEAST CHUNKY PAVO 3 OZ · 93509340000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>93509350000</t>
+          <t>93509340000</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -9978,16 +9975,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FANCY FEAST CHUNKY PAVO 3 OZ · 93509340000</t>
+          <t>FANCY FEAST TRUCHA 3 OZ · 93509370000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>93509340000</t>
+          <t>93509370000</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -9998,36 +9995,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FANCY FEAST TRUCHA 3 OZ · 93509370000</t>
+          <t>FELIX CARNE GATITOS 85G MX · 90038450000</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>93509370000</t>
+          <t>90038450000</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FANCY FEAST</t>
+          <t>FELIX</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FELIX CARNE GATITOS 85G MX · 90038450000</t>
+          <t>FELIX DELICIAS DE LA GRANJA ADULTO 1KG M · 90038530000</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90038450000</t>
+          <t>90038530000</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -10038,16 +10035,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FELIX DELICIAS DE LA GRANJA ADULTO 1KG M · 90038530000</t>
+          <t>FELIX DELICIAS DEL MAR ADULTO 1KG MX · 90038540000</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>90038530000</t>
+          <t>90038540000</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -10058,16 +10055,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FELIX MEGAMIX ADULTO 500G MX · 90038550000</t>
+          <t>FELIX GATITOS 500G MX · 90038510000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90038550000</t>
+          <t>90038510000</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -10078,16 +10075,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FELIX PATE PESCADO Y ATUN 156G · 93502640000</t>
+          <t>FELIX MEGAMIX ADULTO 1KG MX · 90038520000</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>93502640000</t>
+          <t>90038520000</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -10098,16 +10095,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FELIX PATE SALMON 156G · 93502650000</t>
+          <t>FELIX MEGAMIX ADULTO 500G MX · 90038550000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>93502650000</t>
+          <t>90038550000</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -10118,56 +10115,56 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GATI ATUN 2.2LB · 93519180000</t>
+          <t>FELIX PATE PESCADO Y ATUN 156G · 93502640000</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>93519180000</t>
+          <t>93502640000</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GATI</t>
+          <t>FELIX</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GATI GATITOS 2.2LB · 93519200000</t>
+          <t>FELIX PATE SALMON 156G · 93502650000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>93519200000</t>
+          <t>93502650000</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GATI</t>
+          <t>FELIX</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GATI PESCADO 2.2LB · 93519140000</t>
+          <t>GATI ATUN 2.2LB · 93519180000</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>93519140000</t>
+          <t>93519180000</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -10178,16 +10175,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GATI POLLO 2.2LB · 93519130000</t>
+          <t>GATI GATITOS 2.2LB · 93519200000</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>93519130000</t>
+          <t>93519200000</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -10198,56 +10195,56 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SEM ALPISTE  1 LB · 90426180000</t>
+          <t>GATI PESCADO 2.2LB · 93519140000</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>90426180000</t>
+          <t>93519140000</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GENÉRICO (reempaque)</t>
+          <t>GATI</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
+          <t>GATI POLLO 2.2LB · 93519130000</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>90402150000</t>
+          <t>93519130000</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GENÉRICO (reempaque)</t>
+          <t>GATI</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SEMILLAS DE GIRASOL JUMBO 454GR · 90426190000</t>
+          <t>SEM ALPISTE  1 LB · 90426180000</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>90426190000</t>
+          <t>90426180000</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -10258,16 +10255,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SEMILLAS DE GIRASOL JUMBO 5 LB · 90426200000</t>
+          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>90426200000</t>
+          <t>90402150000</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -10278,16 +10275,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
+          <t>SEMILLAS DE GIRASOL JUMBO 454GR · 90426190000</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>93500750000</t>
+          <t>90426190000</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -10298,72 +10295,72 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HIGGINS SUNBURST ALIM COBAYOS 3LB · 93510430000</t>
+          <t>SEMILLAS DE GIRASOL JUMBO 5 LB · 90426200000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>93510430000</t>
+          <t>90426200000</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>HIGGINS</t>
+          <t>GENÉRICO (reempaque)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HIGGINS SUNBURST ALIM P CONEJOS 3LB · 93510440000</t>
+          <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>93510440000</t>
+          <t>93500750000</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HIGGINS</t>
+          <t>GENÉRICO (reempaque)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KT ALIM. SUPREME CONEJO 5 LB · 90405210000</t>
+          <t>HIGGINS SUNBURST ALIM COBAYOS 3LB · 93510430000</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>90405210000</t>
+          <t>93510430000</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KAYTEE</t>
+          <t>HIGGINS</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KORDON VITAMINAS AVES GRANDES 2 OZ · 90720740000</t>
+          <t>HIGGINS SUNBURST ALIM P CONEJOS 3LB · 93510440000</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>90720740000</t>
+          <t>93510440000</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -10371,63 +10368,63 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KORDON</t>
+          <t>HIGGINS</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTO 18KG · 90409680000</t>
+          <t>KT ALIM. SUPREME CONEJO 5 LB · 90405210000</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>90409680000</t>
+          <t>90405210000</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MIMADOS</t>
+          <t>KAYTEE</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTO 2KG · 90400360000</t>
+          <t>KORDON VITAMINAS AVES GRANDES 2 OZ · 90720740000</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>90400360000</t>
+          <t>90720740000</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MIMADOS</t>
+          <t>KORDON</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTOS 4KG · 93513340000</t>
+          <t>MIMADOS ADULTO 18KG · 90409680000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>93513340000</t>
+          <t>90409680000</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -10438,16 +10435,16 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MIMADOS CACHORROS 4KG · 93513280000</t>
+          <t>MIMADOS ADULTO 2KG · 90400360000</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>93513280000</t>
+          <t>90400360000</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -10458,56 +10455,56 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MIRRAPEL CACHORROS 120 ML · 90322660000</t>
+          <t>MIMADOS ADULTOS 4KG · 93513340000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>90322660000</t>
+          <t>93513340000</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MIRRAPEL</t>
+          <t>MIMADOS</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MIRRAPEL CACHORROS 236 ML · 90322670000</t>
+          <t>MIMADOS CACHORROS 4KG · 93513280000</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>90322670000</t>
+          <t>93513280000</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MIRRAPEL</t>
+          <t>MIMADOS</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MIRRAPEL OLEOSO 120 ML · 90322650000</t>
+          <t>MIRRAPEL CACHORROS 120 ML · 90322660000</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>90322650000</t>
+          <t>90322660000</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -10518,16 +10515,16 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MIRRAPEL PET POLVO 300 g · 90301720000</t>
+          <t>MIRRAPEL CACHORROS 236 ML · 90322670000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>90301720000</t>
+          <t>90322670000</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -10538,56 +10535,56 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 2KG · 93510820000</t>
+          <t>MIRRAPEL OLEOSO 120 ML · 90322650000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>93510820000</t>
+          <t>90322650000</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NUTRECAN</t>
+          <t>MIRRAPEL</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
+          <t>MIRRAPEL PET POLVO 300 g · 90301720000</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>93510810000</t>
+          <t>90301720000</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NUTRECAN</t>
+          <t>MIRRAPEL</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTO RM Y RG 800GR · 93505910000</t>
+          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 2KG · 93510820000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>93505910000</t>
+          <t>93510820000</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>134</v>
+        <v>6</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -10598,16 +10595,16 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 16KG · 93505950000</t>
+          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>93505950000</t>
+          <t>93510810000</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -10618,16 +10615,16 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
+          <t>SOLLA NUTRECAN ADULTO RM Y RG 800GR · 93505910000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>93505960000</t>
+          <t>93505910000</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>134</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -10638,16 +10635,16 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 16KG · 93505950000</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>93505920000</t>
+          <t>93505950000</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -10658,16 +10655,16 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>93505930000</t>
+          <t>93505960000</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -10678,16 +10675,16 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 8KG · 93505940000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>93505940000</t>
+          <t>93505920000</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -10698,16 +10695,16 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>90410720000</t>
+          <t>93505930000</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -10718,16 +10715,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 8KG · 93505940000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>90410730000</t>
+          <t>93505940000</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -10738,16 +10735,16 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 8 KG · 90410970000</t>
+          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>90410970000</t>
+          <t>90410720000</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -10758,16 +10755,16 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
+          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>90410800000</t>
+          <t>90410730000</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -10778,16 +10775,16 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 16KG · 90410820000</t>
+          <t>SOLLA NUTRECAN BABIES 8 KG · 90410970000</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>90410820000</t>
+          <t>90410970000</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -10798,16 +10795,16 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
+          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>90410830000</t>
+          <t>90410800000</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -10818,16 +10815,16 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 2KG · 90415960000</t>
+          <t>SOLLA NUTRECAN CAMPO 16KG · 90410820000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>90415960000</t>
+          <t>90410820000</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -10838,12 +10835,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
+          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>90410810000</t>
+          <t>90410830000</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -10858,16 +10855,16 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
+          <t>SOLLA NUTRECAN CAMPO 2KG · 90415960000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>93510840000</t>
+          <t>90415960000</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -10878,16 +10875,16 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
+          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>93510830000</t>
+          <t>90410810000</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -10898,52 +10895,52 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NS CHOICE CACHORR POLLO CEBADA 5LB · 90034090000</t>
+          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>90034090000</t>
+          <t>93510840000</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NUTRISOURCE</t>
+          <t>NUTRECAN</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>NS CHOICE CACHORR POLLO CEBADA 5OZ MUEST · 90034110000</t>
+          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>90034110000</t>
+          <t>93510830000</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NUTRISOURCE</t>
+          <t>NUTRECAN</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NS CHOICE CARNE Y CEBADA 5LB · 90033960000</t>
+          <t>NS CHOICE CACHORR POLLO CEBADA 5LB · 90034090000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>90033960000</t>
+          <t>90034090000</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -10958,16 +10955,16 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NS CHOICE CARNE Y CEBADA 5OZ MUESTRA · 90033980000</t>
+          <t>NS CHOICE CACHORR POLLO CEBADA 5OZ MUEST · 90034110000</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>90033980000</t>
+          <t>90034110000</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -10978,16 +10975,16 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA CACHOR POLLO ARROZ 12.3OZ · 90034200000</t>
+          <t>NS CHOICE CARNE Y CEBADA 5LB · 90033960000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>90034200000</t>
+          <t>90033960000</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10998,16 +10995,16 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA CARNE Y CEBADA 12.3OZ · 90034180000</t>
+          <t>NS CHOICE CARNE Y CEBADA 5OZ MUESTRA · 90033980000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>90034180000</t>
+          <t>90033980000</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11018,16 +11015,16 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA PAVO Y CEBADA 12.3OZ · 90034290000</t>
+          <t>NS CHOICE LATA CACHOR POLLO ARROZ 12.3OZ · 90034200000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>90034290000</t>
+          <t>90034200000</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -11038,16 +11035,16 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA POLLO Y CEBADA 12.3OZ · 90034190000</t>
+          <t>NS CHOICE LATA CARNE Y CEBADA 12.3OZ · 90034180000</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>90034190000</t>
+          <t>90034180000</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -11058,16 +11055,16 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NS CHOICE PAVO Y CEBADA 5LB · 90034130000</t>
+          <t>NS CHOICE LATA PAVO Y CEBADA 12.3OZ · 90034290000</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>90034130000</t>
+          <t>90034290000</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -11078,16 +11075,16 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>NS CHOICE PESCADO Y ARROZ 5LB · 90034160000</t>
+          <t>NS CHOICE LATA POLLO Y CEBADA 12.3OZ · 90034190000</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>90034160000</t>
+          <t>90034190000</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -11098,12 +11095,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>NS CHOICE POLLO Y CEBADA 5LB · 90033990000</t>
+          <t>NS CHOICE PAVO Y CEBADA 5LB · 90034130000</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>90033990000</t>
+          <t>90034130000</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -11118,16 +11115,16 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>NS CHOICE POLLO Y CEBADA 5OZ MUESTRA · 90034020000</t>
+          <t>NS CHOICE PESCADO Y ARROZ 5LB · 90034160000</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>90034020000</t>
+          <t>90034160000</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -11138,16 +11135,16 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>NS CHOICE R GDE POLLO Y CEBADA 5OZ MUEST · 90034060000</t>
+          <t>NS CHOICE POLLO Y CEBADA 5LB · 90033990000</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>90034060000</t>
+          <t>90033990000</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11158,16 +11155,16 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>NS CHOICE SNACK GRILLERS CARNE 12OZ · 90034210000</t>
+          <t>NS CHOICE POLLO Y CEBADA 5OZ MUESTRA · 90034020000</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>90034210000</t>
+          <t>90034020000</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11178,16 +11175,16 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NS CHOICE SNACK GRILLERS PAVO 12OZ · 90034250000</t>
+          <t>NS CHOICE R GDE POLLO Y CEBADA 5OZ MUEST · 90034060000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>90034250000</t>
+          <t>90034060000</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11198,16 +11195,16 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NS CHOICE SNACK GRILLERS POLLO 12OZ · 90034230000</t>
+          <t>NS CHOICE SNACK GRILLERS CARNE 12OZ · 90034210000</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>90034230000</t>
+          <t>90034210000</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11218,16 +11215,16 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NS LATA GF PERRO POLLO 13OZ · 93500000472</t>
+          <t>NS CHOICE SNACK GRILLERS PAVO 12OZ · 90034250000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>93500000472</t>
+          <t>90034250000</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11238,76 +11235,76 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NECTAR PARA COLIBRI 240 · 93502370000</t>
+          <t>NS CHOICE SNACK GRILLERS POLLO 12OZ · 90034230000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>93502370000</t>
+          <t>90034230000</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>PERKY PET</t>
+          <t>NUTRISOURCE</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR M.MANI 8-9IN · 93514280000</t>
+          <t>NS LATA GF PERRO POLLO 13OZ · 93500000472</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>93514280000</t>
+          <t>93500000472</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>PET FACTORY</t>
+          <t>NUTRISOURCE</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PF HUESO/ CARNAZA SABOR POLLO 8-9IN · 93514230000</t>
+          <t>NECTAR PARA COLIBRI 240 · 93502370000</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>93514230000</t>
+          <t>93502370000</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>PET FACTORY</t>
+          <t>PERKY PET</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PF HUESO/CARNAZA SABOR CARNE 4IN-5IN · 93514210000</t>
+          <t>PF HUESO/ CARNAZA SABOR M.MANI 8-9IN · 93514280000</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>93514210000</t>
+          <t>93514280000</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11318,16 +11315,16 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PF HUESO/CARNAZA SABOR POLLO 4IN-5IN · 93514260000</t>
+          <t>PF HUESO/ CARNAZA SABOR POLLO 8-9IN · 93514230000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>93514260000</t>
+          <t>93514230000</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11338,16 +11335,16 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PF ROLLO/ CARNAZA SABOR POLLO 10IN · 93514240000</t>
+          <t>PF HUESO/CARNAZA SABOR CARNE 4IN-5IN · 93514210000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>93514240000</t>
+          <t>93514210000</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11358,16 +11355,16 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PF TRENZA/CARNAZA SABOR NATURAL 7IN · 93517760000</t>
+          <t>PF HUESO/CARNAZA SABOR POLLO 4IN-5IN · 93514260000</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>93517760000</t>
+          <t>93514260000</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11378,56 +11375,56 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PRO PET 1.5KG ADULTO · 93500000100</t>
+          <t>PF ROLLO/ CARNAZA SABOR POLLO 10IN · 93514240000</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>93500000100</t>
+          <t>93514240000</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>PRO PET</t>
+          <t>PET FACTORY</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PRO PET 1.5KG CACHORRO · 93500000200</t>
+          <t>PF TRENZA/CARNAZA SABOR NATURAL 7IN · 93517760000</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>93500000200</t>
+          <t>93517760000</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>PRO PET</t>
+          <t>PET FACTORY</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PRO PET 4KG ADULTO · 93500000300</t>
+          <t>PRO PET 1.5KG ADULTO · 93500000100</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>93500000300</t>
+          <t>93500000100</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11438,16 +11435,16 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PRO PET 4KG CACHORRO · 93500000400</t>
+          <t>PRO PET 1.5KG CACHORRO · 93500000200</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>93500000400</t>
+          <t>93500000200</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11458,56 +11455,56 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PP ADULTO SENSITIVE SKIN  3KG · 93510171000</t>
+          <t>PRO PET 4KG ADULTO · 93500000300</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>93510171000</t>
+          <t>93500000300</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>PRO PLAN</t>
+          <t>PRO PET</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PP PROPLAN CACHORROS RZ MD OPTI 3KG · 93520130000</t>
+          <t>PRO PET 4KG CACHORRO · 93500000400</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>93520130000</t>
+          <t>93500000400</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>PRO PLAN</t>
+          <t>PRO PET</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PROPLAN ADULTO BOCADOS PEQUENOS 1KG MX · 90038590000</t>
+          <t>PP ADULTO SENSITIVE SKIN  3KG · 93510171000</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>90038590000</t>
+          <t>93510171000</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11518,16 +11515,16 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PROPLAN ADULTO RZ MED OPTIHEALTH 3 · 93520000000</t>
+          <t>PP PROPLAN CACHORRO RZ PQNA 1KG · 93520160000</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>93520000000</t>
+          <t>93520160000</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11538,12 +11535,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3 PACK FELIX SURTIDO (3X156G) · 90040920000</t>
+          <t>PP PROPLAN CACHORROS RZ MD OPTI 3KG · 93520130000</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>90040920000</t>
+          <t>93520130000</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -11551,63 +11548,63 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>PURINA</t>
+          <t>PRO PLAN</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4 PACK FELIX SURTIDO (4X85G) · 90040930000</t>
+          <t>PROPLAN ADULTO BOCADOS PEQUENOS 1KG MX · 90038590000</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>90040930000</t>
+          <t>90038590000</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>PURINA</t>
+          <t>PRO PLAN</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CATCHOW GATITO DEFENSE PLUS 1.5KG · 93520020000</t>
+          <t>PROPLAN ADULTO RZ MED OPTIHEALTH 3 · 93520000000</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>93520020000</t>
+          <t>93520000000</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>PURINA</t>
+          <t>PRO PLAN</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PRO PLAN CACHORRO RAZA PEQUEÑA 4x3.5kgMX · 90026950000</t>
+          <t>3 PACK FELIX SURTIDO (3X156G) · 90040920000</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>90026950000</t>
+          <t>90040920000</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11618,16 +11615,16 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PURINA FELIX ATUN EN SALSA 85G · 93516230000</t>
+          <t>4 PACK FELIX SURTIDO (4X85G) · 90040930000</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>93516230000</t>
+          <t>90040930000</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11638,16 +11635,16 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PURINA FELIX PAVO EN SALSA 85G · 93516200000</t>
+          <t>CATCHOW GATITO DEFENSE PLUS 1.5KG · 93520020000</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>93516200000</t>
+          <t>93520020000</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11658,16 +11655,16 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PURINA FELIX PESCADO EN SALSA 85G · 93516210000</t>
+          <t>PRO PLAN CACHORRO RAZA PEQUEÑA 4x3.5kgMX · 90026950000</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>93516210000</t>
+          <t>90026950000</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11678,156 +11675,156 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
+          <t>PURINA FELIX ATUN EN SALSA 85G · 93516230000</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>93512180000</t>
+          <t>93516230000</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>RED BARN</t>
+          <t>PURINA</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>D RD SNACK POPN BITES PESCAD P/GATOS · 93513040000</t>
+          <t>PURINA FELIX PAVO EN SALSA 85G · 93516200000</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>93513040000</t>
+          <t>93516200000</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>RUSH DIRECT</t>
+          <t>PURINA</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>D SB SMARTSTICKS DENTAL 5UD · 93519250000</t>
+          <t>PURINA FELIX PESCADO EN SALSA 85G · 93516210000</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>93519250000</t>
+          <t>93516210000</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>SMARTBONES</t>
+          <t>PURINA</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>D SB SMARTSTICKS POLLO 5UD · 93519230000</t>
+          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>93519230000</t>
+          <t>93512180000</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>SMARTBONES</t>
+          <t>RED BARN</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
+          <t>D RD SNACK POPN BITES PESCAD P/GATOS · 93513040000</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>90022370000</t>
+          <t>93513040000</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>RUSH DIRECT</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 1KG · 93500000342</t>
+          <t>D SB SMARTSTICKS DENTAL 5UD · 93519250000</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>93500000342</t>
+          <t>93519250000</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SMARTBONES</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 500G · 93500000341</t>
+          <t>D SB SMARTSTICKS POLLO 5UD · 93519230000</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>93500000341</t>
+          <t>93519230000</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SMARTBONES</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
+          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>93511670000</t>
+          <t>90022370000</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11838,76 +11835,76 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
+          <t>ROCKY ADULTOS 1KG · 93500000342</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>93509320000</t>
+          <t>93500000342</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
+          <t>ROCKY ADULTOS 500G · 93500000341</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>93508860000</t>
+          <t>93500000341</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 18KG · 93508890000</t>
+          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>93508890000</t>
+          <t>93511670000</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 30KG · 93508900000</t>
+          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>93508900000</t>
+          <t>93509320000</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11918,16 +11915,16 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 4KG · 93508870000</t>
+          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>93508870000</t>
+          <t>93508860000</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11938,16 +11935,16 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 1.5KG · 93508910000</t>
+          <t>SUPRA ADULTO 18KG · 93508890000</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>93508910000</t>
+          <t>93508890000</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11958,16 +11955,16 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 18KG · 93508940000</t>
+          <t>SUPRA ADULTO 30KG · 93508900000</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>93508940000</t>
+          <t>93508900000</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11978,12 +11975,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 30KG · 93508950000</t>
+          <t>SUPRA ADULTO 4KG · 93508870000</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>93508950000</t>
+          <t>93508870000</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -11998,16 +11995,16 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 4KG · 93508920000</t>
+          <t>SUPRA CACHORRO 1.5KG · 93508910000</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>93508920000</t>
+          <t>93508910000</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12018,76 +12015,76 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>D TETRA REPTOMIN 1.94 OZ · 90410040000</t>
+          <t>SUPRA CACHORRO 18KG · 93508940000</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>90410040000</t>
+          <t>93508940000</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>SUPRA</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
+          <t>SUPRA CACHORRO 30KG · 93508950000</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>90409640000</t>
+          <t>93508950000</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>SUPRA</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TETRA BETTAMIN .81OZ  23GR · 90410310000</t>
+          <t>SUPRA CACHORRO 4KG · 93508920000</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>90410310000</t>
+          <t>93508920000</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>SUPRA</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>TETRA HOJUELA GOLDFISH 2.2OZ · 90409670000</t>
+          <t>D TETRA REPTOMIN 1.94 OZ · 90410040000</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>90409670000</t>
+          <t>90410040000</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12098,16 +12095,16 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>TETRA HOJUELAS GOLDFISH .42OZ · 90409900000</t>
+          <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>90409900000</t>
+          <t>90409640000</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12118,16 +12115,16 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TETRA HOJUELAS GOLDFISH 3.53OZ · 90409910000</t>
+          <t>TETRA BETTAMIN .81OZ  23GR · 90410310000</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>90409910000</t>
+          <t>90410310000</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12138,16 +12135,16 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TETRA HOJUELAS TROPICAL 0.42OZ · 90409920000</t>
+          <t>TETRA HOJUELA GOLDFISH 2.2OZ · 90409670000</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>90409920000</t>
+          <t>90409670000</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12158,16 +12155,16 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
+          <t>TETRA HOJUELAS GOLDFISH .42OZ · 90409900000</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>90410990000</t>
+          <t>90409900000</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12178,98 +12175,118 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>D TRIUMPH LATA POLLO ARROZ VEG 13.2OZ · 90412960000</t>
+          <t>TETRA HOJUELAS GOLDFISH 3.53OZ · 90409910000</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>90412960000</t>
+          <t>90409910000</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>TRIUMPH</t>
+          <t>TETRA</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>D ZM ALIMENTO EN BLOQUE P TORTUGAS 5 · 93517490000</t>
+          <t>TETRA HOJUELAS TROPICAL 0.42OZ · 90409920000</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>93517490000</t>
+          <t>90409920000</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ZOO MED</t>
+          <t>TETRA</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ZM CALCIO GDE CON VEGETALES P/AVES · 93503050000</t>
+          <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>93503050000</t>
+          <t>90410990000</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ZOO MED</t>
+          <t>TETRA</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ZM CALCIO PQNO CON VEGETALES P/AVES · 93503060000</t>
+          <t>D TRIUMPH LATA POLLO ARROZ VEG 13.2OZ · 90412960000</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>93503060000</t>
+          <t>90412960000</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ZOO MED</t>
+          <t>TRIUMPH</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ZM MICRO PELLET P/BETTA 0.12OZ · 93514830000</t>
+          <t>D ZM ALIMENTO EN BLOQUE P TORTUGAS 5 · 93517490000</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>93514830000</t>
+          <t>93517490000</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D135" t="inlineStr">
+        <is>
+          <t>ZOO MED</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ZM CALCIO GDE CON VEGETALES P/AVES · 93503050000</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>93503050000</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>10</v>
+      </c>
+      <c r="D136" t="inlineStr">
         <is>
           <t>ZOO MED</t>
         </is>
@@ -12278,34 +12295,74 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sucursal</t>
+          <t>ZM CALCIO PQNO CON VEGETALES P/AVES · 93503060000</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MELO &amp; CIA. | SAN VICENTE</t>
+          <t>93503060000</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>2</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>ZOO MED</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
+          <t>ZM MICRO PELLET P/BETTA 0.12OZ · 93514830000</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>93514830000</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>8</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>ZOO MED</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>MELO &amp; CIA. | SAN VICENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
           <t>Índice</t>
         </is>
       </c>
-      <c r="B138" t="n">
+      <c r="B141" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>Inventario al</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>28.10.2026</t>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>29.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/20.xlsx
+++ b/plantillas/20.xlsx
@@ -9804,7 +9804,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>30.10.2026</t>
         </is>
       </c>
     </row>
